--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6F1C84-9309-4002-8ECC-B989F4495A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDB6937-1463-4E4A-972F-A6A7EAB85AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateCustomerAndSession" sheetId="25" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4189" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="1235">
   <si>
     <t>ZZ</t>
   </si>
@@ -3797,13 +3797,182 @@
   <si>
     <t>2026-02-17 14:56:24</t>
   </si>
+  <si>
+    <t>699444d3ee1d5b7e420b813e</t>
+  </si>
+  <si>
+    <t>2026-02-17 16:07:57</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/customerverification.jsp" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 144.0.7559.134, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62693}, goog:processID: 60312, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62693/devtoo..., se:cdpVersion: 144.0.7559.134, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e6d0b9a38764281625154f7e8cf6c1f2</t>
+  </si>
+  <si>
+    <t>69944579ee1d5b7e420b84e3</t>
+  </si>
+  <si>
+    <t>2026-02-17 16:13:57</t>
+  </si>
+  <si>
+    <t>6994466dee1d5b7e420b8c0f</t>
+  </si>
+  <si>
+    <t>2026-02-17 16:19:46</t>
+  </si>
+  <si>
+    <t>6994599f69e2a855582b09a9</t>
+  </si>
+  <si>
+    <t>2026-02-17 17:40:58</t>
+  </si>
+  <si>
+    <t>69945ac369e2a855582b17a7</t>
+  </si>
+  <si>
+    <t>2026-02-17 17:46:35</t>
+  </si>
+  <si>
+    <t>69945b4f69e2a855582b1b9a</t>
+  </si>
+  <si>
+    <t>2026-02-17 17:48:54</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Error communicating with the remote browser. It may have died.
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [dd4ff92922dfba5e8c515c82271460f2, getCurrentUrl []]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 144.0.7559.134, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60537}, goog:processID: 55248, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60537/devtoo..., se:cdpVersion: 144.0.7559.134, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: dd4ff92922dfba5e8c515c82271460f2</t>
+  </si>
+  <si>
+    <t>69945c6a69e2a855582b1bde</t>
+  </si>
+  <si>
+    <t>2026-02-17 17:50:13</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/customerverification.jsp" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 144.0.7559.134, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55895}, goog:processID: 49648, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55895/devtoo..., se:cdpVersion: 144.0.7559.134, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 197b9818a1c972e430b7e36731a17768</t>
+  </si>
+  <si>
+    <t>69945d1f69e2a855582b1f33</t>
+  </si>
+  <si>
+    <t>2026-02-17 17:56:53</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Error communicating with the remote browser. It may have died.
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [677018c7e31292453c3766edbaf7197c, getCurrentUrl []]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 144.0.7559.134, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:50974}, goog:processID: 4860, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:50974/devtoo..., se:cdpVersion: 144.0.7559.134, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 677018c7e31292453c3766edbaf7197c</t>
+  </si>
+  <si>
+    <t>69945ead69e2a855582b2b4f</t>
+  </si>
+  <si>
+    <t>2026-02-17 17:59:41</t>
+  </si>
+  <si>
+    <t>69945ff469e2a855582b3e87</t>
+  </si>
+  <si>
+    <t>2026-02-17 18:03:43</t>
+  </si>
+  <si>
+    <t>6994606f69e2a855582b4aac</t>
+  </si>
+  <si>
+    <t>2026-02-17 18:05:35</t>
+  </si>
+  <si>
+    <t>699463c469e2a855582b728f</t>
+  </si>
+  <si>
+    <t>2026-02-17 18:19:21</t>
+  </si>
+  <si>
+    <t>6994640d69e2a855582b7620</t>
+  </si>
+  <si>
+    <t>2026-02-17 18:20:34</t>
+  </si>
+  <si>
+    <t>699549ae69e2a855582bb2e0</t>
+  </si>
+  <si>
+    <t>2026-02-18 10:40:24</t>
+  </si>
+  <si>
+    <t>69954bd769e2a855582bb9d5</t>
+  </si>
+  <si>
+    <t>2026-02-18 10:49:36</t>
+  </si>
+  <si>
+    <t>699549ff69e2a855582bb688</t>
+  </si>
+  <si>
+    <t>euroexchange</t>
+  </si>
+  <si>
+    <t>2026-02-18 10:50:41</t>
+  </si>
+  <si>
+    <t>69954fe069e2a855582bc39a</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:06:49</t>
+  </si>
+  <si>
+    <t>6995500a69e2a855582bc712</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:07:29</t>
+  </si>
+  <si>
+    <t>6995516069e2a855582bcd81</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:13:13</t>
+  </si>
+  <si>
+    <t>699551c269e2a855582bd137</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:14:48</t>
+  </si>
+  <si>
+    <t>699553c269e2a855582bd780</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:23:33</t>
+  </si>
+  <si>
+    <t>6995543169e2a855582bdb13</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:30:12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="823" x14ac:knownFonts="1">
+  <fonts count="553" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6013,2486 +6182,1012 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -8688,7 +7383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="824">
+  <cellXfs count="554">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9764,508 +8459,508 @@
     <xf numFmtId="0" fontId="357" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="358" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="359" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="361" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="363" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="365" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="367" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="369" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="371" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="373" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="374" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="375" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="377" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="378" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="379" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="380" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="381" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="382" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="392" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="394" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="396" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="398" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="399" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="400" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="402" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="404" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="407" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="408" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="409" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="410" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="411" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="412" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="413" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="414" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="415" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="416" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="417" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="418" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="419" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="420" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="422" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="423" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="425" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="426" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="427" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="428" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="429" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="430" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="431" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="432" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="433" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="434" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="435" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="436" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="437" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="438" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="440" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="441" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="442" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="443" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="444" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="446" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="447" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="450" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="451" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="452" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="453" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="455" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="456" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="458" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="459" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="460" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="461" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="462" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="464" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="465" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="466" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="467" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="468" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="470" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="471" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="472" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="473" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="474" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="475" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="476" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="477" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="478" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="479" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="480" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="481" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="482" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="483" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="484" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="485" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="486" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="487" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="488" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="489" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="490" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="491" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="492" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="493" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="494" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="495" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="496" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="497" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="498" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="499" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="500" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="501" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="502" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="503" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="504" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="505" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="506" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="507" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="508" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="509" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="510" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="511" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="512" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="513" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="514" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="515" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="516" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="518" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="519" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="521" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="522" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="524" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="525" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="358" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
@@ -10347,816 +9042,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="552" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="554" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="555" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="557" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="558" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="560" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="561" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="563" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="564" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="566" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="567" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="569" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="570" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="572" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="573" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="575" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="576" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="578" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="579" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="581" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="582" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="583" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="584" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="585" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="586" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="587" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="588" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="589" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="590" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="591" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="593" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="595" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="597" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="600" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="601" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="602" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="604" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="606" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="612" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="627" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="628" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="630" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="632" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="634" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="636" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="638" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="639" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="640" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="641" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="642" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="643" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="644" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="645" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="646" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="647" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="648" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="649" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="650" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="651" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="652" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="653" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="654" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="655" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="656" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="657" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="658" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="659" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="660" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="661" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="662" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="663" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="664" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="665" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="666" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="667" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="668" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="669" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="670" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="671" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="672" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="673" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="674" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="675" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="676" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="677" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="678" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="679" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="680" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="681" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="682" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="683" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="684" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="685" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="686" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="687" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="688" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="689" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="690" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="691" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="692" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="693" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="694" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="695" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="696" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="697" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="698" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="699" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="700" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="701" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="702" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="703" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="704" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="705" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="706" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="707" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="708" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="709" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="710" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="711" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="712" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="714" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="716" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="717" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="718" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="719" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="720" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="721" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="722" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="723" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="724" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="725" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="726" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="727" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="728" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="729" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="730" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="731" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="732" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="733" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="734" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="735" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="736" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="737" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="738" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="739" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="740" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="741" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="742" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="743" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="744" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="745" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="746" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="747" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="748" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="749" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="750" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="751" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="752" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="753" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="754" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="755" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="756" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="757" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="758" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="759" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="760" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="761" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="762" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="763" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="764" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="765" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="767" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="768" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="769" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="770" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="771" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="772" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="773" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="775" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="777" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="779" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="781" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="783" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="784" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="785" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="786" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="787" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="788" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="789" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="791" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="793" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="794" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="795" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="796" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="797" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="799" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="800" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="801" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="803" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="805" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="807" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="809" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="810" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="811" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="812" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="813" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="814" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="815" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="816" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="817" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="818" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="819" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="820" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="821" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="822" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -12743,7 +10628,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s" s="0">
         <v>74</v>
       </c>
@@ -12753,7 +10638,7 @@
       <c r="C60" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="D60" s="360" t="s">
+      <c r="D60" s="359" t="s">
         <v>836</v>
       </c>
       <c r="E60" t="s" s="0">
@@ -12769,7 +10654,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s" s="0">
         <v>446</v>
       </c>
@@ -12779,7 +10664,7 @@
       <c r="C61" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="D61" s="363" t="s">
+      <c r="D61" s="360" t="s">
         <v>836</v>
       </c>
       <c r="E61" t="s" s="0">
@@ -12802,7 +10687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA34F65-7F3E-463D-89AD-80F26EAF0109}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="32.1796875"/>
@@ -16567,6 +14452,84 @@
         <v>831</v>
       </c>
     </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A146" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D146" s="517" t="s">
+        <v>652</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>1193</v>
+      </c>
+      <c r="F146" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G146" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H146" t="s" s="0">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A147" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C147" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D147" s="525" t="s">
+        <v>99</v>
+      </c>
+      <c r="E147" t="s" s="0">
+        <v>1212</v>
+      </c>
+      <c r="F147" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G147" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H147" t="s" s="0">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C148" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D148" s="526" t="s">
+        <v>99</v>
+      </c>
+      <c r="E148" t="s" s="0">
+        <v>1214</v>
+      </c>
+      <c r="F148" t="s" s="0">
+        <v>1086</v>
+      </c>
+      <c r="G148" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H148" t="s" s="0">
+        <v>1215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16574,7 +14537,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61A2F25-557C-42DF-BC8E-85ED6FEA9686}">
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="31.81640625"/>
@@ -20352,7 +18315,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s" s="0">
         <v>505</v>
       </c>
@@ -20362,7 +18325,7 @@
       <c r="C151" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D151" s="367" t="s">
+      <c r="D151" s="361" t="s">
         <v>843</v>
       </c>
       <c r="E151" t="s" s="0">
@@ -20378,7 +18341,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s" s="0">
         <v>512</v>
       </c>
@@ -20388,7 +18351,7 @@
       <c r="C152" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D152" s="370" t="s">
+      <c r="D152" s="362" t="s">
         <v>843</v>
       </c>
       <c r="E152" t="s" s="0">
@@ -20404,7 +18367,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s" s="0">
         <v>505</v>
       </c>
@@ -20414,7 +18377,7 @@
       <c r="C153" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D153" s="373" t="s">
+      <c r="D153" s="363" t="s">
         <v>843</v>
       </c>
       <c r="E153" t="s" s="0">
@@ -20430,7 +18393,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s" s="0">
         <v>512</v>
       </c>
@@ -20440,7 +18403,7 @@
       <c r="C154" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D154" s="376" t="s">
+      <c r="D154" s="364" t="s">
         <v>843</v>
       </c>
       <c r="E154" t="s" s="0">
@@ -20456,7 +18419,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s" s="0">
         <v>239</v>
       </c>
@@ -20466,7 +18429,7 @@
       <c r="C155" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D155" s="379" t="s">
+      <c r="D155" s="365" t="s">
         <v>853</v>
       </c>
       <c r="E155" t="s" s="0">
@@ -20482,7 +18445,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s" s="0">
         <v>233</v>
       </c>
@@ -20492,7 +18455,7 @@
       <c r="C156" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D156" s="382" t="s">
+      <c r="D156" s="366" t="s">
         <v>853</v>
       </c>
       <c r="E156" t="s" s="0">
@@ -20508,7 +18471,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s" s="0">
         <v>233</v>
       </c>
@@ -20518,7 +18481,7 @@
       <c r="C157" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D157" s="385" t="s">
+      <c r="D157" s="367" t="s">
         <v>853</v>
       </c>
       <c r="E157" t="s" s="0">
@@ -20534,7 +18497,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s" s="0">
         <v>239</v>
       </c>
@@ -20544,7 +18507,7 @@
       <c r="C158" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D158" s="388" t="s">
+      <c r="D158" s="368" t="s">
         <v>853</v>
       </c>
       <c r="E158" t="s" s="0">
@@ -20560,7 +18523,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s" s="0">
         <v>409</v>
       </c>
@@ -20570,7 +18533,7 @@
       <c r="C159" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D159" s="391" t="s">
+      <c r="D159" s="369" t="s">
         <v>843</v>
       </c>
       <c r="E159" t="s" s="0">
@@ -20586,7 +18549,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s" s="0">
         <v>864</v>
       </c>
@@ -20596,7 +18559,7 @@
       <c r="C160" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D160" s="394" t="s">
+      <c r="D160" s="370" t="s">
         <v>843</v>
       </c>
       <c r="E160" t="s" s="0">
@@ -20612,7 +18575,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" t="s" s="0">
         <v>867</v>
       </c>
@@ -20622,7 +18585,7 @@
       <c r="C161" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D161" s="397" t="s">
+      <c r="D161" s="371" t="s">
         <v>843</v>
       </c>
       <c r="E161" t="s" s="0">
@@ -20638,7 +18601,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" t="s" s="0">
         <v>870</v>
       </c>
@@ -20648,7 +18611,7 @@
       <c r="C162" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D162" s="400" t="s">
+      <c r="D162" s="372" t="s">
         <v>843</v>
       </c>
       <c r="E162" t="s" s="0">
@@ -20664,7 +18627,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" t="s" s="0">
         <v>873</v>
       </c>
@@ -20674,7 +18637,7 @@
       <c r="C163" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D163" s="403" t="s">
+      <c r="D163" s="373" t="s">
         <v>843</v>
       </c>
       <c r="E163" t="s" s="0">
@@ -20690,7 +18653,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s" s="0">
         <v>239</v>
       </c>
@@ -20700,7 +18663,7 @@
       <c r="C164" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D164" s="406" t="s">
+      <c r="D164" s="374" t="s">
         <v>853</v>
       </c>
       <c r="E164" t="s" s="0">
@@ -20716,7 +18679,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" t="s" s="0">
         <v>233</v>
       </c>
@@ -20726,7 +18689,7 @@
       <c r="C165" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D165" s="409" t="s">
+      <c r="D165" s="375" t="s">
         <v>853</v>
       </c>
       <c r="E165" t="s" s="0">
@@ -20742,7 +18705,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" t="s" s="0">
         <v>233</v>
       </c>
@@ -20752,7 +18715,7 @@
       <c r="C166" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D166" s="412" t="s">
+      <c r="D166" s="376" t="s">
         <v>853</v>
       </c>
       <c r="E166" t="s" s="0">
@@ -20768,7 +18731,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" t="s" s="0">
         <v>239</v>
       </c>
@@ -20778,7 +18741,7 @@
       <c r="C167" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D167" s="415" t="s">
+      <c r="D167" s="377" t="s">
         <v>853</v>
       </c>
       <c r="E167" t="s" s="0">
@@ -20794,7 +18757,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" t="s" s="0">
         <v>233</v>
       </c>
@@ -20804,7 +18767,7 @@
       <c r="C168" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D168" s="418" t="s">
+      <c r="D168" s="378" t="s">
         <v>853</v>
       </c>
       <c r="E168" t="s" s="0">
@@ -20820,7 +18783,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" t="s" s="0">
         <v>233</v>
       </c>
@@ -20830,7 +18793,7 @@
       <c r="C169" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D169" s="421" t="s">
+      <c r="D169" s="379" t="s">
         <v>853</v>
       </c>
       <c r="E169" t="s" s="0">
@@ -20846,7 +18809,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" t="s" s="0">
         <v>239</v>
       </c>
@@ -20856,7 +18819,7 @@
       <c r="C170" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D170" s="424" t="s">
+      <c r="D170" s="380" t="s">
         <v>853</v>
       </c>
       <c r="E170" t="s" s="0">
@@ -20872,7 +18835,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" t="s" s="0">
         <v>233</v>
       </c>
@@ -20882,7 +18845,7 @@
       <c r="C171" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D171" s="427" t="s">
+      <c r="D171" s="381" t="s">
         <v>853</v>
       </c>
       <c r="E171" t="s" s="0">
@@ -20898,7 +18861,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" t="s" s="0">
         <v>239</v>
       </c>
@@ -20908,7 +18871,7 @@
       <c r="C172" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D172" s="430" t="s">
+      <c r="D172" s="382" t="s">
         <v>853</v>
       </c>
       <c r="E172" t="s" s="0">
@@ -20924,7 +18887,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s" s="0">
         <v>233</v>
       </c>
@@ -20934,7 +18897,7 @@
       <c r="C173" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D173" s="433" t="s">
+      <c r="D173" s="383" t="s">
         <v>853</v>
       </c>
       <c r="E173" t="s" s="0">
@@ -20950,7 +18913,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" t="s" s="0">
         <v>233</v>
       </c>
@@ -20960,7 +18923,7 @@
       <c r="C174" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D174" s="436" t="s">
+      <c r="D174" s="384" t="s">
         <v>853</v>
       </c>
       <c r="E174" t="s" s="0">
@@ -20976,7 +18939,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" t="s" s="0">
         <v>236</v>
       </c>
@@ -20986,7 +18949,7 @@
       <c r="C175" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D175" s="439" t="s">
+      <c r="D175" s="385" t="s">
         <v>853</v>
       </c>
       <c r="E175" t="s" s="0">
@@ -21002,7 +18965,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" t="s" s="0">
         <v>239</v>
       </c>
@@ -21012,7 +18975,7 @@
       <c r="C176" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D176" s="442" t="s">
+      <c r="D176" s="386" t="s">
         <v>853</v>
       </c>
       <c r="E176" t="s" s="0">
@@ -21028,7 +18991,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" t="s" s="0">
         <v>233</v>
       </c>
@@ -21038,7 +19001,7 @@
       <c r="C177" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D177" s="445" t="s">
+      <c r="D177" s="387" t="s">
         <v>853</v>
       </c>
       <c r="E177" t="s" s="0">
@@ -21054,7 +19017,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" t="s" s="0">
         <v>239</v>
       </c>
@@ -21064,7 +19027,7 @@
       <c r="C178" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D178" s="448" t="s">
+      <c r="D178" s="388" t="s">
         <v>853</v>
       </c>
       <c r="E178" t="s" s="0">
@@ -21080,7 +19043,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" t="s" s="0">
         <v>239</v>
       </c>
@@ -21090,7 +19053,7 @@
       <c r="C179" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D179" s="451" t="s">
+      <c r="D179" s="389" t="s">
         <v>853</v>
       </c>
       <c r="E179" t="s" s="0">
@@ -21106,7 +19069,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" t="s" s="0">
         <v>233</v>
       </c>
@@ -21116,7 +19079,7 @@
       <c r="C180" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D180" s="454" t="s">
+      <c r="D180" s="390" t="s">
         <v>853</v>
       </c>
       <c r="E180" t="s" s="0">
@@ -21132,7 +19095,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" t="s" s="0">
         <v>233</v>
       </c>
@@ -21142,7 +19105,7 @@
       <c r="C181" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D181" s="457" t="s">
+      <c r="D181" s="391" t="s">
         <v>853</v>
       </c>
       <c r="E181" t="s" s="0">
@@ -21158,7 +19121,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" t="s" s="0">
         <v>236</v>
       </c>
@@ -21168,7 +19131,7 @@
       <c r="C182" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D182" s="460" t="s">
+      <c r="D182" s="392" t="s">
         <v>853</v>
       </c>
       <c r="E182" t="s" s="0">
@@ -21184,7 +19147,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" t="s" s="0">
         <v>239</v>
       </c>
@@ -21194,7 +19157,7 @@
       <c r="C183" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D183" s="463" t="s">
+      <c r="D183" s="393" t="s">
         <v>853</v>
       </c>
       <c r="E183" t="s" s="0">
@@ -21210,7 +19173,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" t="s" s="0">
         <v>239</v>
       </c>
@@ -21220,7 +19183,7 @@
       <c r="C184" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D184" s="466" t="s">
+      <c r="D184" s="394" t="s">
         <v>916</v>
       </c>
       <c r="E184" t="s" s="0">
@@ -21236,7 +19199,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" t="s" s="0">
         <v>239</v>
       </c>
@@ -21246,7 +19209,7 @@
       <c r="C185" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D185" s="469" t="s">
+      <c r="D185" s="395" t="s">
         <v>916</v>
       </c>
       <c r="E185" t="s" s="0">
@@ -21262,7 +19225,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" t="s" s="0">
         <v>233</v>
       </c>
@@ -21272,7 +19235,7 @@
       <c r="C186" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D186" s="472" t="s">
+      <c r="D186" s="396" t="s">
         <v>916</v>
       </c>
       <c r="E186" t="s" s="0">
@@ -21288,7 +19251,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" t="s" s="0">
         <v>233</v>
       </c>
@@ -21298,7 +19261,7 @@
       <c r="C187" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D187" s="475" t="s">
+      <c r="D187" s="397" t="s">
         <v>916</v>
       </c>
       <c r="E187" t="s" s="0">
@@ -21314,7 +19277,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" t="s" s="0">
         <v>236</v>
       </c>
@@ -21324,7 +19287,7 @@
       <c r="C188" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D188" s="478" t="s">
+      <c r="D188" s="398" t="s">
         <v>916</v>
       </c>
       <c r="E188" t="s" s="0">
@@ -21340,7 +19303,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" t="s" s="0">
         <v>239</v>
       </c>
@@ -21350,7 +19313,7 @@
       <c r="C189" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D189" s="481" t="s">
+      <c r="D189" s="399" t="s">
         <v>916</v>
       </c>
       <c r="E189" t="s" s="0">
@@ -21366,7 +19329,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" t="s" s="0">
         <v>242</v>
       </c>
@@ -21376,7 +19339,7 @@
       <c r="C190" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D190" s="484" t="s">
+      <c r="D190" s="400" t="s">
         <v>916</v>
       </c>
       <c r="E190" t="s" s="0">
@@ -21392,7 +19355,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" t="s" s="0">
         <v>594</v>
       </c>
@@ -21402,10 +19365,9 @@
       <c r="C191" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D191" s="487" t="s">
+      <c r="D191" s="401" t="s">
         <v>932</v>
       </c>
-      <c r="E191" s="0"/>
       <c r="F191" t="s" s="0">
         <v>918</v>
       </c>
@@ -21416,7 +19378,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" t="s" s="0">
         <v>597</v>
       </c>
@@ -21426,7 +19388,7 @@
       <c r="C192" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D192" s="490" t="s">
+      <c r="D192" s="402" t="s">
         <v>916</v>
       </c>
       <c r="E192" t="s" s="0">
@@ -21442,7 +19404,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" t="s" s="0">
         <v>936</v>
       </c>
@@ -21452,7 +19414,7 @@
       <c r="C193" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D193" s="493" t="s">
+      <c r="D193" s="403" t="s">
         <v>916</v>
       </c>
       <c r="E193" t="s" s="0">
@@ -21468,7 +19430,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" t="s" s="0">
         <v>939</v>
       </c>
@@ -21478,7 +19440,7 @@
       <c r="C194" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D194" s="496" t="s">
+      <c r="D194" s="404" t="s">
         <v>916</v>
       </c>
       <c r="E194" t="s" s="0">
@@ -21494,7 +19456,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" t="s" s="0">
         <v>942</v>
       </c>
@@ -21504,7 +19466,7 @@
       <c r="C195" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D195" s="499" t="s">
+      <c r="D195" s="405" t="s">
         <v>916</v>
       </c>
       <c r="E195" t="s" s="0">
@@ -21520,7 +19482,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" t="s" s="0">
         <v>219</v>
       </c>
@@ -21530,7 +19492,7 @@
       <c r="C196" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D196" s="502" t="s">
+      <c r="D196" s="406" t="s">
         <v>916</v>
       </c>
       <c r="E196" t="s" s="0">
@@ -21546,7 +19508,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" t="s" s="0">
         <v>947</v>
       </c>
@@ -21556,7 +19518,7 @@
       <c r="C197" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D197" s="505" t="s">
+      <c r="D197" s="407" t="s">
         <v>916</v>
       </c>
       <c r="E197" t="s" s="0">
@@ -21572,7 +19534,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" t="s" s="0">
         <v>236</v>
       </c>
@@ -21582,7 +19544,7 @@
       <c r="C198" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D198" s="508" t="s">
+      <c r="D198" s="408" t="s">
         <v>916</v>
       </c>
       <c r="E198" t="s" s="0">
@@ -21598,7 +19560,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" t="s" s="0">
         <v>239</v>
       </c>
@@ -21608,7 +19570,7 @@
       <c r="C199" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D199" s="511" t="s">
+      <c r="D199" s="409" t="s">
         <v>916</v>
       </c>
       <c r="E199" t="s" s="0">
@@ -21624,7 +19586,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" t="s" s="0">
         <v>239</v>
       </c>
@@ -21634,7 +19596,7 @@
       <c r="C200" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D200" s="514" t="s">
+      <c r="D200" s="410" t="s">
         <v>954</v>
       </c>
       <c r="E200" t="s" s="0">
@@ -21650,7 +19612,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s" s="0">
         <v>239</v>
       </c>
@@ -21660,7 +19622,7 @@
       <c r="C201" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D201" s="517" t="s">
+      <c r="D201" s="411" t="s">
         <v>957</v>
       </c>
       <c r="E201" t="s" s="0">
@@ -21676,7 +19638,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" t="s" s="0">
         <v>239</v>
       </c>
@@ -21686,7 +19648,7 @@
       <c r="C202" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D202" s="520" t="s">
+      <c r="D202" s="412" t="s">
         <v>339</v>
       </c>
       <c r="E202" t="s" s="0">
@@ -21702,7 +19664,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" t="s" s="0">
         <v>239</v>
       </c>
@@ -21712,10 +19674,9 @@
       <c r="C203" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D203" s="523" t="s">
+      <c r="D203" s="413" t="s">
         <v>932</v>
       </c>
-      <c r="E203" s="0"/>
       <c r="F203" t="s" s="0">
         <v>918</v>
       </c>
@@ -21726,7 +19687,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" t="s" s="0">
         <v>239</v>
       </c>
@@ -21736,7 +19697,7 @@
       <c r="C204" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D204" s="526" t="s">
+      <c r="D204" s="414" t="s">
         <v>339</v>
       </c>
       <c r="E204" t="s" s="0">
@@ -21752,7 +19713,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" t="s" s="0">
         <v>239</v>
       </c>
@@ -21762,7 +19723,7 @@
       <c r="C205" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D205" s="529" t="s">
+      <c r="D205" s="415" t="s">
         <v>965</v>
       </c>
       <c r="E205" t="s" s="0">
@@ -21778,7 +19739,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" t="s" s="0">
         <v>239</v>
       </c>
@@ -21788,7 +19749,7 @@
       <c r="C206" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D206" s="531" t="s">
+      <c r="D206" s="416" t="s">
         <v>304</v>
       </c>
       <c r="E206" t="s" s="0">
@@ -21804,7 +19765,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" t="s" s="0">
         <v>239</v>
       </c>
@@ -21814,7 +19775,7 @@
       <c r="C207" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D207" s="535" t="s">
+      <c r="D207" s="417" t="s">
         <v>339</v>
       </c>
       <c r="E207" t="s" s="0">
@@ -21830,7 +19791,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" t="s" s="0">
         <v>239</v>
       </c>
@@ -21840,7 +19801,7 @@
       <c r="C208" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D208" s="538" t="s">
+      <c r="D208" s="418" t="s">
         <v>339</v>
       </c>
       <c r="E208" t="s" s="0">
@@ -21856,7 +19817,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" t="s" s="0">
         <v>239</v>
       </c>
@@ -21866,7 +19827,7 @@
       <c r="C209" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D209" s="541" t="s">
+      <c r="D209" s="419" t="s">
         <v>339</v>
       </c>
       <c r="E209" t="s" s="0">
@@ -21882,7 +19843,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" t="s" s="0">
         <v>239</v>
       </c>
@@ -21892,7 +19853,7 @@
       <c r="C210" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D210" s="544" t="s">
+      <c r="D210" s="420" t="s">
         <v>976</v>
       </c>
       <c r="E210" t="s" s="0">
@@ -21908,7 +19869,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" t="s" s="0">
         <v>239</v>
       </c>
@@ -21918,7 +19879,7 @@
       <c r="C211" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D211" s="547" t="s">
+      <c r="D211" s="421" t="s">
         <v>979</v>
       </c>
       <c r="E211" t="s" s="0">
@@ -21934,7 +19895,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" t="s" s="0">
         <v>239</v>
       </c>
@@ -21944,7 +19905,7 @@
       <c r="C212" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D212" s="550" t="s">
+      <c r="D212" s="422" t="s">
         <v>339</v>
       </c>
       <c r="E212" t="s" s="0">
@@ -21960,7 +19921,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" t="s" s="0">
         <v>239</v>
       </c>
@@ -21970,7 +19931,7 @@
       <c r="C213" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D213" s="553" t="s">
+      <c r="D213" s="423" t="s">
         <v>339</v>
       </c>
       <c r="E213" t="s" s="0">
@@ -21986,7 +19947,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" t="s" s="0">
         <v>239</v>
       </c>
@@ -21996,10 +19957,9 @@
       <c r="C214" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D214" s="556" t="s">
+      <c r="D214" s="424" t="s">
         <v>932</v>
       </c>
-      <c r="E214" s="0"/>
       <c r="F214" t="s" s="0">
         <v>183</v>
       </c>
@@ -22010,7 +19970,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" t="s" s="0">
         <v>987</v>
       </c>
@@ -22020,7 +19980,7 @@
       <c r="C215" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D215" s="559" t="s">
+      <c r="D215" s="425" t="s">
         <v>988</v>
       </c>
       <c r="E215" t="s" s="0">
@@ -22036,7 +19996,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" t="s" s="0">
         <v>987</v>
       </c>
@@ -22046,7 +20006,7 @@
       <c r="C216" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D216" s="562" t="s">
+      <c r="D216" s="426" t="s">
         <v>991</v>
       </c>
       <c r="E216" t="s" s="0">
@@ -22062,7 +20022,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" t="s" s="0">
         <v>987</v>
       </c>
@@ -22072,7 +20032,7 @@
       <c r="C217" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D217" s="565" t="s">
+      <c r="D217" s="427" t="s">
         <v>994</v>
       </c>
       <c r="E217" t="s" s="0">
@@ -22088,7 +20048,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" t="s" s="0">
         <v>987</v>
       </c>
@@ -22098,7 +20058,7 @@
       <c r="C218" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D218" s="568" t="s">
+      <c r="D218" s="428" t="s">
         <v>997</v>
       </c>
       <c r="E218" t="s" s="0">
@@ -22114,7 +20074,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" t="s" s="0">
         <v>987</v>
       </c>
@@ -22124,7 +20084,7 @@
       <c r="C219" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D219" s="571" t="s">
+      <c r="D219" s="429" t="s">
         <v>339</v>
       </c>
       <c r="E219" t="s" s="0">
@@ -22140,7 +20100,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" t="s" s="0">
         <v>987</v>
       </c>
@@ -22150,7 +20110,7 @@
       <c r="C220" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D220" s="574" t="s">
+      <c r="D220" s="430" t="s">
         <v>339</v>
       </c>
       <c r="E220" t="s" s="0">
@@ -22166,7 +20126,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22176,7 +20136,7 @@
       <c r="C221" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D221" s="577" t="s">
+      <c r="D221" s="431" t="s">
         <v>1005</v>
       </c>
       <c r="E221" t="s" s="0">
@@ -22192,7 +20152,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22202,7 +20162,7 @@
       <c r="C222" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D222" s="580" t="s">
+      <c r="D222" s="432" t="s">
         <v>1008</v>
       </c>
       <c r="E222" t="s" s="0">
@@ -22218,7 +20178,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" t="s" s="0">
         <v>236</v>
       </c>
@@ -22228,7 +20188,7 @@
       <c r="C223" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D223" s="583" t="s">
+      <c r="D223" s="433" t="s">
         <v>1011</v>
       </c>
       <c r="E223" t="s" s="0">
@@ -22244,7 +20204,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" t="s" s="0">
         <v>987</v>
       </c>
@@ -22254,10 +20214,9 @@
       <c r="C224" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D224" s="586" t="s">
+      <c r="D224" s="434" t="s">
         <v>932</v>
       </c>
-      <c r="E224" s="0"/>
       <c r="F224" t="s" s="0">
         <v>183</v>
       </c>
@@ -22268,7 +20227,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" t="s" s="0">
         <v>987</v>
       </c>
@@ -22278,7 +20237,7 @@
       <c r="C225" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D225" s="589" t="s">
+      <c r="D225" s="435" t="s">
         <v>1016</v>
       </c>
       <c r="E225" t="s" s="0">
@@ -22294,7 +20253,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" t="s" s="0">
         <v>987</v>
       </c>
@@ -22304,7 +20263,7 @@
       <c r="C226" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D226" s="592" t="s">
+      <c r="D226" s="436" t="s">
         <v>1016</v>
       </c>
       <c r="E226" t="s" s="0">
@@ -22320,7 +20279,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" t="s" s="0">
         <v>987</v>
       </c>
@@ -22330,7 +20289,7 @@
       <c r="C227" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D227" s="595" t="s">
+      <c r="D227" s="437" t="s">
         <v>1016</v>
       </c>
       <c r="E227" t="s" s="0">
@@ -22346,7 +20305,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228" t="s" s="0">
         <v>987</v>
       </c>
@@ -22356,7 +20315,7 @@
       <c r="C228" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D228" s="598" t="s">
+      <c r="D228" s="438" t="s">
         <v>1016</v>
       </c>
       <c r="E228" t="s" s="0">
@@ -22372,7 +20331,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229" t="s" s="0">
         <v>987</v>
       </c>
@@ -22382,7 +20341,7 @@
       <c r="C229" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D229" s="600" t="s">
+      <c r="D229" s="439" t="s">
         <v>304</v>
       </c>
       <c r="E229" t="s" s="0">
@@ -22398,7 +20357,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22408,7 +20367,7 @@
       <c r="C230" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D230" s="603" t="s">
+      <c r="D230" s="440" t="s">
         <v>304</v>
       </c>
       <c r="E230" t="s" s="0">
@@ -22424,7 +20383,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A231" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22434,7 +20393,7 @@
       <c r="C231" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D231" s="606" t="s">
+      <c r="D231" s="441" t="s">
         <v>304</v>
       </c>
       <c r="E231" t="s" s="0">
@@ -22450,7 +20409,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A232" t="s" s="0">
         <v>236</v>
       </c>
@@ -22460,7 +20419,7 @@
       <c r="C232" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D232" s="609" t="s">
+      <c r="D232" s="442" t="s">
         <v>304</v>
       </c>
       <c r="E232" t="s" s="0">
@@ -22476,7 +20435,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233" t="s" s="0">
         <v>732</v>
       </c>
@@ -22486,7 +20445,7 @@
       <c r="C233" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D233" s="612" t="s">
+      <c r="D233" s="443" t="s">
         <v>72</v>
       </c>
       <c r="E233" t="s" s="0">
@@ -22502,7 +20461,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A234" t="s" s="0">
         <v>1036</v>
       </c>
@@ -22512,7 +20471,7 @@
       <c r="C234" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D234" s="615" t="s">
+      <c r="D234" s="444" t="s">
         <v>72</v>
       </c>
       <c r="E234" t="s" s="0">
@@ -22528,7 +20487,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A235" t="s" s="0">
         <v>1039</v>
       </c>
@@ -22538,7 +20497,7 @@
       <c r="C235" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D235" s="618" t="s">
+      <c r="D235" s="445" t="s">
         <v>72</v>
       </c>
       <c r="E235" t="s" s="0">
@@ -22554,7 +20513,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A236" t="s" s="0">
         <v>358</v>
       </c>
@@ -22564,7 +20523,7 @@
       <c r="C236" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D236" s="622" t="s">
+      <c r="D236" s="446" t="s">
         <v>72</v>
       </c>
       <c r="E236" t="s" s="0">
@@ -22580,7 +20539,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A237" t="s" s="0">
         <v>358</v>
       </c>
@@ -22590,7 +20549,7 @@
       <c r="C237" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D237" s="625" t="s">
+      <c r="D237" s="447" t="s">
         <v>72</v>
       </c>
       <c r="E237" t="s" s="0">
@@ -22606,7 +20565,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A238" t="s" s="0">
         <v>987</v>
       </c>
@@ -22616,7 +20575,7 @@
       <c r="C238" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D238" s="628" t="s">
+      <c r="D238" s="448" t="s">
         <v>339</v>
       </c>
       <c r="E238" t="s" s="0">
@@ -22632,7 +20591,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A239" t="s" s="0">
         <v>1048</v>
       </c>
@@ -22642,7 +20601,7 @@
       <c r="C239" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D239" s="631" t="s">
+      <c r="D239" s="449" t="s">
         <v>72</v>
       </c>
       <c r="E239" t="s" s="0">
@@ -22658,7 +20617,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A240" t="s" s="0">
         <v>987</v>
       </c>
@@ -22668,7 +20627,7 @@
       <c r="C240" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D240" s="633" t="s">
+      <c r="D240" s="450" t="s">
         <v>304</v>
       </c>
       <c r="E240" t="s" s="0">
@@ -22684,7 +20643,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22694,7 +20653,7 @@
       <c r="C241" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D241" s="636" t="s">
+      <c r="D241" s="451" t="s">
         <v>304</v>
       </c>
       <c r="E241" t="s" s="0">
@@ -22710,7 +20669,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242" t="s" s="0">
         <v>236</v>
       </c>
@@ -22720,7 +20679,7 @@
       <c r="C242" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D242" s="640" t="s">
+      <c r="D242" s="452" t="s">
         <v>1055</v>
       </c>
       <c r="E242" t="s" s="0">
@@ -22736,7 +20695,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243" t="s" s="0">
         <v>358</v>
       </c>
@@ -22746,7 +20705,7 @@
       <c r="C243" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D243" s="642" t="s">
+      <c r="D243" s="453" t="s">
         <v>72</v>
       </c>
       <c r="E243" t="s" s="0">
@@ -22762,7 +20721,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244" t="s" s="0">
         <v>987</v>
       </c>
@@ -22772,7 +20731,7 @@
       <c r="C244" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D244" s="645" t="s">
+      <c r="D244" s="454" t="s">
         <v>304</v>
       </c>
       <c r="E244" t="s" s="0">
@@ -22788,7 +20747,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22798,7 +20757,7 @@
       <c r="C245" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D245" s="648" t="s">
+      <c r="D245" s="455" t="s">
         <v>304</v>
       </c>
       <c r="E245" t="s" s="0">
@@ -22814,7 +20773,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22824,7 +20783,7 @@
       <c r="C246" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D246" s="651" t="s">
+      <c r="D246" s="456" t="s">
         <v>304</v>
       </c>
       <c r="E246" t="s" s="0">
@@ -22840,7 +20799,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247" t="s" s="0">
         <v>236</v>
       </c>
@@ -22850,7 +20809,7 @@
       <c r="C247" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D247" s="654" t="s">
+      <c r="D247" s="457" t="s">
         <v>304</v>
       </c>
       <c r="E247" t="s" s="0">
@@ -22866,7 +20825,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248" t="s" s="0">
         <v>987</v>
       </c>
@@ -22876,7 +20835,7 @@
       <c r="C248" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D248" s="657" t="s">
+      <c r="D248" s="458" t="s">
         <v>304</v>
       </c>
       <c r="E248" t="s" s="0">
@@ -22892,7 +20851,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22902,7 +20861,7 @@
       <c r="C249" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D249" s="660" t="s">
+      <c r="D249" s="459" t="s">
         <v>304</v>
       </c>
       <c r="E249" t="s" s="0">
@@ -22918,7 +20877,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250" t="s" s="0">
         <v>1004</v>
       </c>
@@ -22928,7 +20887,7 @@
       <c r="C250" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D250" s="663" t="s">
+      <c r="D250" s="460" t="s">
         <v>304</v>
       </c>
       <c r="E250" t="s" s="0">
@@ -22944,7 +20903,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251" t="s" s="0">
         <v>236</v>
       </c>
@@ -22954,7 +20913,7 @@
       <c r="C251" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D251" s="666" t="s">
+      <c r="D251" s="461" t="s">
         <v>304</v>
       </c>
       <c r="E251" t="s" s="0">
@@ -22970,7 +20929,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252" t="s" s="0">
         <v>239</v>
       </c>
@@ -22980,7 +20939,7 @@
       <c r="C252" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D252" s="670" t="s">
+      <c r="D252" s="462" t="s">
         <v>1076</v>
       </c>
       <c r="E252" t="s" s="0">
@@ -22996,7 +20955,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253" t="s" s="0">
         <v>242</v>
       </c>
@@ -23006,7 +20965,7 @@
       <c r="C253" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D253" s="672" t="s">
+      <c r="D253" s="463" t="s">
         <v>304</v>
       </c>
       <c r="E253" t="s" s="0">
@@ -23022,7 +20981,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254" t="s" s="0">
         <v>594</v>
       </c>
@@ -23032,10 +20991,9 @@
       <c r="C254" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D254" s="676" t="s">
+      <c r="D254" s="464" t="s">
         <v>932</v>
       </c>
-      <c r="E254" s="0"/>
       <c r="F254" t="s" s="0">
         <v>1018</v>
       </c>
@@ -23046,7 +21004,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255" t="s" s="0">
         <v>597</v>
       </c>
@@ -23056,7 +21014,7 @@
       <c r="C255" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D255" s="678" t="s">
+      <c r="D255" s="465" t="s">
         <v>304</v>
       </c>
       <c r="E255" t="s" s="0">
@@ -23072,7 +21030,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256" t="s" s="0">
         <v>987</v>
       </c>
@@ -23082,7 +21040,7 @@
       <c r="C256" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D256" s="682" t="s">
+      <c r="D256" s="466" t="s">
         <v>1084</v>
       </c>
       <c r="E256" t="s" s="0">
@@ -23098,7 +21056,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" t="s" s="0">
         <v>987</v>
       </c>
@@ -23108,7 +21066,7 @@
       <c r="C257" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D257" s="684" t="s">
+      <c r="D257" s="467" t="s">
         <v>304</v>
       </c>
       <c r="E257" t="s" s="0">
@@ -23124,7 +21082,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" t="s" s="0">
         <v>987</v>
       </c>
@@ -23134,7 +21092,7 @@
       <c r="C258" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D258" s="687" t="s">
+      <c r="D258" s="468" t="s">
         <v>304</v>
       </c>
       <c r="E258" t="s" s="0">
@@ -23150,7 +21108,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" t="s" s="0">
         <v>1004</v>
       </c>
@@ -23160,7 +21118,7 @@
       <c r="C259" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D259" s="690" t="s">
+      <c r="D259" s="469" t="s">
         <v>304</v>
       </c>
       <c r="E259" t="s" s="0">
@@ -23176,7 +21134,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" t="s" s="0">
         <v>1004</v>
       </c>
@@ -23186,7 +21144,7 @@
       <c r="C260" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D260" s="693" t="s">
+      <c r="D260" s="470" t="s">
         <v>304</v>
       </c>
       <c r="E260" t="s" s="0">
@@ -23202,7 +21160,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" t="s" s="0">
         <v>236</v>
       </c>
@@ -23212,7 +21170,7 @@
       <c r="C261" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D261" s="696" t="s">
+      <c r="D261" s="471" t="s">
         <v>304</v>
       </c>
       <c r="E261" t="s" s="0">
@@ -23228,7 +21186,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s" s="0">
         <v>239</v>
       </c>
@@ -23238,7 +21196,7 @@
       <c r="C262" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D262" s="699" t="s">
+      <c r="D262" s="472" t="s">
         <v>304</v>
       </c>
       <c r="E262" t="s" s="0">
@@ -23254,7 +21212,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" t="s" s="0">
         <v>242</v>
       </c>
@@ -23264,7 +21222,7 @@
       <c r="C263" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D263" s="702" t="s">
+      <c r="D263" s="473" t="s">
         <v>304</v>
       </c>
       <c r="E263" t="s" s="0">
@@ -23280,7 +21238,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" t="s" s="0">
         <v>594</v>
       </c>
@@ -23290,10 +21248,9 @@
       <c r="C264" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D264" s="706" t="s">
+      <c r="D264" s="474" t="s">
         <v>932</v>
       </c>
-      <c r="E264" s="0"/>
       <c r="F264" t="s" s="0">
         <v>1086</v>
       </c>
@@ -23304,7 +21261,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" t="s" s="0">
         <v>597</v>
       </c>
@@ -23314,7 +21271,7 @@
       <c r="C265" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D265" s="708" t="s">
+      <c r="D265" s="475" t="s">
         <v>304</v>
       </c>
       <c r="E265" t="s" s="0">
@@ -23330,7 +21287,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" t="s" s="0">
         <v>936</v>
       </c>
@@ -23340,7 +21297,7 @@
       <c r="C266" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D266" s="711" t="s">
+      <c r="D266" s="476" t="s">
         <v>304</v>
       </c>
       <c r="E266" t="s" s="0">
@@ -23356,7 +21313,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" t="s" s="0">
         <v>939</v>
       </c>
@@ -23366,7 +21323,7 @@
       <c r="C267" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D267" s="714" t="s">
+      <c r="D267" s="477" t="s">
         <v>304</v>
       </c>
       <c r="E267" t="s" s="0">
@@ -23382,7 +21339,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" t="s" s="0">
         <v>942</v>
       </c>
@@ -23392,7 +21349,7 @@
       <c r="C268" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D268" s="717" t="s">
+      <c r="D268" s="478" t="s">
         <v>304</v>
       </c>
       <c r="E268" t="s" s="0">
@@ -23408,7 +21365,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" t="s" s="0">
         <v>219</v>
       </c>
@@ -23418,7 +21375,7 @@
       <c r="C269" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D269" s="720" t="s">
+      <c r="D269" s="479" t="s">
         <v>304</v>
       </c>
       <c r="E269" t="s" s="0">
@@ -23434,7 +21391,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" t="s" s="0">
         <v>947</v>
       </c>
@@ -23444,7 +21401,7 @@
       <c r="C270" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D270" s="723" t="s">
+      <c r="D270" s="480" t="s">
         <v>304</v>
       </c>
       <c r="E270" t="s" s="0">
@@ -23460,7 +21417,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" t="s" s="0">
         <v>236</v>
       </c>
@@ -23470,7 +21427,7 @@
       <c r="C271" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D271" s="726" t="s">
+      <c r="D271" s="481" t="s">
         <v>304</v>
       </c>
       <c r="E271" t="s" s="0">
@@ -23486,7 +21443,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" t="s" s="0">
         <v>239</v>
       </c>
@@ -23496,7 +21453,7 @@
       <c r="C272" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D272" s="729" t="s">
+      <c r="D272" s="482" t="s">
         <v>304</v>
       </c>
       <c r="E272" t="s" s="0">
@@ -23512,7 +21469,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" t="s" s="0">
         <v>242</v>
       </c>
@@ -23522,7 +21479,7 @@
       <c r="C273" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D273" s="732" t="s">
+      <c r="D273" s="483" t="s">
         <v>304</v>
       </c>
       <c r="E273" t="s" s="0">
@@ -23538,7 +21495,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" t="s" s="0">
         <v>594</v>
       </c>
@@ -23548,10 +21505,9 @@
       <c r="C274" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D274" s="736" t="s">
+      <c r="D274" s="484" t="s">
         <v>932</v>
       </c>
-      <c r="E274" s="0"/>
       <c r="F274" t="s" s="0">
         <v>1086</v>
       </c>
@@ -23562,7 +21518,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" t="s" s="0">
         <v>597</v>
       </c>
@@ -23572,7 +21528,7 @@
       <c r="C275" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D275" s="738" t="s">
+      <c r="D275" s="485" t="s">
         <v>304</v>
       </c>
       <c r="E275" t="s" s="0">
@@ -23588,7 +21544,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" t="s" s="0">
         <v>987</v>
       </c>
@@ -23598,7 +21554,7 @@
       <c r="C276" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D276" s="741" t="s">
+      <c r="D276" s="486" t="s">
         <v>304</v>
       </c>
       <c r="E276" t="s" s="0">
@@ -23614,7 +21570,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" t="s" s="0">
         <v>1004</v>
       </c>
@@ -23624,7 +21580,7 @@
       <c r="C277" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D277" s="744" t="s">
+      <c r="D277" s="487" t="s">
         <v>304</v>
       </c>
       <c r="E277" t="s" s="0">
@@ -23640,7 +21596,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" t="s" s="0">
         <v>1004</v>
       </c>
@@ -23650,7 +21606,7 @@
       <c r="C278" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D278" s="747" t="s">
+      <c r="D278" s="488" t="s">
         <v>304</v>
       </c>
       <c r="E278" t="s" s="0">
@@ -23666,7 +21622,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A279" t="s" s="0">
         <v>236</v>
       </c>
@@ -23676,7 +21632,7 @@
       <c r="C279" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D279" s="750" t="s">
+      <c r="D279" s="489" t="s">
         <v>304</v>
       </c>
       <c r="E279" t="s" s="0">
@@ -23692,7 +21648,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" t="s" s="0">
         <v>239</v>
       </c>
@@ -23702,7 +21658,7 @@
       <c r="C280" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D280" s="753" t="s">
+      <c r="D280" s="490" t="s">
         <v>304</v>
       </c>
       <c r="E280" t="s" s="0">
@@ -23718,7 +21674,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" t="s" s="0">
         <v>242</v>
       </c>
@@ -23728,7 +21684,7 @@
       <c r="C281" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D281" s="757" t="s">
+      <c r="D281" s="491" t="s">
         <v>1134</v>
       </c>
       <c r="E281" t="s" s="0">
@@ -23744,7 +21700,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" t="s" s="0">
         <v>594</v>
       </c>
@@ -23754,10 +21710,9 @@
       <c r="C282" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D282" s="760" t="s">
+      <c r="D282" s="492" t="s">
         <v>932</v>
       </c>
-      <c r="E282" s="0"/>
       <c r="F282" t="s" s="0">
         <v>1086</v>
       </c>
@@ -23768,7 +21723,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" t="s" s="0">
         <v>597</v>
       </c>
@@ -23778,7 +21733,7 @@
       <c r="C283" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D283" s="762" t="s">
+      <c r="D283" s="493" t="s">
         <v>304</v>
       </c>
       <c r="E283" t="s" s="0">
@@ -23794,7 +21749,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" t="s" s="0">
         <v>936</v>
       </c>
@@ -23804,7 +21759,7 @@
       <c r="C284" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D284" s="766" t="s">
+      <c r="D284" s="494" t="s">
         <v>1140</v>
       </c>
       <c r="E284" t="s" s="0">
@@ -23820,7 +21775,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" t="s" s="0">
         <v>939</v>
       </c>
@@ -23830,7 +21785,7 @@
       <c r="C285" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D285" s="769" t="s">
+      <c r="D285" s="495" t="s">
         <v>1143</v>
       </c>
       <c r="E285" t="s" s="0">
@@ -23846,7 +21801,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" t="s" s="0">
         <v>942</v>
       </c>
@@ -23856,7 +21811,7 @@
       <c r="C286" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D286" s="771" t="s">
+      <c r="D286" s="496" t="s">
         <v>304</v>
       </c>
       <c r="E286" t="s" s="0">
@@ -23872,7 +21827,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" t="s" s="0">
         <v>219</v>
       </c>
@@ -23882,7 +21837,7 @@
       <c r="C287" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D287" s="774" t="s">
+      <c r="D287" s="497" t="s">
         <v>304</v>
       </c>
       <c r="E287" t="s" s="0">
@@ -23898,7 +21853,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" t="s" s="0">
         <v>987</v>
       </c>
@@ -23908,7 +21863,7 @@
       <c r="C288" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D288" s="777" t="s">
+      <c r="D288" s="498" t="s">
         <v>304</v>
       </c>
       <c r="E288" t="s" s="0">
@@ -23924,7 +21879,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289" t="s" s="0">
         <v>987</v>
       </c>
@@ -23934,7 +21889,7 @@
       <c r="C289" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D289" s="781" t="s">
+      <c r="D289" s="499" t="s">
         <v>1152</v>
       </c>
       <c r="E289" t="s" s="0">
@@ -23950,7 +21905,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290" t="s" s="0">
         <v>239</v>
       </c>
@@ -23960,7 +21915,7 @@
       <c r="C290" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D290" s="784" t="s">
+      <c r="D290" s="500" t="s">
         <v>1155</v>
       </c>
       <c r="E290" t="s" s="0">
@@ -23976,7 +21931,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A291" t="s" s="0">
         <v>239</v>
       </c>
@@ -23986,7 +21941,7 @@
       <c r="C291" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D291" s="786" t="s">
+      <c r="D291" s="501" t="s">
         <v>304</v>
       </c>
       <c r="E291" t="s" s="0">
@@ -24002,7 +21957,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A292" t="s" s="0">
         <v>987</v>
       </c>
@@ -24012,7 +21967,7 @@
       <c r="C292" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D292" s="790" t="s">
+      <c r="D292" s="502" t="s">
         <v>339</v>
       </c>
       <c r="E292" t="s" s="0">
@@ -24028,7 +21983,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A293" t="s" s="0">
         <v>987</v>
       </c>
@@ -24038,7 +21993,7 @@
       <c r="C293" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D293" s="792" t="s">
+      <c r="D293" s="503" t="s">
         <v>304</v>
       </c>
       <c r="E293" t="s" s="0">
@@ -24054,7 +22009,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A294" t="s" s="0">
         <v>239</v>
       </c>
@@ -24064,7 +22019,7 @@
       <c r="C294" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D294" s="796" t="s">
+      <c r="D294" s="504" t="s">
         <v>1164</v>
       </c>
       <c r="E294" t="s" s="0">
@@ -24080,7 +22035,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A295" t="s" s="0">
         <v>1004</v>
       </c>
@@ -24090,7 +22045,7 @@
       <c r="C295" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D295" s="798" t="s">
+      <c r="D295" s="505" t="s">
         <v>304</v>
       </c>
       <c r="E295" t="s" s="0">
@@ -24106,7 +22061,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A296" t="s" s="0">
         <v>236</v>
       </c>
@@ -24116,7 +22071,7 @@
       <c r="C296" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D296" s="801" t="s">
+      <c r="D296" s="506" t="s">
         <v>304</v>
       </c>
       <c r="E296" t="s" s="0">
@@ -24132,7 +22087,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A297" t="s" s="0">
         <v>987</v>
       </c>
@@ -24142,7 +22097,7 @@
       <c r="C297" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D297" s="804" t="s">
+      <c r="D297" s="507" t="s">
         <v>304</v>
       </c>
       <c r="E297" t="s" s="0">
@@ -24158,7 +22113,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A298" t="s" s="0">
         <v>239</v>
       </c>
@@ -24168,7 +22123,7 @@
       <c r="C298" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D298" s="807" t="s">
+      <c r="D298" s="508" t="s">
         <v>304</v>
       </c>
       <c r="E298" t="s" s="0">
@@ -24184,7 +22139,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A299" t="s" s="0">
         <v>1004</v>
       </c>
@@ -24194,7 +22149,7 @@
       <c r="C299" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D299" s="810" t="s">
+      <c r="D299" s="509" t="s">
         <v>304</v>
       </c>
       <c r="E299" t="s" s="0">
@@ -24210,7 +22165,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A300" t="s" s="0">
         <v>236</v>
       </c>
@@ -24220,7 +22175,7 @@
       <c r="C300" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D300" s="813" t="s">
+      <c r="D300" s="510" t="s">
         <v>304</v>
       </c>
       <c r="E300" t="s" s="0">
@@ -24236,7 +22191,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A301" t="s" s="0">
         <v>987</v>
       </c>
@@ -24246,7 +22201,7 @@
       <c r="C301" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D301" s="816" t="s">
+      <c r="D301" s="511" t="s">
         <v>304</v>
       </c>
       <c r="E301" t="s" s="0">
@@ -24262,7 +22217,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A302" t="s" s="0">
         <v>239</v>
       </c>
@@ -24272,7 +22227,7 @@
       <c r="C302" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="D302" s="819" t="s">
+      <c r="D302" s="512" t="s">
         <v>304</v>
       </c>
       <c r="E302" t="s" s="0">
@@ -24288,7 +22243,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A303" t="s" s="0">
         <v>987</v>
       </c>
@@ -24298,7 +22253,7 @@
       <c r="C303" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D303" s="823" t="s">
+      <c r="D303" s="513" t="s">
         <v>1183</v>
       </c>
       <c r="E303" t="s" s="0">
@@ -24312,6 +22267,266 @@
       </c>
       <c r="H303" t="s" s="0">
         <v>1185</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A304" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B304" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C304" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D304" s="514" t="s">
+        <v>304</v>
+      </c>
+      <c r="E304" t="s" s="0">
+        <v>1186</v>
+      </c>
+      <c r="F304" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G304" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H304" t="s" s="0">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A305" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B305" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C305" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D305" s="515" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E305" t="s" s="0">
+        <v>1189</v>
+      </c>
+      <c r="F305" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G305" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H305" t="s" s="0">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A306" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B306" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C306" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D306" s="516" t="s">
+        <v>339</v>
+      </c>
+      <c r="E306" t="s" s="0">
+        <v>1191</v>
+      </c>
+      <c r="F306" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G306" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H306" t="s" s="0">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A307" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B307" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C307" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D307" s="518" t="s">
+        <v>339</v>
+      </c>
+      <c r="E307" t="s" s="0">
+        <v>1195</v>
+      </c>
+      <c r="F307" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G307" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H307" t="s" s="0">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A308" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B308" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C308" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D308" s="519" t="s">
+        <v>339</v>
+      </c>
+      <c r="E308" t="s" s="0">
+        <v>1197</v>
+      </c>
+      <c r="F308" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G308" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H308" t="s" s="0">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A309" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B309" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C309" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D309" s="520" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E309" t="s" s="0">
+        <v>1200</v>
+      </c>
+      <c r="F309" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G309" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H309" t="s" s="0">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A310" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B310" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C310" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D310" s="521" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E310" t="s" s="0">
+        <v>1203</v>
+      </c>
+      <c r="F310" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G310" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H310" t="s" s="0">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A311" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B311" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C311" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D311" s="522" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E311" t="s" s="0">
+        <v>1206</v>
+      </c>
+      <c r="F311" t="s" s="0">
+        <v>918</v>
+      </c>
+      <c r="G311" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H311" t="s" s="0">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A312" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B312" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C312" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D312" s="523" t="s">
+        <v>304</v>
+      </c>
+      <c r="E312" t="s" s="0">
+        <v>1208</v>
+      </c>
+      <c r="F312" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G312" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H312" t="s" s="0">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A313" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B313" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C313" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D313" s="524" t="s">
+        <v>304</v>
+      </c>
+      <c r="E313" t="s" s="0">
+        <v>1210</v>
+      </c>
+      <c r="F313" t="s" s="0">
+        <v>1086</v>
+      </c>
+      <c r="G313" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H313" t="s" s="0">
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -24321,7 +22536,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BDC955-3C30-4B5A-8054-E6594B0C03CB}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="18.453125"/>
@@ -25112,6 +23327,226 @@
       </c>
       <c r="H30" t="s" s="0">
         <v>257</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B31" s="0"/>
+      <c r="C31" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>1216</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B32" s="0"/>
+      <c r="C32" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>1218</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D33" s="534" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>1220</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>1221</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B34" s="0"/>
+      <c r="C34" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>1223</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B35" s="0"/>
+      <c r="C35" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>1225</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B36" s="0"/>
+      <c r="C36" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>1227</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B37" s="0"/>
+      <c r="C37" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>1229</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B38" s="0"/>
+      <c r="C38" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>1231</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D39" s="552" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>1233</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>1234</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="1290">
   <si>
     <t>ZZ</t>
   </si>
@@ -3966,13 +3966,178 @@
   <si>
     <t>2026-02-18 11:30:12</t>
   </si>
+  <si>
+    <t>69969fd308c50ae3c00e650d</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:00:39</t>
+  </si>
+  <si>
+    <t>6996a04208c50ae3c00e68c1</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:07:25</t>
+  </si>
+  <si>
+    <t>6996a43e08c50ae3c00e7448</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:19:26</t>
+  </si>
+  <si>
+    <t>6996a3ab08c50ae3c00e70e7</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:21:59</t>
+  </si>
+  <si>
+    <t>6996a52f08c50ae3c00e782d</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:23:27</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: I</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:29:32</t>
+  </si>
+  <si>
+    <t>USA1</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: USA1</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:29:57</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: 12</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:30:23</t>
+  </si>
+  <si>
+    <t>@IN</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: @IN</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:30:41</t>
+  </si>
+  <si>
+    <t>#US</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: #US</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:31:04</t>
+  </si>
+  <si>
+    <t>IND123</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: IND123</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:31:28</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: abcd</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:31:50</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>PASS → Country rejected correctly as expected: 1234</t>
+  </si>
+  <si>
+    <t>2026-02-19 11:32:07</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Unsupported PSP: payIn</t>
+  </si>
+  <si>
+    <t>6996e5294d34b98aa8199284</t>
+  </si>
+  <si>
+    <t>payIn</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:55:57</t>
+  </si>
+  <si>
+    <t>6996e5c74d34b98aa8199681</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:58:35</t>
+  </si>
+  <si>
+    <t>6996e4984d34b98aa8198ef8</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:59:03</t>
+  </si>
+  <si>
+    <t>6996e71f4d34b98aa8199af3</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:04:19</t>
+  </si>
+  <si>
+    <t>6996e7fa4d34b98aa819a463</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:08:26</t>
+  </si>
+  <si>
+    <t>6996e9194d34b98aa819b4b3</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:13:14</t>
+  </si>
+  <si>
+    <t>6996e96b4d34b98aa819bbaf</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:14:35</t>
+  </si>
+  <si>
+    <t>6996ea434d34b98aa819c2ff</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:18:13</t>
+  </si>
+  <si>
+    <t>6996ec844d34b98aa819cc42</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:27:50</t>
+  </si>
+  <si>
+    <t>6996ede14d34b98aa819ced7</t>
+  </si>
+  <si>
+    <t>2026-02-19 16:33:37</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="553" x14ac:knownFonts="1">
+  <fonts count="622" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7188,6 +7353,397 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -7383,7 +7939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="554">
+  <cellXfs count="623">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9042,6 +9598,213 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="552" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="581" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="591" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -14537,7 +15300,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61A2F25-557C-42DF-BC8E-85ED6FEA9686}">
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="31.81640625"/>
@@ -22527,6 +23290,588 @@
       </c>
       <c r="H313" t="s" s="0">
         <v>1211</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B314" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C314" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D314" s="555" t="s">
+        <v>304</v>
+      </c>
+      <c r="E314" t="s" s="0">
+        <v>1235</v>
+      </c>
+      <c r="F314" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="G314" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="H314" t="s" s="0">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B315" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C315" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D315" s="559" t="s">
+        <v>339</v>
+      </c>
+      <c r="E315" t="s" s="0">
+        <v>1237</v>
+      </c>
+      <c r="F315" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="G315" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="H315" t="s" s="0">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B316" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C316" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D316" s="561" t="s">
+        <v>304</v>
+      </c>
+      <c r="E316" t="s" s="0">
+        <v>1239</v>
+      </c>
+      <c r="F316" t="s" s="0">
+        <v>1086</v>
+      </c>
+      <c r="G316" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H316" t="s" s="0">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B317" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C317" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D317" s="565" t="s">
+        <v>339</v>
+      </c>
+      <c r="E317" t="s" s="0">
+        <v>1241</v>
+      </c>
+      <c r="F317" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G317" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H317" t="s" s="0">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B318" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C318" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D318" s="567" t="s">
+        <v>304</v>
+      </c>
+      <c r="E318" t="s" s="0">
+        <v>1243</v>
+      </c>
+      <c r="F318" t="s" s="0">
+        <v>1086</v>
+      </c>
+      <c r="G318" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H318" t="s" s="0">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="0">
+        <v>1245</v>
+      </c>
+      <c r="B319" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C319" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D319" s="570" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E319" s="0"/>
+      <c r="F319" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G319" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H319" t="s" s="0">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="0">
+        <v>1248</v>
+      </c>
+      <c r="B320" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C320" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D320" s="573" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E320" s="0"/>
+      <c r="F320" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G320" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H320" t="s" s="0">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="0">
+        <v>1251</v>
+      </c>
+      <c r="B321" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C321" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D321" s="576" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E321" s="0"/>
+      <c r="F321" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G321" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H321" t="s" s="0">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="0">
+        <v>1254</v>
+      </c>
+      <c r="B322" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C322" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D322" s="579" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E322" s="0"/>
+      <c r="F322" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G322" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H322" t="s" s="0">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="0">
+        <v>1257</v>
+      </c>
+      <c r="B323" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C323" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D323" s="582" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E323" s="0"/>
+      <c r="F323" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G323" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H323" t="s" s="0">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="0">
+        <v>1260</v>
+      </c>
+      <c r="B324" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C324" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D324" s="585" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E324" s="0"/>
+      <c r="F324" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G324" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H324" t="s" s="0">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="0">
+        <v>439</v>
+      </c>
+      <c r="B325" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C325" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D325" s="588" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E325" s="0"/>
+      <c r="F325" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G325" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H325" t="s" s="0">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="0">
+        <v>1265</v>
+      </c>
+      <c r="B326" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C326" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D326" s="591" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E326" s="0"/>
+      <c r="F326" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G326" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H326" t="s" s="0">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B327" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C327" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D327" s="595" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E327" t="s" s="0">
+        <v>1269</v>
+      </c>
+      <c r="F327" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G327" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H327" t="s" s="0">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B328" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C328" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D328" s="598" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E328" t="s" s="0">
+        <v>1272</v>
+      </c>
+      <c r="F328" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G328" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H328" t="s" s="0">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B329" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C329" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D329" s="601" t="s">
+        <v>339</v>
+      </c>
+      <c r="E329" t="s" s="0">
+        <v>1274</v>
+      </c>
+      <c r="F329" t="s" s="0">
+        <v>1018</v>
+      </c>
+      <c r="G329" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H329" t="s" s="0">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B330" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C330" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D330" s="604" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E330" t="s" s="0">
+        <v>1276</v>
+      </c>
+      <c r="F330" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G330" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H330" t="s" s="0">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B331" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C331" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D331" s="606" t="s">
+        <v>304</v>
+      </c>
+      <c r="E331" t="s" s="0">
+        <v>1278</v>
+      </c>
+      <c r="F331" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G331" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H331" t="s" s="0">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B332" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C332" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D332" s="609" t="s">
+        <v>304</v>
+      </c>
+      <c r="E332" t="s" s="0">
+        <v>1280</v>
+      </c>
+      <c r="F332" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G332" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H332" t="s" s="0">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B333" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C333" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D333" s="612" t="s">
+        <v>304</v>
+      </c>
+      <c r="E333" t="s" s="0">
+        <v>1282</v>
+      </c>
+      <c r="F333" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G333" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H333" t="s" s="0">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B334" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C334" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D334" s="615" t="s">
+        <v>304</v>
+      </c>
+      <c r="E334" t="s" s="0">
+        <v>1284</v>
+      </c>
+      <c r="F334" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G334" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H334" t="s" s="0">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B335" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C335" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D335" s="619" t="s">
+        <v>339</v>
+      </c>
+      <c r="E335" t="s" s="0">
+        <v>1286</v>
+      </c>
+      <c r="F335" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G335" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H335" t="s" s="0">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="0">
+        <v>987</v>
+      </c>
+      <c r="B336" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C336" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D336" s="621" t="s">
+        <v>304</v>
+      </c>
+      <c r="E336" t="s" s="0">
+        <v>1288</v>
+      </c>
+      <c r="F336" t="s" s="0">
+        <v>1270</v>
+      </c>
+      <c r="G336" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="H336" t="s" s="0">
+        <v>1289</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="69">
   <si>
     <t>Test Data</t>
   </si>
@@ -169,6 +169,81 @@
   </si>
   <si>
     <t>2026-02-23 14:27:11</t>
+  </si>
+  <si>
+    <t>699fef5b211c8417167594d9</t>
+  </si>
+  <si>
+    <t>payerworld_payin</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:30:22</t>
+  </si>
+  <si>
+    <t>699fefb3211c841716759961</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:31:49</t>
+  </si>
+  <si>
+    <t>699ff035211c841716759df1</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:34:00</t>
+  </si>
+  <si>
+    <t>699ff32de296fb47ac09c268</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:46:40</t>
+  </si>
+  <si>
+    <t>699ff36ee296fb47ac09c5a8</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:47:43</t>
+  </si>
+  <si>
+    <t>699ff3ace296fb47ac09c8cc</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:48:45</t>
+  </si>
+  <si>
+    <t>69a0139b594162c32cce90e2</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:05:04</t>
+  </si>
+  <si>
+    <t>69a013e5594162c32cce9685</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:06:16</t>
+  </si>
+  <si>
+    <t>69a0142c594162c32cce99aa</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:07:26</t>
+  </si>
+  <si>
+    <t>69a0150e594162c32cce9d1f</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:11:16</t>
+  </si>
+  <si>
+    <t>69a0156c594162c32ccea08d</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:12:46</t>
+  </si>
+  <si>
+    <t>69a015c1594162c32ccea660</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:14:12</t>
   </si>
 </sst>
 </file>
@@ -176,7 +251,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="71" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +281,210 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -418,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -520,6 +799,114 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -865,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -1242,6 +1629,318 @@
         <v>43</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D25" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D26" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="189">
   <si>
     <t>Test Data</t>
   </si>
@@ -244,6 +244,396 @@
   </si>
   <si>
     <t>2026-02-26 15:14:12</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/8b4a19632ca4cbb79af9facec5006c64/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64016}, goog:processID: 23724, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64016/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2977d470bc920e43d4e1e28f2b2a3d06</t>
+  </si>
+  <si>
+    <t>69a01d0ca1935f1b71470677</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:45:42</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/231867baefcd9e17e6756fae0986794e/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:51777}, goog:processID: 5768, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:51777/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f1f3fae36863171f05393d8926fed847</t>
+  </si>
+  <si>
+    <t>69a02206a1935f1b714731f5</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:06:48</t>
+  </si>
+  <si>
+    <t>user1234@example.com</t>
+  </si>
+  <si>
+    <t>69a02257a1935f1b71473ac4</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:07:52</t>
+  </si>
+  <si>
+    <t>user_namee@example.com</t>
+  </si>
+  <si>
+    <t>69a0229aa1935f1b7147410d</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:09:00</t>
+  </si>
+  <si>
+    <t>69a022d3a1935f1b714746b4</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:09:58</t>
+  </si>
+  <si>
+    <t>user-name@example.com</t>
+  </si>
+  <si>
+    <t>69a0230fa1935f1b71474d17</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:11:00</t>
+  </si>
+  <si>
+    <t>user+promo@example.com</t>
+  </si>
+  <si>
+    <t>69a0234da1935f1b71475360</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:12:00</t>
+  </si>
+  <si>
+    <t>user.test+1@example.com</t>
+  </si>
+  <si>
+    <t>FAIL → Email was rejected but expected to pass</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:12:17</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/503cc5df4bacc33d0f0948287e6cce28/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:52741}, goog:processID: 1400, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:52741/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6756909f23fdc35e2b7ff1c00c3e598a</t>
+  </si>
+  <si>
+    <t>69a02398a1935f1b71475ffa</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:13:29</t>
+  </si>
+  <si>
+    <t>user@example.co.in</t>
+  </si>
+  <si>
+    <t>69a023e0a1935f1b71476cad</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:14:26</t>
+  </si>
+  <si>
+    <t>USER@EXAMPLE.COM</t>
+  </si>
+  <si>
+    <t>69a0241aa1935f1b7147794d</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:15:28</t>
+  </si>
+  <si>
+    <t>a@b.co</t>
+  </si>
+  <si>
+    <t>69a02460a1935f1b7147891d</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:16:32</t>
+  </si>
+  <si>
+    <t>69a024a4a1935f1b71479b58</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:17:41</t>
+  </si>
+  <si>
+    <t>69a024e9a1935f1b7147afec</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:18:48</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/3423a4dbf009e8f1a5de8e2c0e83f13d/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:53009}, goog:processID: 23260, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:53009/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 29632c38107f6c99862e2e0559bcffff</t>
+  </si>
+  <si>
+    <t>69a02521a1935f1b7147bca5</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:20:14</t>
+  </si>
+  <si>
+    <t>user123@example.com</t>
+  </si>
+  <si>
+    <t>69a02579a1935f1b7147d22c</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:21:17</t>
+  </si>
+  <si>
+    <t>69a025bba1935f1b7147e5ac</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:22:23</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:22:41</t>
+  </si>
+  <si>
+    <t>69a0260ba1935f1b7147fc9d</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:23:48</t>
+  </si>
+  <si>
+    <t>69a0265aa1935f1b71480d3f</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:24:58</t>
+  </si>
+  <si>
+    <t>test@example</t>
+  </si>
+  <si>
+    <t>PASS → Email rejected correctly as expected</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:25:25</t>
+  </si>
+  <si>
+    <t>test@@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:25:49</t>
+  </si>
+  <si>
+    <t>te@st@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:26:13</t>
+  </si>
+  <si>
+    <t>test@example..com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:26:30</t>
+  </si>
+  <si>
+    <t>test..email@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:26:54</t>
+  </si>
+  <si>
+    <t>.test@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:27:18</t>
+  </si>
+  <si>
+    <t>test.@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:27:37</t>
+  </si>
+  <si>
+    <t>test@example,com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:27:55</t>
+  </si>
+  <si>
+    <t>test@example/com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:28:10</t>
+  </si>
+  <si>
+    <t>test@example@com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:28:32</t>
+  </si>
+  <si>
+    <t>test@example.c</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:28:55</t>
+  </si>
+  <si>
+    <t>@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:29:12</t>
+  </si>
+  <si>
+    <t>test@example.com' OR '1'='1</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:29:37</t>
+  </si>
+  <si>
+    <t>test@example.com; DROP TABLE users;</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:29:55</t>
+  </si>
+  <si>
+    <t>test@example.com\n</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/login" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:52752}, goog:processID: 20992, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:52752/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 0f44c808ba776688609be0cfb6496e9c</t>
+  </si>
+  <si>
+    <t>69a027c1a1935f1b714825ca</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:44:07</t>
+  </si>
+  <si>
+    <t>test@example.com\r</t>
+  </si>
+  <si>
+    <t>69a02b1b798c082418295c40</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:45:18</t>
+  </si>
+  <si>
+    <t>tést@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:45:45</t>
+  </si>
+  <si>
+    <t>user😊@example.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:46:09</t>
+  </si>
+  <si>
+    <t>test@example.com,abc@test.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:46:35</t>
+  </si>
+  <si>
+    <t>test@example.com abc@test.com</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:47:05</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:47:31</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:47:56</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:48:21</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:48:46</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:49:05</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:49:34</t>
+  </si>
+  <si>
+    <t>69a02c5e798c0824182972b3</t>
+  </si>
+  <si>
+    <t>2026-02-26 16:50:40</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/login" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:49711}, goog:processID: 4480, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:49711/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 9e8cb0cdc69b74c38de9da131297016f</t>
+  </si>
+  <si>
+    <t>69a02ca0798c0824182976b9</t>
+  </si>
+  <si>
+    <t>2026-02-26 17:04:53</t>
+  </si>
+  <si>
+    <t>69a02ff8798c082418298943</t>
+  </si>
+  <si>
+    <t>2026-02-26 17:06:03</t>
+  </si>
+  <si>
+    <t>69a0403d43623aac1e06cae8</t>
+  </si>
+  <si>
+    <t>2026-02-26 18:15:27</t>
+  </si>
+  <si>
+    <t>69a0412e43623aac1e06dcc8</t>
+  </si>
+  <si>
+    <t>2026-02-26 18:19:28</t>
+  </si>
+  <si>
+    <t>69a0416f43623aac1e06e00a</t>
+  </si>
+  <si>
+    <t>2026-02-26 18:20:34</t>
+  </si>
+  <si>
+    <t>69a041b143623aac1e06e667</t>
+  </si>
+  <si>
+    <t>2026-02-26 18:21:38</t>
+  </si>
+  <si>
+    <t>69a0428f43623aac1e06e9cb</t>
+  </si>
+  <si>
+    <t>2026-02-26 18:25:19</t>
   </si>
 </sst>
 </file>
@@ -251,7 +641,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="71" x14ac:knownFonts="1">
+  <fonts count="233" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +671,924 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -697,7 +2005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -907,6 +2215,492 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1252,7 +3046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -1941,6 +3735,1358 @@
         <v>68</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D27" s="73" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D28" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D29" s="79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D30" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D31" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D32" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D33" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D34" s="94" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="0"/>
+      <c r="F34" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D35" s="97" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D36" s="100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D37" s="103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D38" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D39" s="109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D40" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D41" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D42" s="118" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D43" s="121" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D44" s="124" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="0"/>
+      <c r="F44" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H44" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D45" s="127" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="F45" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D46" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D47" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" s="0"/>
+      <c r="F47" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D48" s="135" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="0"/>
+      <c r="F48" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H48" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D49" s="138" t="s">
+        <v>123</v>
+      </c>
+      <c r="E49" s="0"/>
+      <c r="F49" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D50" s="141" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="0"/>
+      <c r="F50" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D51" s="144" t="s">
+        <v>123</v>
+      </c>
+      <c r="E51" s="0"/>
+      <c r="F51" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D52" s="147" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52" s="0"/>
+      <c r="F52" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H52" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D53" s="150" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" s="0"/>
+      <c r="F53" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G53" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D54" s="153" t="s">
+        <v>123</v>
+      </c>
+      <c r="E54" s="0"/>
+      <c r="F54" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H54" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D55" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="E55" s="0"/>
+      <c r="F55" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D56" s="159" t="s">
+        <v>123</v>
+      </c>
+      <c r="E56" s="0"/>
+      <c r="F56" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D57" s="162" t="s">
+        <v>123</v>
+      </c>
+      <c r="E57" s="0"/>
+      <c r="F57" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D58" s="165" t="s">
+        <v>123</v>
+      </c>
+      <c r="E58" s="0"/>
+      <c r="F58" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D59" s="168" t="s">
+        <v>123</v>
+      </c>
+      <c r="E59" s="0"/>
+      <c r="F59" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D60" s="171" t="s">
+        <v>123</v>
+      </c>
+      <c r="E60" s="0"/>
+      <c r="F60" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H60" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D61" s="174" t="s">
+        <v>152</v>
+      </c>
+      <c r="E61" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="F61" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D62" s="177" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="F62" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G62" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H62" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D63" s="180" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="0"/>
+      <c r="F63" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G63" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H63" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D64" s="183" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" s="0"/>
+      <c r="F64" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H64" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D65" s="186" t="s">
+        <v>123</v>
+      </c>
+      <c r="E65" s="0"/>
+      <c r="F65" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D66" s="189" t="s">
+        <v>123</v>
+      </c>
+      <c r="E66" s="0"/>
+      <c r="F66" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D67" s="192" t="s">
+        <v>123</v>
+      </c>
+      <c r="E67" s="0"/>
+      <c r="F67" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H67" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D68" s="195" t="s">
+        <v>123</v>
+      </c>
+      <c r="E68" s="0"/>
+      <c r="F68" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H68" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D69" s="198" t="s">
+        <v>123</v>
+      </c>
+      <c r="E69" s="0"/>
+      <c r="F69" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H69" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D70" s="201" t="s">
+        <v>123</v>
+      </c>
+      <c r="E70" s="0"/>
+      <c r="F70" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H70" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D71" s="204" t="s">
+        <v>123</v>
+      </c>
+      <c r="E71" s="0"/>
+      <c r="F71" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H71" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D72" s="207" t="s">
+        <v>123</v>
+      </c>
+      <c r="E72" s="0"/>
+      <c r="F72" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G72" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H72" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D73" s="211" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="F73" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G73" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H73" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D74" s="214" t="s">
+        <v>174</v>
+      </c>
+      <c r="E74" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H74" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D75" s="217" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="F75" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H75" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D76" s="220" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="F76" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H76" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D77" s="223" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="F77" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H77" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D78" s="226" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="F78" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G78" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H78" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D79" s="229" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="F79" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G79" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H79" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D80" s="232" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="F80" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H80" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Purchase_Result" sheetId="2" r:id="rId2"/>
+    <sheet name="s2s_Result" r:id="rId6" sheetId="3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="262">
   <si>
     <t>Test Data</t>
   </si>
@@ -635,13 +636,238 @@
   <si>
     <t>2026-02-26 18:25:19</t>
   </si>
+  <si>
+    <t>test123@example.com</t>
+  </si>
+  <si>
+    <t>69a66b1fbd77a9764021775d</t>
+  </si>
+  <si>
+    <t>2026-03-03 10:32:01</t>
+  </si>
+  <si>
+    <t>69a66cdebd77a97640217a9d</t>
+  </si>
+  <si>
+    <t>2026-03-03 10:39:28</t>
+  </si>
+  <si>
+    <t>69a66ecfbd77a976402181ef</t>
+  </si>
+  <si>
+    <t>2026-03-03 10:47:45</t>
+  </si>
+  <si>
+    <t>69a66f54bd77a97640218522</t>
+  </si>
+  <si>
+    <t>2026-03-03 10:49:58</t>
+  </si>
+  <si>
+    <t>69a671d6bd77a97640218c29</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:00:41</t>
+  </si>
+  <si>
+    <t>69a6777abd77a97640218fb8</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:24:44</t>
+  </si>
+  <si>
+    <t>69a67934bd77a976402197e8</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:32:05</t>
+  </si>
+  <si>
+    <t>69a67e21bd77a9764021af7f</t>
+  </si>
+  <si>
+    <t>unicornpayment</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:53:08</t>
+  </si>
+  <si>
+    <t>110001</t>
+  </si>
+  <si>
+    <t>Pass → Payment succeeded as expected</t>
+  </si>
+  <si>
+    <t>69a67f22bd77a9764021bb18</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:57:26</t>
+  </si>
+  <si>
+    <t>iPhone 14</t>
+  </si>
+  <si>
+    <t>69a67f5cbd77a9764021be8c</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:58:23</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S23</t>
+  </si>
+  <si>
+    <t>69a67f97bd77a9764021c530</t>
+  </si>
+  <si>
+    <t>2026-03-03 11:59:23</t>
+  </si>
+  <si>
+    <t>69a680b8bd77a9764021c875</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:04:13</t>
+  </si>
+  <si>
+    <t>Payment failed but expected to pass</t>
+  </si>
+  <si>
+    <t>69a68161bd77a9764021cc18</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:06:26</t>
+  </si>
+  <si>
+    <t>69a6825dbd77a9764021cf97</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:11:13</t>
+  </si>
+  <si>
+    <t>69a6836abd77a9764021da0e</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:15:42</t>
+  </si>
+  <si>
+    <t>69a68448bd77a9764021dd87</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:19:26</t>
+  </si>
+  <si>
+    <t>69a68579bd77a9764021e47d</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:24:29</t>
+  </si>
+  <si>
+    <t>69a68804bd77a9764021e846</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:35:19</t>
+  </si>
+  <si>
+    <t>69a688a8bd77a9764021f242</t>
+  </si>
+  <si>
+    <t>2026-03-03 12:38:07</t>
+  </si>
+  <si>
+    <t>69a6931ec46935d1717d8fd7</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:22:41</t>
+  </si>
+  <si>
+    <t>69a6941dc46935d1717da16f</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:26:58</t>
+  </si>
+  <si>
+    <t>69a69520c46935d1717da8b5</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:31:15</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Error communicating with the remote browser. It may have died.
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [1eea68547993eccd0e3a03c16a0d8ee4, setCurrentWindowSize [height, width]]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60007}, goog:processID: 5720, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60007/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1eea68547993eccd0e3a03c16a0d8ee4</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:31:57</t>
+  </si>
+  <si>
+    <t>69a6963fc46935d1717dac71</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:36:02</t>
+  </si>
+  <si>
+    <t>69a6976bc46935d1717db022</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:41:01</t>
+  </si>
+  <si>
+    <t>69a69880c46935d1717db3cc</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:45:38</t>
+  </si>
+  <si>
+    <t>69a69a12c46935d1717db777</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:52:20</t>
+  </si>
+  <si>
+    <t>69a69b03c46935d1717dbe75</t>
+  </si>
+  <si>
+    <t>2026-03-03 13:56:21</t>
+  </si>
+  <si>
+    <t>69a69c19c46935d1717dc21e</t>
+  </si>
+  <si>
+    <t>2026-03-03 14:00:59</t>
+  </si>
+  <si>
+    <t>69a69cbfc46935d1717dc5c3</t>
+  </si>
+  <si>
+    <t>2026-03-03 14:03:45</t>
+  </si>
+  <si>
+    <t>69a69e6ac46935d1717dcd1b</t>
+  </si>
+  <si>
+    <t>2026-03-03 14:10:54</t>
+  </si>
+  <si>
+    <t>69a69f40c46935d1717dd0c0</t>
+  </si>
+  <si>
+    <t>2026-03-03 14:14:29</t>
+  </si>
+  <si>
+    <t>69a69f91c46935d1717dd803</t>
+  </si>
+  <si>
+    <t>2026-03-03 14:15:47</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="233" x14ac:knownFonts="1">
+  <fonts count="332" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +897,567 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -2005,7 +2792,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="332">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2701,6 +3488,303 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="232" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3046,7 +4130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -5087,7 +6171,911 @@
         <v>188</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D81" s="235" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="F81" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G81" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H81" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D82" s="238" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="F82" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G82" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H82" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D83" s="241" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="F83" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G83" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H83" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D84" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="F84" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G84" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H84" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D85" s="247" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="F85" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G85" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H85" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D86" s="250" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="F86" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H86" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D87" s="253" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="F87" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H87" t="s" s="0">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D88" s="256" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="F88" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G88" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H88" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D89" s="258" t="s">
+        <v>208</v>
+      </c>
+      <c r="E89" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="F89" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G89" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H89" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D90" s="262" t="s">
+        <v>208</v>
+      </c>
+      <c r="E90" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="F90" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G90" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H90" t="s" s="0">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D91" s="265" t="s">
+        <v>208</v>
+      </c>
+      <c r="E91" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G91" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H91" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D92" s="267" t="s">
+        <v>208</v>
+      </c>
+      <c r="E92" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="F92" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G92" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H92" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D93" s="274" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="F93" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G93" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H93" t="s" s="0">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D94" s="277" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="F94" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G94" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H94" t="s" s="0">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D95" s="280" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="F95" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G95" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H95" t="s" s="0">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D96" s="282" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="F96" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G96" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H96" t="s" s="0">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D97" s="286" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="F97" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G97" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H97" t="s" s="0">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D98" s="289" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="F98" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G98" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H98" t="s" s="0">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D99" s="292" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="F99" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G99" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H99" t="s" s="0">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D100" s="294" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="F100" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G100" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H100" t="s" s="0">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D101" s="297" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="F101" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G101" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H101" t="s" s="0">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D102" s="301" t="s">
+        <v>240</v>
+      </c>
+      <c r="E102" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="F102" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G102" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H102" t="s" s="0">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D103" s="303" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="F103" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G103" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H103" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D104" s="306" t="s">
+        <v>26</v>
+      </c>
+      <c r="E104" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="F104" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G104" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H104" t="s" s="0">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D105" s="309" t="s">
+        <v>26</v>
+      </c>
+      <c r="E105" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="F105" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G105" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H105" t="s" s="0">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D106" s="312" t="s">
+        <v>26</v>
+      </c>
+      <c r="E106" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="F106" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G106" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H106" t="s" s="0">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D107" s="315" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="F107" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G107" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H107" t="s" s="0">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D108" s="318" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="F108" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G108" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H108" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D109" s="321" t="s">
+        <v>26</v>
+      </c>
+      <c r="E109" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="F109" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G109" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D110" s="324" t="s">
+        <v>26</v>
+      </c>
+      <c r="E110" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="F110" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G110" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H110" t="s" s="0">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D111" s="327" t="s">
+        <v>26</v>
+      </c>
+      <c r="E111" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="F111" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G111" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H111" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D112" s="330" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="F112" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G112" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H112" t="s" s="0">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="19.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.2734375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.171875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.5859375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="25.1953125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.9765625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.19140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.95703125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="269">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="269">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="269">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="269">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="269">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="269">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="269">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="269">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D2" s="271" t="s">
+        <v>219</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="294">
   <si>
     <t>Test Data</t>
   </si>
@@ -861,13 +861,109 @@
   <si>
     <t>2026-03-03 14:15:47</t>
   </si>
+  <si>
+    <t>69a6a94ec46935d1717e1505</t>
+  </si>
+  <si>
+    <t>2026-03-03 14:57:19</t>
+  </si>
+  <si>
+    <t>69a6aa08c46935d1717e1c57</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:00:27</t>
+  </si>
+  <si>
+    <t>69a6aaa3c46935d1717e1fff</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:03:01</t>
+  </si>
+  <si>
+    <t>69a6aaedc46935d1717e23ba</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:04:13</t>
+  </si>
+  <si>
+    <t>69a6ab63c46935d1717e2764</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:06:13</t>
+  </si>
+  <si>
+    <t>69a6aba8c46935d1717e2b06</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:07:22</t>
+  </si>
+  <si>
+    <t>123 Main Street</t>
+  </si>
+  <si>
+    <t>69a6ac6fc46935d1717e3261</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:10:44</t>
+  </si>
+  <si>
+    <t>69a6ad4ac46935d1717e3637</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:14:23</t>
+  </si>
+  <si>
+    <t>560001</t>
+  </si>
+  <si>
+    <t>69a6ad9bc46935d1717e39f3</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:15:41</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>69a6ade7c46935d1717e40e6</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:16:58</t>
+  </si>
+  <si>
+    <t>90210</t>
+  </si>
+  <si>
+    <t>69a6ae3fc46935d1717e47d6</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:18:25</t>
+  </si>
+  <si>
+    <t>SW1A 1AA</t>
+  </si>
+  <si>
+    <t>69a6ae98c46935d1717e4b94</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:19:53</t>
+  </si>
+  <si>
+    <t>H0H 0H0</t>
+  </si>
+  <si>
+    <t>69a6aeebc46935d1717e52d3</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:21:16</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="332" x14ac:knownFonts="1">
+  <fonts count="371" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -897,6 +993,227 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -2792,7 +3109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="332">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3785,6 +4102,123 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="331" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4130,7 +4564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -7001,6 +7435,344 @@
       </c>
       <c r="H112" t="s" s="0">
         <v>261</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D113" s="333" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="F113" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G113" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H113" t="s" s="0">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D114" s="336" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="F114" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G114" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H114" t="s" s="0">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D115" s="339" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="F115" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G115" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H115" t="s" s="0">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D116" s="342" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="F116" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G116" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H116" t="s" s="0">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D117" s="345" t="s">
+        <v>26</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="F117" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H117" t="s" s="0">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D118" s="348" t="s">
+        <v>26</v>
+      </c>
+      <c r="E118" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="F118" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G118" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H118" t="s" s="0">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D119" s="351" t="s">
+        <v>208</v>
+      </c>
+      <c r="E119" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="F119" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G119" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H119" t="s" s="0">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D120" s="354" t="s">
+        <v>208</v>
+      </c>
+      <c r="E120" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="F120" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G120" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H120" t="s" s="0">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D121" s="357" t="s">
+        <v>208</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G121" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H121" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D122" s="360" t="s">
+        <v>208</v>
+      </c>
+      <c r="E122" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="F122" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G122" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H122" t="s" s="0">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>285</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D123" s="363" t="s">
+        <v>208</v>
+      </c>
+      <c r="E123" t="s" s="0">
+        <v>286</v>
+      </c>
+      <c r="F123" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G123" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H123" t="s" s="0">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D124" s="366" t="s">
+        <v>208</v>
+      </c>
+      <c r="E124" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="F124" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G124" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H124" t="s" s="0">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>291</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D125" s="369" t="s">
+        <v>208</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="F125" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G125" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H125" t="s" s="0">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="304">
   <si>
     <t>Test Data</t>
   </si>
@@ -963,12 +963,37 @@
   <si>
     <t>2026-03-03 15:38:49</t>
   </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Payment succeeded as expected</t>
+  </si>
+  <si>
+    <t>69a6b4abc46935d1717e78ed</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:45:14</t>
+  </si>
+  <si>
+    <t>69a6b590c46935d1717e7cc6</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:49:04</t>
+  </si>
+  <si>
+    <t>69a6b5fcc46935d1717e8076</t>
+  </si>
+  <si>
+    <t>2026-03-03 15:51:26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="129" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="138" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1742,8 +1767,59 @@
       <color indexed="9"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1760,6 +1836,16 @@
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1773,7 +1859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2157,6 +2243,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="128" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2502,17 +2615,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.7265625" customWidth="1"/>
-    <col min="2" max="2" width="21.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" customWidth="1"/>
-    <col min="4" max="4" width="49.36328125" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" customWidth="1"/>
-    <col min="6" max="6" width="20.90625" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="22.7265625"/>
+    <col min="2" max="2" customWidth="true" width="21.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.7265625"/>
+    <col min="4" max="4" customWidth="true" width="49.36328125"/>
+    <col min="5" max="5" customWidth="true" width="29.6328125"/>
+    <col min="6" max="6" customWidth="true" width="20.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -2542,3175 +2655,3201 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F2" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="F3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="F4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="F5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="F6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="F7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="F8" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="F9" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s" s="0">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="F10" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="F11" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s" s="0">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="F12" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s" s="0">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F13" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s" s="0">
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="G14" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s" s="0">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="G15" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s" s="0">
         <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="G16" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s" s="0">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="G17" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s" s="0">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="F18" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s" s="0">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="F19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s" s="0">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s" s="0">
         <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="F21" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s" s="0">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D22" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="F22" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H22" t="s" s="0">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="F23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s" s="0">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="F24" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s" s="0">
         <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="F25" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s" s="0">
         <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D26" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="F26" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s" s="0">
         <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D27" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="F27" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s" s="0">
         <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B28" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D28" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="F28" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s" s="0">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B29" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D29" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="F29" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s" s="0">
         <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D30" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="F30" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s" s="0">
         <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D31" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="F31" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s" s="0">
         <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D32" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="F32" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H32" t="s" s="0">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D33" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="F33" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s" s="0">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B34" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D34" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="F34" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H34" t="s" s="0">
         <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B35" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D35" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="F35" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s" s="0">
         <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D36" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="F36" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s" s="0">
         <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="F37" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s" s="0">
         <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B38" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="F38" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s" s="0">
         <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D39" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" t="s">
+      <c r="F39" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s" s="0">
         <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D40" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="F40" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="F40" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s" s="0">
         <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B41" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D41" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="F41" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="F41" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s" s="0">
         <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B42" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D42" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="F42" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s">
+      <c r="F42" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s" s="0">
         <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B43" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D43" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="F43" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="F43" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s" s="0">
         <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B44" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D44" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" t="s">
+      <c r="F44" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H44" t="s" s="0">
         <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B45" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D45" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="F45" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="F45" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s" s="0">
         <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D46" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="F46" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="F46" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s" s="0">
         <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B47" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D47" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="F47" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="F47" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s" s="0">
         <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B48" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D48" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="F48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="F48" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H48" t="s" s="0">
         <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B49" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D49" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="F49" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="F49" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s" s="0">
         <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>129</v>
       </c>
-      <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B50" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D50" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="F50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" t="s">
+      <c r="F50" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s" s="0">
         <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B51" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D51" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="F51" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="F51" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s" s="0">
         <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>133</v>
       </c>
-      <c r="B52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B52" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D52" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="F52" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="F52" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H52" t="s" s="0">
         <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="B53" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B53" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D53" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="F53" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="F53" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G53" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s" s="0">
         <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D54" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="F54" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="F54" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H54" t="s" s="0">
         <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="B55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B55" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D55" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="F55" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="F55" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s" s="0">
         <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="B56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B56" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D56" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="F56" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="F56" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s" s="0">
         <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="B57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B57" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D57" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="F57" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="F57" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s" s="0">
         <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="B58" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="F58" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="F58" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s" s="0">
         <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="B59" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="B59" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D59" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F59" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="F59" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s" s="0">
         <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B60" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D60" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="F60" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="F60" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H60" t="s" s="0">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>151</v>
       </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="B61" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D61" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="F61" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="F61" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s" s="0">
         <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="B62" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D62" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="F62" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="F62" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G62" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H62" t="s" s="0">
         <v>157</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B63" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D63" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="F63" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G63" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H63" t="s" s="0">
         <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="B64" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D64" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="F64" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="F64" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H64" t="s" s="0">
         <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="B65" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D65" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="F65" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="F65" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s" s="0">
         <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="B66" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D66" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="F66" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="F66" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s" s="0">
         <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="B67" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="B67" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D67" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="F67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="F67" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H67" t="s" s="0">
         <v>166</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="B68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="B68" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D68" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="F68" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="F68" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H68" t="s" s="0">
         <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="B69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="B69" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D69" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="F69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" t="s">
+      <c r="F69" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H69" t="s" s="0">
         <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="B70" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="B70" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D70" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="F70" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="F70" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H70" t="s" s="0">
         <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="B71" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="B71" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D71" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="F71" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" t="s">
+      <c r="F71" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H71" t="s" s="0">
         <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="B72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="B72" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D72" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="F72" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" t="s">
+      <c r="F72" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G72" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H72" t="s" s="0">
         <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B73" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D73" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="F73" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" t="s">
+      <c r="F73" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G73" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H73" t="s" s="0">
         <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="B74" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D74" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="F74" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" t="s">
+      <c r="F74" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H74" t="s" s="0">
         <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B75" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="B75" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D75" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" t="s" s="0">
         <v>177</v>
       </c>
-      <c r="F75" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" t="s">
+      <c r="F75" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H75" t="s" s="0">
         <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="B76" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D76" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="F76" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="F76" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H76" t="s" s="0">
         <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B77" t="s">
-        <v>9</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B77" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D77" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" t="s" s="0">
         <v>181</v>
       </c>
-      <c r="F77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" t="s">
-        <v>14</v>
-      </c>
-      <c r="H77" t="s">
+      <c r="F77" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H77" t="s" s="0">
         <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="B78" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C78" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D78" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="F78" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="F78" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G78" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H78" t="s" s="0">
         <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B79" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="B79" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D79" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" t="s" s="0">
         <v>185</v>
       </c>
-      <c r="F79" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" t="s">
-        <v>14</v>
-      </c>
-      <c r="H79" t="s">
+      <c r="F79" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G79" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H79" t="s" s="0">
         <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B80" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D80" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="F80" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" t="s">
-        <v>14</v>
-      </c>
-      <c r="H80" t="s">
+      <c r="F80" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H80" t="s" s="0">
         <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B81" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="B81" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D81" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="F81" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" t="s">
+      <c r="F81" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G81" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H81" t="s" s="0">
         <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B82" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D82" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="F82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" t="s">
+      <c r="F82" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G82" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H82" t="s" s="0">
         <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B83" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="B83" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D83" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="F83" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" t="s">
+      <c r="F83" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G83" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H83" t="s" s="0">
         <v>195</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="B84" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D84" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="F84" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" t="s">
-        <v>14</v>
-      </c>
-      <c r="H84" t="s">
+      <c r="F84" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G84" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H84" t="s" s="0">
         <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="B85" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D85" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="F85" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" t="s">
+      <c r="F85" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G85" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H85" t="s" s="0">
         <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="B86" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D86" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="F86" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" t="s">
-        <v>14</v>
-      </c>
-      <c r="H86" t="s">
+      <c r="F86" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H86" t="s" s="0">
         <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B87" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="B87" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D87" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="F87" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" t="s">
+      <c r="F87" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H87" t="s" s="0">
         <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="B88" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D88" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G88" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" t="s">
+      <c r="G88" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H88" t="s" s="0">
         <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="B89" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="B89" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D89" s="89" t="s">
         <v>208</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" t="s" s="0">
         <v>209</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G89" t="s">
-        <v>14</v>
-      </c>
-      <c r="H89" t="s">
+      <c r="G89" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H89" t="s" s="0">
         <v>210</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>211</v>
       </c>
-      <c r="B90" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="B90" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D90" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="F90" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" t="s">
+      <c r="F90" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G90" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H90" t="s" s="0">
         <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="B91" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="B91" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D91" s="91" t="s">
         <v>208</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="F91" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" t="s">
+      <c r="F91" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G91" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H91" t="s" s="0">
         <v>216</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="B92" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="B92" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D92" s="92" t="s">
         <v>208</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" t="s" s="0">
         <v>217</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G92" t="s">
-        <v>14</v>
-      </c>
-      <c r="H92" t="s">
+      <c r="G92" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H92" t="s" s="0">
         <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B93" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="B93" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C93" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D93" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" t="s" s="0">
         <v>222</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G93" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" t="s">
+      <c r="G93" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H93" t="s" s="0">
         <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B94" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="B94" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D94" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G94" t="s">
-        <v>14</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="G94" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H94" t="s" s="0">
         <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="B95" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D95" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G95" t="s">
-        <v>14</v>
-      </c>
-      <c r="H95" t="s">
+      <c r="G95" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H95" t="s" s="0">
         <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B96" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="B96" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D96" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G96" t="s">
-        <v>14</v>
-      </c>
-      <c r="H96" t="s">
+      <c r="G96" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H96" t="s" s="0">
         <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B97" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="B97" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D97" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" t="s" s="0">
         <v>230</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G97" t="s">
-        <v>14</v>
-      </c>
-      <c r="H97" t="s">
+      <c r="G97" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H97" t="s" s="0">
         <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="B98" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C98" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D98" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G98" t="s">
-        <v>14</v>
-      </c>
-      <c r="H98" t="s">
+      <c r="G98" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H98" t="s" s="0">
         <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B99" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="B99" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D99" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G99" t="s">
-        <v>14</v>
-      </c>
-      <c r="H99" t="s">
+      <c r="G99" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H99" t="s" s="0">
         <v>235</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="B100" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D100" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G100" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" t="s">
+      <c r="G100" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H100" t="s" s="0">
         <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="B101" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D101" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G101" t="s">
-        <v>14</v>
-      </c>
-      <c r="H101" t="s">
+      <c r="G101" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H101" t="s" s="0">
         <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D102" s="104" t="s">
         <v>240</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G102" t="s">
-        <v>14</v>
-      </c>
-      <c r="H102" t="s">
+      <c r="G102" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H102" t="s" s="0">
         <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="B103" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D103" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G103" t="s">
-        <v>14</v>
-      </c>
-      <c r="H103" t="s">
+      <c r="G103" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H103" t="s" s="0">
         <v>243</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B104" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="B104" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C104" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D104" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G104" t="s">
-        <v>14</v>
-      </c>
-      <c r="H104" t="s">
+      <c r="G104" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H104" t="s" s="0">
         <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B105" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="B105" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C105" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D105" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G105" t="s">
-        <v>14</v>
-      </c>
-      <c r="H105" t="s">
+      <c r="G105" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H105" t="s" s="0">
         <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="B106" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D106" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G106" t="s">
-        <v>14</v>
-      </c>
-      <c r="H106" t="s">
+      <c r="G106" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H106" t="s" s="0">
         <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="B107" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D107" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" t="s" s="0">
         <v>250</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G107" t="s">
-        <v>14</v>
-      </c>
-      <c r="H107" t="s">
+      <c r="G107" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H107" t="s" s="0">
         <v>251</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="B108" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C108" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D108" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G108" t="s">
-        <v>14</v>
-      </c>
-      <c r="H108" t="s">
+      <c r="G108" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H108" t="s" s="0">
         <v>253</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B109" t="s">
-        <v>9</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="B109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C109" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D109" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F109" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G109" t="s">
-        <v>14</v>
-      </c>
-      <c r="H109" t="s">
+      <c r="G109" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s" s="0">
         <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B110" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="B110" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C110" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D110" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" t="s">
+      <c r="G110" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H110" t="s" s="0">
         <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B111" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="B111" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D111" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F111" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G111" t="s">
-        <v>14</v>
-      </c>
-      <c r="H111" t="s">
+      <c r="G111" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H111" t="s" s="0">
         <v>259</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B112" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="B112" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D112" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" t="s">
+      <c r="G112" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H112" t="s" s="0">
         <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B113" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="B113" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D113" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G113" t="s">
-        <v>14</v>
-      </c>
-      <c r="H113" t="s">
+      <c r="G113" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H113" t="s" s="0">
         <v>263</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B114" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="B114" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D114" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G114" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" t="s">
+      <c r="G114" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H114" t="s" s="0">
         <v>265</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B115" t="s">
-        <v>9</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="B115" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D115" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G115" t="s">
-        <v>14</v>
-      </c>
-      <c r="H115" t="s">
+      <c r="G115" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H115" t="s" s="0">
         <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="B116" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="B116" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D116" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G116" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" t="s">
+      <c r="G116" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H116" t="s" s="0">
         <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B117" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C117" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D117" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G117" t="s">
-        <v>14</v>
-      </c>
-      <c r="H117" t="s">
+      <c r="G117" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H117" t="s" s="0">
         <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="B118" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D118" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G118" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" t="s">
+      <c r="G118" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H118" t="s" s="0">
         <v>273</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="B119" t="s">
-        <v>9</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B119" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D119" s="121" t="s">
         <v>208</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" t="s" s="0">
         <v>275</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G119" t="s">
-        <v>14</v>
-      </c>
-      <c r="H119" t="s">
+      <c r="G119" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H119" t="s" s="0">
         <v>276</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="B120" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C120" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D120" s="122" t="s">
         <v>208</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" t="s" s="0">
         <v>277</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F120" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G120" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" t="s">
+      <c r="G120" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H120" t="s" s="0">
         <v>278</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="B121" t="s">
-        <v>9</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="B121" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C121" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D121" s="123" t="s">
         <v>208</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G121" t="s">
-        <v>14</v>
-      </c>
-      <c r="H121" t="s">
+      <c r="G121" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H121" t="s" s="0">
         <v>281</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="B122" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="B122" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C122" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D122" s="124" t="s">
         <v>208</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G122" t="s">
-        <v>14</v>
-      </c>
-      <c r="H122" t="s">
+      <c r="G122" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H122" t="s" s="0">
         <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>285</v>
       </c>
-      <c r="B123" t="s">
-        <v>9</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="B123" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C123" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D123" s="125" t="s">
         <v>208</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F123" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G123" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" t="s">
+      <c r="G123" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H123" t="s" s="0">
         <v>287</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B124" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C124" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D124" s="126" t="s">
         <v>208</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" t="s" s="0">
         <v>289</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G124" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" t="s">
+      <c r="G124" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H124" t="s" s="0">
         <v>290</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>291</v>
       </c>
-      <c r="B125" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="B125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D125" s="127" t="s">
         <v>208</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G125" t="s">
-        <v>14</v>
-      </c>
-      <c r="H125" t="s">
+      <c r="G125" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H125" t="s" s="0">
         <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B126" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B126" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C126" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D126" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" t="s" s="0">
         <v>294</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F126" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G126" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" t="s">
+      <c r="G126" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H126" t="s" s="0">
         <v>295</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D127" s="136" t="s">
+        <v>26</v>
+      </c>
+      <c r="E127" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="F127" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G127" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H127" t="s" s="0">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -5720,17 +5859,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.90625" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="19.7265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.26953125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.1796875"/>
+    <col min="4" max="4" customWidth="true" width="47.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="25.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -5760,29 +5899,81 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>69</v>
       </c>
       <c r="D2" s="94" t="s">
         <v>219</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s" s="0">
         <v>221</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>297</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D4" s="133" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="348">
   <si>
     <t>Test Data</t>
   </si>
@@ -987,13 +987,200 @@
   <si>
     <t>2026-03-03 15:51:26</t>
   </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:58638}, goog:processID: 18464, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:58638/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 04bf109f0670918053a83f4eddacb5b3</t>
+  </si>
+  <si>
+    <t>69a6d291dec8195eff226b36</t>
+  </si>
+  <si>
+    <t>2026-03-03 17:53:36</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61619}, goog:processID: 13812, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61619/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 64f3b357451b3bc3800ed1fa2617454a</t>
+  </si>
+  <si>
+    <t>69a6d2dadec8195eff226f1d</t>
+  </si>
+  <si>
+    <t>2026-03-03 17:54:47</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:51380}, goog:processID: 29136, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:51380/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: fea6475a6a9c23c959e2da78a7c2ccd1</t>
+  </si>
+  <si>
+    <t>69a6d431dec8195eff228176</t>
+  </si>
+  <si>
+    <t>2026-03-03 18:00:31</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/e88781900db9e42dc6f328420b3acde5/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55294}, goog:processID: 29968, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55294/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 4868c9fb9e1f3b125416b74cf7a808b5</t>
+  </si>
+  <si>
+    <t>69a6d477dec8195eff228894</t>
+  </si>
+  <si>
+    <t>2026-03-03 18:01:42</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:51404}, goog:processID: 29708, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:51404/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6bd4e06e72c66acd1811cc0354a9165d</t>
+  </si>
+  <si>
+    <t>69a6d60fdec8195eff22a5cc</t>
+  </si>
+  <si>
+    <t>2026-03-03 18:08:31</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/Error" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62125}, goog:processID: 21056, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62125/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f9ca964b08d4ac3201e9229ceb4c31ab</t>
+  </si>
+  <si>
+    <t>69a90f37f8460c747c9ffa4a</t>
+  </si>
+  <si>
+    <t>2026-03-05 10:36:58</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54375}, goog:processID: 29772, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54375/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: b2ff1794abc1ecf6eb380aeb4b151f9a</t>
+  </si>
+  <si>
+    <t>69a9409cf8460c747ca0707b</t>
+  </si>
+  <si>
+    <t>unicornpayment3ds</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:07:44</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:53656}, goog:processID: 10296, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:53656/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e3e1c44a7bf022fea790356342bc65ad</t>
+  </si>
+  <si>
+    <t>69a94114f8460c747ca07403</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:09:43</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:51592}, goog:processID: 35684, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:51592/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f0a27a5010e122dae9d65558abcbe68f</t>
+  </si>
+  <si>
+    <t>69a942fe7f44d5547169761b</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:22:53</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of Proxy element for: DefaultElementLocator 'By.xpath: //input[@name='password']' (tried for 20 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>69a9444c7f44d554716979e1</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:23:42</t>
+  </si>
+  <si>
+    <t>69a945c67f44d554716984bf</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:30:01</t>
+  </si>
+  <si>
+    <t>69a947567f44d5547169913f</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:36:54</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64651}, goog:processID: 16216, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64651/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 500057e93330b0a64b42f60bbde14853</t>
+  </si>
+  <si>
+    <t>69a9489c7f44d554716997ae</t>
+  </si>
+  <si>
+    <t>unicornpaymentds</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:47:13</t>
+  </si>
+  <si>
+    <t>69a94add7f44d5547169aa2f</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:51:42</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://quickpay.ugpayments.ch/threedauthentication" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61890}, goog:processID: 35528, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61890/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: adc5ac6d38e2fc93c3cebc7c02808de7</t>
+  </si>
+  <si>
+    <t>69a949dc7f44d55471699f91</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:52:35</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="138" x14ac:knownFonts="1">
+  <fonts count="183" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1766,6 +1953,261 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -1859,7 +2301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2270,6 +2712,141 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2615,7 +3192,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -5850,6 +6427,396 @@
       </c>
       <c r="H127" t="s" s="0">
         <v>303</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D128" s="140" t="s">
+        <v>304</v>
+      </c>
+      <c r="E128" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="F128" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G128" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H128" t="s" s="0">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D129" s="143" t="s">
+        <v>307</v>
+      </c>
+      <c r="E129" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G129" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H129" t="s" s="0">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C130" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D130" s="146" t="s">
+        <v>310</v>
+      </c>
+      <c r="E130" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="F130" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G130" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H130" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C131" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D131" s="149" t="s">
+        <v>313</v>
+      </c>
+      <c r="E131" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="F131" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G131" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H131" t="s" s="0">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C132" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D132" s="152" t="s">
+        <v>316</v>
+      </c>
+      <c r="E132" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="F132" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G132" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H132" t="s" s="0">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D133" s="155" t="s">
+        <v>319</v>
+      </c>
+      <c r="E133" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="F133" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G133" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H133" t="s" s="0">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C134" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D134" s="158" t="s">
+        <v>322</v>
+      </c>
+      <c r="E134" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="F134" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="G134" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H134" t="s" s="0">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D135" s="161" t="s">
+        <v>326</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="F135" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="G135" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H135" t="s" s="0">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C136" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D136" s="164" t="s">
+        <v>329</v>
+      </c>
+      <c r="E136" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="F136" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="G136" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H136" t="s" s="0">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D137" s="167" t="s">
+        <v>332</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="F137" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="G137" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H137" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C138" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D138" s="170" t="s">
+        <v>332</v>
+      </c>
+      <c r="E138" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="F138" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="G138" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H138" t="s" s="0">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C139" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D139" s="173" t="s">
+        <v>332</v>
+      </c>
+      <c r="E139" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="F139" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="G139" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H139" t="s" s="0">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C140" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D140" s="176" t="s">
+        <v>339</v>
+      </c>
+      <c r="E140" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="F140" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G140" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H140" t="s" s="0">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C141" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D141" s="178" t="s">
+        <v>26</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="F141" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G141" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H141" t="s" s="0">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C142" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D142" s="182" t="s">
+        <v>345</v>
+      </c>
+      <c r="E142" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="F142" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G142" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H142" t="s" s="0">
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="423">
   <si>
     <t>Test Data</t>
   </si>
@@ -1174,13 +1174,311 @@
   <si>
     <t>2026-03-05 14:52:35</t>
   </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "threed". Current url: "https://staging.paysecure.net/getResponse.jsp?issucces=false" (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56639}, goog:processID: 34972, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56639/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 58bdaecc49355e6ed5f59ae75270a30e</t>
+  </si>
+  <si>
+    <t>69a94eeecf5d2a0f31870de3</t>
+  </si>
+  <si>
+    <t>2026-03-05 15:08:44</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id: session deleted as the browser has closed the connection
+from disconnected: not connected to DevTools
+  (Session info: chrome=145.0.7632.117)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [b120051d4b3268bc434e688f6864c3cc, getCurrentUrl {}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56899}, goog:processID: 19984, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56899/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: b120051d4b3268bc434e688f6864c3cc</t>
+  </si>
+  <si>
+    <t>69a955a7cf5d2a0f31877eae</t>
+  </si>
+  <si>
+    <t>2026-03-05 15:36:57</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of Proxy element for: DefaultElementLocator 'By.xpath: //input[@name='password']' (tried for 40 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>69a95e1e8ee6106423900e92</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:14:31</t>
+  </si>
+  <si>
+    <t>69a95f048ee610642390136b</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:17:41</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "threed". Current url: "https://staging.paysecure.net/getResponse.jsp?issucces=false" (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54442}, goog:processID: 23072, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54442/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 84c279cbe4d50c5fcdff6d7a31d29837</t>
+  </si>
+  <si>
+    <t>69a95f918ee6106423901844</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:19:44</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "threed". Current url: "https://staging.paysecure.net/getResponse.jsp?issucces=false" (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62111}, goog:processID: 5412, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62111/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 9e6ea5c1fe94dececf8ba5df30c14110</t>
+  </si>
+  <si>
+    <t>69a960858ee6106423901d27</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:24:07</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "threed". Current url: "https://staging.paysecure.net/getResponse.jsp?issucces=false" (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.117, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:52970}, goog:processID: 7392, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:52970/devtoo..., se:cdpVersion: 145.0.7632.117, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: fcbcb39745b7c8a88a172a478dd5e673</t>
+  </si>
+  <si>
+    <t>69a9617a8ee6106423902855</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:28:13</t>
+  </si>
+  <si>
+    <t>69a962278ee610642390305b</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:31:02</t>
+  </si>
+  <si>
+    <t>69a9628f8ee6106423903478</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:32:44</t>
+  </si>
+  <si>
+    <t>69a962f58ee61064239038a0</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:34:24</t>
+  </si>
+  <si>
+    <t>69a9635b8ee6106423903cc0</t>
+  </si>
+  <si>
+    <t>2026-03-05 16:36:08</t>
+  </si>
+  <si>
+    <t>69aeb63fa4ab9fb8a03139c1</t>
+  </si>
+  <si>
+    <t>ccavenue</t>
+  </si>
+  <si>
+    <t>2026-03-09 17:30:45</t>
+  </si>
+  <si>
+    <t>69aeb780d46ec9e504c6097d</t>
+  </si>
+  <si>
+    <t>2026-03-09 17:36:05</t>
+  </si>
+  <si>
+    <t>69aeb787d46ec9e504c60987</t>
+  </si>
+  <si>
+    <t>2026-03-09 17:36:12</t>
+  </si>
+  <si>
+    <t>69aeb8f2d46ec9e504c62d66</t>
+  </si>
+  <si>
+    <t>2026-03-09 17:42:13</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://secure.ccavenue.ae/transaction/transaction.do?command=initiateTransaction" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:58592}, goog:processID: 23652, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:58592/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f6c1265b62036255d86352dd1faedfc1</t>
+  </si>
+  <si>
+    <t>69aebc0b2b3b50238d47b26c</t>
+  </si>
+  <si>
+    <t>2026-03-09 17:55:42</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://secure.ccavenue.ae/transaction/transaction.do" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56859}, goog:processID: 1484, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56859/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: c4a063fabb7405fc09ddce7d2d66c50e</t>
+  </si>
+  <si>
+    <t>69aebf1c2b3b50238d47e6ae</t>
+  </si>
+  <si>
+    <t>MASTER</t>
+  </si>
+  <si>
+    <t>2026-03-09 18:08:48</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://secure.ccavenue.ae/transaction/transaction.do" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:58439}, goog:processID: 26540, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:58439/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 52b35baeb68ad8820bdfb3d045ec8382</t>
+  </si>
+  <si>
+    <t>69afb91fba1acbaab1c8d77e</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:57:01</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://secure.ccavenue.ae/transaction/transaction.do" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54919}, goog:processID: 1152, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54919/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e9d8c0a89387882a46b8b94dd0e87d17</t>
+  </si>
+  <si>
+    <t>69afba5fba1acbaab1c8e094</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:05:25</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://secure.ccavenue.ae/transaction/transaction.do" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54809}, goog:processID: 11708, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54809/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: c5cc97d877c2c6eacc15a0dc06a0d9f1</t>
+  </si>
+  <si>
+    <t>69afbb2bba1acbaab1c8e463</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:08:49</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of all [Proxy element for: DefaultElementLocator 'By.xpath: //select[@id='selectAuthResult']'] (tried for 40 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>69afc034ba1acbaab1c8ef4f</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:26:37</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of Proxy element for: DefaultElementLocator 'By.xpath: //select[@id='selectAuthResult']' (tried for 40 second(s) with 500 milliseconds interval)</t>
+  </si>
+  <si>
+    <t>69afc164ba1acbaab1c90dc3</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:31:34</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of element located by By.id: selectAuthResult (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60599}, goog:processID: 23780, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60599/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 76b3dee0aecdf9a6551c3857a452c3ef</t>
+  </si>
+  <si>
+    <t>69afc35fba1acbaab1c92c04</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:39:29</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of element located by By.id: selectAuthResult (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:59559}, goog:processID: 4000, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:59559/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2190d5f140767c8635c20d7691dfeb4e</t>
+  </si>
+  <si>
+    <t>69afc404ba1acbaab1c93470</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:42:21</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of element located by By.id: selectAuthResult (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:51290}, goog:processID: 36004, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:51290/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 90760d0fb0e119651791cabb80701da6</t>
+  </si>
+  <si>
+    <t>69afc4d9ba1acbaab1c939c8</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:46:13</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for visibility of element located by By.id: selectAuthResult (tried for 40 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54647}, goog:processID: 22524, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54647/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f4815c26c8e6dfb639772f86848f3958</t>
+  </si>
+  <si>
+    <t>69afc5e1ba1acbaab1c951e7</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:50:08</t>
+  </si>
+  <si>
+    <t>69afc81aba1acbaab1c95d5f</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:59:23</t>
+  </si>
+  <si>
+    <t>69afc9b2ba1acbaab1c96852</t>
+  </si>
+  <si>
+    <t>2026-03-10 13:06:12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="183" x14ac:knownFonts="1">
+  <fonts count="267" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1953,6 +2251,482 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -2301,7 +3075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2847,6 +3621,258 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="182" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3192,7 +4218,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -6817,6 +7843,734 @@
       </c>
       <c r="H142" t="s" s="0">
         <v>347</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C143" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D143" s="185" t="s">
+        <v>348</v>
+      </c>
+      <c r="E143" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="F143" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G143" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H143" t="s" s="0">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C144" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D144" s="188" t="s">
+        <v>351</v>
+      </c>
+      <c r="E144" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="F144" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G144" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H144" t="s" s="0">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C145" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D145" s="191" t="s">
+        <v>354</v>
+      </c>
+      <c r="E145" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="F145" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G145" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H145" t="s" s="0">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D146" s="193" t="s">
+        <v>26</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="F146" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G146" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H146" t="s" s="0">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C147" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D147" s="197" t="s">
+        <v>359</v>
+      </c>
+      <c r="E147" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="F147" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G147" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H147" t="s" s="0">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C148" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D148" s="200" t="s">
+        <v>362</v>
+      </c>
+      <c r="E148" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="F148" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G148" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H148" t="s" s="0">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C149" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D149" s="203" t="s">
+        <v>365</v>
+      </c>
+      <c r="E149" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="F149" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G149" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H149" t="s" s="0">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C150" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D150" s="205" t="s">
+        <v>26</v>
+      </c>
+      <c r="E150" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="F150" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G150" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H150" t="s" s="0">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C151" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D151" s="208" t="s">
+        <v>26</v>
+      </c>
+      <c r="E151" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="F151" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G151" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H151" t="s" s="0">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C152" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D152" s="211" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="F152" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G152" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H152" t="s" s="0">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C153" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D153" s="214" t="s">
+        <v>26</v>
+      </c>
+      <c r="E153" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="F153" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="G153" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H153" t="s" s="0">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C154" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D154" s="218" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="F154" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G154" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H154" t="s" s="0">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C155" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D155" s="221" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="F155" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G155" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H155" t="s" s="0">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C156" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D156" s="224" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="F156" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G156" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H156" t="s" s="0">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D157" s="227" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="F157" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G157" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H157" t="s" s="0">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C158" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D158" s="230" t="s">
+        <v>385</v>
+      </c>
+      <c r="E158" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="F158" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G158" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H158" t="s" s="0">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C159" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D159" s="233" t="s">
+        <v>388</v>
+      </c>
+      <c r="E159" t="s" s="0">
+        <v>389</v>
+      </c>
+      <c r="F159" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G159" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H159" t="s" s="0">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C160" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D160" s="236" t="s">
+        <v>392</v>
+      </c>
+      <c r="E160" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="F160" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G160" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H160" t="s" s="0">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C161" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D161" s="239" t="s">
+        <v>395</v>
+      </c>
+      <c r="E161" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="F161" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G161" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H161" t="s" s="0">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C162" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D162" s="242" t="s">
+        <v>398</v>
+      </c>
+      <c r="E162" t="s" s="0">
+        <v>399</v>
+      </c>
+      <c r="F162" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G162" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H162" t="s" s="0">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C163" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D163" s="245" t="s">
+        <v>401</v>
+      </c>
+      <c r="E163" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="F163" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G163" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H163" t="s" s="0">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C164" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D164" s="248" t="s">
+        <v>404</v>
+      </c>
+      <c r="E164" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="F164" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G164" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H164" t="s" s="0">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C165" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D165" s="251" t="s">
+        <v>407</v>
+      </c>
+      <c r="E165" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="F165" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G165" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H165" t="s" s="0">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C166" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D166" s="254" t="s">
+        <v>410</v>
+      </c>
+      <c r="E166" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="F166" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G166" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H166" t="s" s="0">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C167" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D167" s="257" t="s">
+        <v>413</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>414</v>
+      </c>
+      <c r="F167" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G167" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H167" t="s" s="0">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C168" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D168" s="260" t="s">
+        <v>416</v>
+      </c>
+      <c r="E168" t="s" s="0">
+        <v>417</v>
+      </c>
+      <c r="F168" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G168" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H168" t="s" s="0">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C169" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D169" s="262" t="s">
+        <v>26</v>
+      </c>
+      <c r="E169" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="F169" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G169" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H169" t="s" s="0">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C170" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D170" s="265" t="s">
+        <v>26</v>
+      </c>
+      <c r="E170" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="F170" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G170" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H170" t="s" s="0">
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="488">
   <si>
     <t>Test Data</t>
   </si>
@@ -1472,13 +1472,214 @@
   <si>
     <t>2026-03-10 13:06:12</t>
   </si>
+  <si>
+    <t>FAIL → Exception: java.lang.RuntimeException: ✗ selectAuthResult dropdown NOT found in any iframe!</t>
+  </si>
+  <si>
+    <t>69afdb16ba1acbaab1ca0867</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:21:07</t>
+  </si>
+  <si>
+    <t>69afdb8aba1acbaab1ca1781</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:23:04</t>
+  </si>
+  <si>
+    <t>69afdc03ba1acbaab1ca2384</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:25:06</t>
+  </si>
+  <si>
+    <t>69afdc7dba1acbaab1ca3279</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:27:11</t>
+  </si>
+  <si>
+    <t>69afdd02ba1acbaab1ca41cc</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:29:24</t>
+  </si>
+  <si>
+    <t>69afdd7fba1acbaab1ca50df</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:31:39</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:32:01</t>
+  </si>
+  <si>
+    <t>69afde1bba1acbaab1ca58fa</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:34:07</t>
+  </si>
+  <si>
+    <t>69afde9bba1acbaab1ca60c1</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:36:23</t>
+  </si>
+  <si>
+    <t>69afdf25ba1acbaab1ca68d1</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:38:36</t>
+  </si>
+  <si>
+    <t>69afdfb0ba1acbaab1ca7b5c</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:40:47</t>
+  </si>
+  <si>
+    <t>69afe029ba1acbaab1ca8331</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:42:47</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [e342ea867a8459197f7a32fbfcb45a1b, switchToFrame {id=null}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54464}, goog:processID: 13872, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54464/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e342ea867a8459197f7a32fbfcb45a1b</t>
+  </si>
+  <si>
+    <t>69afe0a2ba1acbaab1ca872a</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:00:27</t>
+  </si>
+  <si>
+    <t>69afe4c9ba1acbaab1caa612</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:02:32</t>
+  </si>
+  <si>
+    <t>69afe543ba1acbaab1caab56</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:04:34</t>
+  </si>
+  <si>
+    <t>69afe5bbba1acbaab1cab638</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:06:34</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:06:54</t>
+  </si>
+  <si>
+    <t>69afe64aba1acbaab1cabb62</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:08:57</t>
+  </si>
+  <si>
+    <t>69afe6c5ba1acbaab1cac093</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:11:00</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:11:20</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:11:40</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:11:58</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:12:20</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:12:39</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:12:57</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:13:16</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:13:36</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:13:56</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:14:13</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:14:32</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:14:50</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:15:09</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:15:27</t>
+  </si>
+  <si>
+    <t>69afe848ba1acbaab1cacfc8</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:17:28</t>
+  </si>
+  <si>
+    <t>69afe8c3ba1acbaab1cad4f4</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:19:29</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:19:48</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:20:06</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:20:25</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:20:42</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:20:59</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:21:17</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:21:36</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:21:54</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:22:12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="267" x14ac:knownFonts="1">
+  <fonts count="399" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2251,6 +2452,754 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -3075,7 +4024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="399">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3873,6 +4822,402 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="266" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4218,7 +5563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -8571,6 +9916,1100 @@
       </c>
       <c r="H170" t="s" s="0">
         <v>422</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C171" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D171" s="269" t="s">
+        <v>423</v>
+      </c>
+      <c r="E171" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="F171" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G171" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H171" t="s" s="0">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C172" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D172" s="272" t="s">
+        <v>423</v>
+      </c>
+      <c r="E172" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="F172" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G172" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H172" t="s" s="0">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C173" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D173" s="275" t="s">
+        <v>423</v>
+      </c>
+      <c r="E173" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="F173" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G173" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H173" t="s" s="0">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C174" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D174" s="278" t="s">
+        <v>423</v>
+      </c>
+      <c r="E174" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="F174" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G174" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H174" t="s" s="0">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C175" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D175" s="281" t="s">
+        <v>423</v>
+      </c>
+      <c r="E175" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="F175" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G175" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H175" t="s" s="0">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C176" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D176" s="284" t="s">
+        <v>423</v>
+      </c>
+      <c r="E176" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="F176" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G176" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H176" t="s" s="0">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C177" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D177" s="287" t="s">
+        <v>91</v>
+      </c>
+      <c r="E177" s="0"/>
+      <c r="F177" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G177" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H177" t="s" s="0">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C178" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D178" s="290" t="s">
+        <v>423</v>
+      </c>
+      <c r="E178" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="F178" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G178" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H178" t="s" s="0">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D179" s="293" t="s">
+        <v>423</v>
+      </c>
+      <c r="E179" t="s" s="0">
+        <v>439</v>
+      </c>
+      <c r="F179" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G179" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H179" t="s" s="0">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C180" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D180" s="296" t="s">
+        <v>423</v>
+      </c>
+      <c r="E180" t="s" s="0">
+        <v>441</v>
+      </c>
+      <c r="F180" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G180" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H180" t="s" s="0">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C181" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D181" s="299" t="s">
+        <v>423</v>
+      </c>
+      <c r="E181" t="s" s="0">
+        <v>443</v>
+      </c>
+      <c r="F181" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G181" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H181" t="s" s="0">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C182" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D182" s="302" t="s">
+        <v>423</v>
+      </c>
+      <c r="E182" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="F182" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G182" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H182" t="s" s="0">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C183" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D183" s="305" t="s">
+        <v>447</v>
+      </c>
+      <c r="E183" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="F183" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G183" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H183" t="s" s="0">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C184" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D184" s="308" t="s">
+        <v>423</v>
+      </c>
+      <c r="E184" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="F184" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G184" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H184" t="s" s="0">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D185" s="311" t="s">
+        <v>423</v>
+      </c>
+      <c r="E185" t="s" s="0">
+        <v>452</v>
+      </c>
+      <c r="F185" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G185" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H185" t="s" s="0">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C186" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D186" s="314" t="s">
+        <v>423</v>
+      </c>
+      <c r="E186" t="s" s="0">
+        <v>454</v>
+      </c>
+      <c r="F186" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G186" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H186" t="s" s="0">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C187" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D187" s="317" t="s">
+        <v>91</v>
+      </c>
+      <c r="E187" s="0"/>
+      <c r="F187" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G187" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H187" t="s" s="0">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C188" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D188" s="320" t="s">
+        <v>423</v>
+      </c>
+      <c r="E188" t="s" s="0">
+        <v>457</v>
+      </c>
+      <c r="F188" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G188" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H188" t="s" s="0">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C189" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D189" s="323" t="s">
+        <v>423</v>
+      </c>
+      <c r="E189" t="s" s="0">
+        <v>459</v>
+      </c>
+      <c r="F189" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G189" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H189" t="s" s="0">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D190" s="325" t="s">
+        <v>123</v>
+      </c>
+      <c r="E190" s="0"/>
+      <c r="F190" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G190" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H190" t="s" s="0">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D191" s="328" t="s">
+        <v>123</v>
+      </c>
+      <c r="E191" s="0"/>
+      <c r="F191" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G191" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H191" t="s" s="0">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C192" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D192" s="331" t="s">
+        <v>123</v>
+      </c>
+      <c r="E192" s="0"/>
+      <c r="F192" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G192" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H192" t="s" s="0">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C193" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D193" s="334" t="s">
+        <v>123</v>
+      </c>
+      <c r="E193" s="0"/>
+      <c r="F193" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G193" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H193" t="s" s="0">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C194" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D194" s="337" t="s">
+        <v>123</v>
+      </c>
+      <c r="E194" s="0"/>
+      <c r="F194" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G194" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H194" t="s" s="0">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C195" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D195" s="340" t="s">
+        <v>123</v>
+      </c>
+      <c r="E195" s="0"/>
+      <c r="F195" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G195" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H195" t="s" s="0">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C196" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D196" s="343" t="s">
+        <v>123</v>
+      </c>
+      <c r="E196" s="0"/>
+      <c r="F196" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G196" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H196" t="s" s="0">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C197" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D197" s="346" t="s">
+        <v>123</v>
+      </c>
+      <c r="E197" s="0"/>
+      <c r="F197" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G197" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H197" t="s" s="0">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C198" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D198" s="349" t="s">
+        <v>123</v>
+      </c>
+      <c r="E198" s="0"/>
+      <c r="F198" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G198" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H198" t="s" s="0">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C199" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D199" s="352" t="s">
+        <v>123</v>
+      </c>
+      <c r="E199" s="0"/>
+      <c r="F199" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G199" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H199" t="s" s="0">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C200" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D200" s="355" t="s">
+        <v>123</v>
+      </c>
+      <c r="E200" s="0"/>
+      <c r="F200" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G200" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H200" t="s" s="0">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C201" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D201" s="358" t="s">
+        <v>123</v>
+      </c>
+      <c r="E201" s="0"/>
+      <c r="F201" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G201" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H201" t="s" s="0">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C202" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D202" s="361" t="s">
+        <v>123</v>
+      </c>
+      <c r="E202" s="0"/>
+      <c r="F202" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G202" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H202" t="s" s="0">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C203" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D203" s="364" t="s">
+        <v>123</v>
+      </c>
+      <c r="E203" s="0"/>
+      <c r="F203" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G203" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H203" t="s" s="0">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C204" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D204" s="367" t="s">
+        <v>423</v>
+      </c>
+      <c r="E204" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="F204" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G204" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H204" t="s" s="0">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C205" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D205" s="370" t="s">
+        <v>423</v>
+      </c>
+      <c r="E205" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="F205" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G205" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H205" t="s" s="0">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C206" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D206" s="373" t="s">
+        <v>123</v>
+      </c>
+      <c r="E206" s="0"/>
+      <c r="F206" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G206" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H206" t="s" s="0">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C207" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D207" s="376" t="s">
+        <v>123</v>
+      </c>
+      <c r="E207" s="0"/>
+      <c r="F207" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G207" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H207" t="s" s="0">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C208" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D208" s="379" t="s">
+        <v>123</v>
+      </c>
+      <c r="E208" s="0"/>
+      <c r="F208" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G208" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H208" t="s" s="0">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C209" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D209" s="382" t="s">
+        <v>123</v>
+      </c>
+      <c r="E209" s="0"/>
+      <c r="F209" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G209" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H209" t="s" s="0">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C210" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D210" s="385" t="s">
+        <v>123</v>
+      </c>
+      <c r="E210" s="0"/>
+      <c r="F210" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G210" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H210" t="s" s="0">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C211" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D211" s="388" t="s">
+        <v>123</v>
+      </c>
+      <c r="E211" s="0"/>
+      <c r="F211" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G211" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H211" t="s" s="0">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C212" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D212" s="391" t="s">
+        <v>123</v>
+      </c>
+      <c r="E212" s="0"/>
+      <c r="F212" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G212" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H212" t="s" s="0">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C213" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D213" s="394" t="s">
+        <v>123</v>
+      </c>
+      <c r="E213" s="0"/>
+      <c r="F213" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G213" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H213" t="s" s="0">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C214" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D214" s="397" t="s">
+        <v>123</v>
+      </c>
+      <c r="E214" s="0"/>
+      <c r="F214" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G214" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H214" t="s" s="0">
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D747F974-9C19-464E-8110-836F9ED1A7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{68975EE5-F996-4CF0-B8DC-F4BE96411B1F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{68975EE5-F996-4CF0-B8DC-F4BE96411B1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="498">
   <si>
     <t>Test Data</t>
   </si>
@@ -1673,13 +1673,58 @@
   <si>
     <t>2026-03-10 15:22:12</t>
   </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/2659134186273ad9726d3ff520083d56/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:50654}, goog:processID: 22948, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:50654/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: beb7ed458595ea62259e4bbf76eb9a6c</t>
+  </si>
+  <si>
+    <t>69b24e7cf36bd5f2176f7a39</t>
+  </si>
+  <si>
+    <t>exactly</t>
+  </si>
+  <si>
+    <t>2026-03-12 10:57:17</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/9614a49983366f1735c7fde9883338fa/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54917}, goog:processID: 416, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54917/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 79d4012993ae01a8bfac722351fca383</t>
+  </si>
+  <si>
+    <t>69b24f24f36bd5f2176f7ea7</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:00:09</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/bfee574e450c7c60bb51984aa69581d8/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 145.0.7632.160, chrome: {chromedriverVersion: 145.0.7632.117 (de4e5d6e13b..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56359}, goog:processID: 24328, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56359/devtoo..., se:cdpVersion: 145.0.7632.160, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: ef5c3f3142968795560c40f0de46b72f</t>
+  </si>
+  <si>
+    <t>69b2500bf36bd5f2176f86cc</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:04:03</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="399" x14ac:knownFonts="1">
+  <fonts count="228" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2454,1483 +2499,544 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -4024,7 +3130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="399">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4410,274 +3516,274 @@
     <xf numFmtId="0" fontId="128" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="189" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="191" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="193" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="197" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="199" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="201" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="203" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="205" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="209" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="213" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="129" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="219" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
@@ -4705,519 +3811,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="227" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="247" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="263" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="265" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="269" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="271" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="275" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="277" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="281" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="283" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="287" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="289" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="293" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="295" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="299" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="301" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="305" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="307" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="309" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="311" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="313" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="315" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="317" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="319" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="321" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="323" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="325" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="327" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="329" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="330" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="331" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="333" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="335" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="337" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="339" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="340" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="341" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="343" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="345" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="346" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="347" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="349" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="351" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="352" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="353" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="355" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="357" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="358" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="359" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="361" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="363" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="365" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="367" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="369" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="371" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="373" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="374" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="375" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="376" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="377" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="378" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="379" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="380" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="381" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="382" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="392" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="394" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="396" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="398" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5563,7 +4156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H217"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -8774,7 +7367,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s" s="0">
         <v>189</v>
       </c>
@@ -8784,7 +7377,7 @@
       <c r="C127" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D127" s="136" t="s">
+      <c r="D127" s="131" t="s">
         <v>26</v>
       </c>
       <c r="E127" t="s" s="0">
@@ -8800,7 +7393,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s" s="0">
         <v>189</v>
       </c>
@@ -8810,7 +7403,7 @@
       <c r="C128" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D128" s="140" t="s">
+      <c r="D128" s="132" t="s">
         <v>304</v>
       </c>
       <c r="E128" t="s" s="0">
@@ -8826,7 +7419,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s" s="0">
         <v>76</v>
       </c>
@@ -8836,7 +7429,7 @@
       <c r="C129" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D129" s="143" t="s">
+      <c r="D129" s="133" t="s">
         <v>307</v>
       </c>
       <c r="E129" t="s" s="0">
@@ -8852,7 +7445,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s" s="0">
         <v>189</v>
       </c>
@@ -8862,7 +7455,7 @@
       <c r="C130" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D130" s="146" t="s">
+      <c r="D130" s="134" t="s">
         <v>310</v>
       </c>
       <c r="E130" t="s" s="0">
@@ -8878,7 +7471,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s" s="0">
         <v>76</v>
       </c>
@@ -8888,7 +7481,7 @@
       <c r="C131" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D131" s="149" t="s">
+      <c r="D131" s="135" t="s">
         <v>313</v>
       </c>
       <c r="E131" t="s" s="0">
@@ -8904,7 +7497,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s" s="0">
         <v>189</v>
       </c>
@@ -8914,7 +7507,7 @@
       <c r="C132" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D132" s="152" t="s">
+      <c r="D132" s="136" t="s">
         <v>316</v>
       </c>
       <c r="E132" t="s" s="0">
@@ -8930,7 +7523,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s" s="0">
         <v>189</v>
       </c>
@@ -8940,7 +7533,7 @@
       <c r="C133" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D133" s="155" t="s">
+      <c r="D133" s="137" t="s">
         <v>319</v>
       </c>
       <c r="E133" t="s" s="0">
@@ -8956,7 +7549,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s" s="0">
         <v>189</v>
       </c>
@@ -8966,7 +7559,7 @@
       <c r="C134" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D134" s="158" t="s">
+      <c r="D134" s="138" t="s">
         <v>322</v>
       </c>
       <c r="E134" t="s" s="0">
@@ -8982,7 +7575,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s" s="0">
         <v>189</v>
       </c>
@@ -8992,7 +7585,7 @@
       <c r="C135" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D135" s="161" t="s">
+      <c r="D135" s="139" t="s">
         <v>326</v>
       </c>
       <c r="E135" t="s" s="0">
@@ -9008,7 +7601,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s" s="0">
         <v>189</v>
       </c>
@@ -9018,7 +7611,7 @@
       <c r="C136" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D136" s="164" t="s">
+      <c r="D136" s="140" t="s">
         <v>329</v>
       </c>
       <c r="E136" t="s" s="0">
@@ -9034,7 +7627,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s" s="0">
         <v>189</v>
       </c>
@@ -9044,7 +7637,7 @@
       <c r="C137" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D137" s="167" t="s">
+      <c r="D137" s="141" t="s">
         <v>332</v>
       </c>
       <c r="E137" t="s" s="0">
@@ -9060,7 +7653,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s" s="0">
         <v>189</v>
       </c>
@@ -9070,7 +7663,7 @@
       <c r="C138" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D138" s="170" t="s">
+      <c r="D138" s="142" t="s">
         <v>332</v>
       </c>
       <c r="E138" t="s" s="0">
@@ -9086,7 +7679,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s" s="0">
         <v>189</v>
       </c>
@@ -9096,7 +7689,7 @@
       <c r="C139" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D139" s="173" t="s">
+      <c r="D139" s="143" t="s">
         <v>332</v>
       </c>
       <c r="E139" t="s" s="0">
@@ -9112,7 +7705,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s" s="0">
         <v>189</v>
       </c>
@@ -9122,7 +7715,7 @@
       <c r="C140" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D140" s="176" t="s">
+      <c r="D140" s="144" t="s">
         <v>339</v>
       </c>
       <c r="E140" t="s" s="0">
@@ -9138,7 +7731,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s" s="0">
         <v>189</v>
       </c>
@@ -9148,7 +7741,7 @@
       <c r="C141" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D141" s="178" t="s">
+      <c r="D141" s="145" t="s">
         <v>26</v>
       </c>
       <c r="E141" t="s" s="0">
@@ -9164,7 +7757,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s" s="0">
         <v>189</v>
       </c>
@@ -9174,7 +7767,7 @@
       <c r="C142" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D142" s="182" t="s">
+      <c r="D142" s="146" t="s">
         <v>345</v>
       </c>
       <c r="E142" t="s" s="0">
@@ -9190,7 +7783,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s" s="0">
         <v>189</v>
       </c>
@@ -9200,7 +7793,7 @@
       <c r="C143" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D143" s="185" t="s">
+      <c r="D143" s="147" t="s">
         <v>348</v>
       </c>
       <c r="E143" t="s" s="0">
@@ -9216,7 +7809,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s" s="0">
         <v>189</v>
       </c>
@@ -9226,7 +7819,7 @@
       <c r="C144" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D144" s="188" t="s">
+      <c r="D144" s="148" t="s">
         <v>351</v>
       </c>
       <c r="E144" t="s" s="0">
@@ -9242,7 +7835,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s" s="0">
         <v>189</v>
       </c>
@@ -9252,7 +7845,7 @@
       <c r="C145" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D145" s="191" t="s">
+      <c r="D145" s="149" t="s">
         <v>354</v>
       </c>
       <c r="E145" t="s" s="0">
@@ -9268,7 +7861,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s" s="0">
         <v>189</v>
       </c>
@@ -9278,7 +7871,7 @@
       <c r="C146" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D146" s="193" t="s">
+      <c r="D146" s="150" t="s">
         <v>26</v>
       </c>
       <c r="E146" t="s" s="0">
@@ -9294,7 +7887,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s" s="0">
         <v>189</v>
       </c>
@@ -9304,7 +7897,7 @@
       <c r="C147" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D147" s="197" t="s">
+      <c r="D147" s="151" t="s">
         <v>359</v>
       </c>
       <c r="E147" t="s" s="0">
@@ -9320,7 +7913,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s" s="0">
         <v>189</v>
       </c>
@@ -9330,7 +7923,7 @@
       <c r="C148" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D148" s="200" t="s">
+      <c r="D148" s="152" t="s">
         <v>362</v>
       </c>
       <c r="E148" t="s" s="0">
@@ -9346,7 +7939,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s" s="0">
         <v>189</v>
       </c>
@@ -9356,7 +7949,7 @@
       <c r="C149" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D149" s="203" t="s">
+      <c r="D149" s="153" t="s">
         <v>365</v>
       </c>
       <c r="E149" t="s" s="0">
@@ -9372,7 +7965,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s" s="0">
         <v>189</v>
       </c>
@@ -9382,7 +7975,7 @@
       <c r="C150" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D150" s="205" t="s">
+      <c r="D150" s="154" t="s">
         <v>26</v>
       </c>
       <c r="E150" t="s" s="0">
@@ -9398,7 +7991,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s" s="0">
         <v>76</v>
       </c>
@@ -9408,7 +8001,7 @@
       <c r="C151" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D151" s="208" t="s">
+      <c r="D151" s="155" t="s">
         <v>26</v>
       </c>
       <c r="E151" t="s" s="0">
@@ -9424,7 +8017,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s" s="0">
         <v>79</v>
       </c>
@@ -9434,7 +8027,7 @@
       <c r="C152" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D152" s="211" t="s">
+      <c r="D152" s="156" t="s">
         <v>26</v>
       </c>
       <c r="E152" t="s" s="0">
@@ -9450,7 +8043,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s" s="0">
         <v>79</v>
       </c>
@@ -9460,7 +8053,7 @@
       <c r="C153" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D153" s="214" t="s">
+      <c r="D153" s="157" t="s">
         <v>26</v>
       </c>
       <c r="E153" t="s" s="0">
@@ -9476,7 +8069,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s" s="0">
         <v>189</v>
       </c>
@@ -9486,7 +8079,7 @@
       <c r="C154" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D154" s="218" t="s">
+      <c r="D154" s="158" t="s">
         <v>11</v>
       </c>
       <c r="E154" t="s" s="0">
@@ -9502,7 +8095,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s" s="0">
         <v>189</v>
       </c>
@@ -9512,7 +8105,7 @@
       <c r="C155" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D155" s="221" t="s">
+      <c r="D155" s="159" t="s">
         <v>11</v>
       </c>
       <c r="E155" t="s" s="0">
@@ -9528,7 +8121,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s" s="0">
         <v>189</v>
       </c>
@@ -9538,7 +8131,7 @@
       <c r="C156" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D156" s="224" t="s">
+      <c r="D156" s="160" t="s">
         <v>11</v>
       </c>
       <c r="E156" t="s" s="0">
@@ -9554,7 +8147,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s" s="0">
         <v>189</v>
       </c>
@@ -9564,7 +8157,7 @@
       <c r="C157" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D157" s="227" t="s">
+      <c r="D157" s="161" t="s">
         <v>11</v>
       </c>
       <c r="E157" t="s" s="0">
@@ -9580,7 +8173,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s" s="0">
         <v>189</v>
       </c>
@@ -9590,7 +8183,7 @@
       <c r="C158" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D158" s="230" t="s">
+      <c r="D158" s="162" t="s">
         <v>385</v>
       </c>
       <c r="E158" t="s" s="0">
@@ -9606,7 +8199,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s" s="0">
         <v>189</v>
       </c>
@@ -9616,7 +8209,7 @@
       <c r="C159" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D159" s="233" t="s">
+      <c r="D159" s="163" t="s">
         <v>388</v>
       </c>
       <c r="E159" t="s" s="0">
@@ -9632,7 +8225,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s" s="0">
         <v>189</v>
       </c>
@@ -9642,7 +8235,7 @@
       <c r="C160" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D160" s="236" t="s">
+      <c r="D160" s="164" t="s">
         <v>392</v>
       </c>
       <c r="E160" t="s" s="0">
@@ -9658,7 +8251,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" t="s" s="0">
         <v>189</v>
       </c>
@@ -9668,7 +8261,7 @@
       <c r="C161" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D161" s="239" t="s">
+      <c r="D161" s="165" t="s">
         <v>395</v>
       </c>
       <c r="E161" t="s" s="0">
@@ -9684,7 +8277,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" t="s" s="0">
         <v>189</v>
       </c>
@@ -9694,7 +8287,7 @@
       <c r="C162" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D162" s="242" t="s">
+      <c r="D162" s="166" t="s">
         <v>398</v>
       </c>
       <c r="E162" t="s" s="0">
@@ -9710,7 +8303,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" t="s" s="0">
         <v>189</v>
       </c>
@@ -9720,7 +8313,7 @@
       <c r="C163" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D163" s="245" t="s">
+      <c r="D163" s="167" t="s">
         <v>401</v>
       </c>
       <c r="E163" t="s" s="0">
@@ -9736,7 +8329,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s" s="0">
         <v>189</v>
       </c>
@@ -9746,7 +8339,7 @@
       <c r="C164" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D164" s="248" t="s">
+      <c r="D164" s="168" t="s">
         <v>404</v>
       </c>
       <c r="E164" t="s" s="0">
@@ -9762,7 +8355,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" t="s" s="0">
         <v>189</v>
       </c>
@@ -9772,7 +8365,7 @@
       <c r="C165" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D165" s="251" t="s">
+      <c r="D165" s="169" t="s">
         <v>407</v>
       </c>
       <c r="E165" t="s" s="0">
@@ -9788,7 +8381,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" t="s" s="0">
         <v>189</v>
       </c>
@@ -9798,7 +8391,7 @@
       <c r="C166" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D166" s="254" t="s">
+      <c r="D166" s="170" t="s">
         <v>410</v>
       </c>
       <c r="E166" t="s" s="0">
@@ -9814,7 +8407,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" t="s" s="0">
         <v>189</v>
       </c>
@@ -9824,7 +8417,7 @@
       <c r="C167" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D167" s="257" t="s">
+      <c r="D167" s="171" t="s">
         <v>413</v>
       </c>
       <c r="E167" t="s" s="0">
@@ -9840,7 +8433,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" t="s" s="0">
         <v>189</v>
       </c>
@@ -9850,7 +8443,7 @@
       <c r="C168" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D168" s="260" t="s">
+      <c r="D168" s="172" t="s">
         <v>416</v>
       </c>
       <c r="E168" t="s" s="0">
@@ -9866,7 +8459,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" t="s" s="0">
         <v>189</v>
       </c>
@@ -9876,7 +8469,7 @@
       <c r="C169" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D169" s="262" t="s">
+      <c r="D169" s="173" t="s">
         <v>26</v>
       </c>
       <c r="E169" t="s" s="0">
@@ -9892,7 +8485,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" t="s" s="0">
         <v>189</v>
       </c>
@@ -9902,7 +8495,7 @@
       <c r="C170" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D170" s="265" t="s">
+      <c r="D170" s="174" t="s">
         <v>26</v>
       </c>
       <c r="E170" t="s" s="0">
@@ -9918,7 +8511,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" t="s" s="0">
         <v>189</v>
       </c>
@@ -9928,7 +8521,7 @@
       <c r="C171" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D171" s="269" t="s">
+      <c r="D171" s="175" t="s">
         <v>423</v>
       </c>
       <c r="E171" t="s" s="0">
@@ -9944,7 +8537,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" t="s" s="0">
         <v>76</v>
       </c>
@@ -9954,7 +8547,7 @@
       <c r="C172" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D172" s="272" t="s">
+      <c r="D172" s="176" t="s">
         <v>423</v>
       </c>
       <c r="E172" t="s" s="0">
@@ -9970,7 +8563,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s" s="0">
         <v>79</v>
       </c>
@@ -9980,7 +8573,7 @@
       <c r="C173" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D173" s="275" t="s">
+      <c r="D173" s="177" t="s">
         <v>423</v>
       </c>
       <c r="E173" t="s" s="0">
@@ -9996,7 +8589,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" t="s" s="0">
         <v>79</v>
       </c>
@@ -10006,7 +8599,7 @@
       <c r="C174" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D174" s="278" t="s">
+      <c r="D174" s="178" t="s">
         <v>423</v>
       </c>
       <c r="E174" t="s" s="0">
@@ -10022,7 +8615,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" t="s" s="0">
         <v>84</v>
       </c>
@@ -10032,7 +8625,7 @@
       <c r="C175" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D175" s="281" t="s">
+      <c r="D175" s="179" t="s">
         <v>423</v>
       </c>
       <c r="E175" t="s" s="0">
@@ -10048,7 +8641,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" t="s" s="0">
         <v>87</v>
       </c>
@@ -10058,7 +8651,7 @@
       <c r="C176" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D176" s="284" t="s">
+      <c r="D176" s="180" t="s">
         <v>423</v>
       </c>
       <c r="E176" t="s" s="0">
@@ -10074,7 +8667,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" t="s" s="0">
         <v>90</v>
       </c>
@@ -10084,10 +8677,9 @@
       <c r="C177" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D177" s="287" t="s">
+      <c r="D177" s="181" t="s">
         <v>91</v>
       </c>
-      <c r="E177" s="0"/>
       <c r="F177" t="s" s="0">
         <v>377</v>
       </c>
@@ -10098,7 +8690,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" t="s" s="0">
         <v>19</v>
       </c>
@@ -10108,7 +8700,7 @@
       <c r="C178" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D178" s="290" t="s">
+      <c r="D178" s="182" t="s">
         <v>423</v>
       </c>
       <c r="E178" t="s" s="0">
@@ -10124,7 +8716,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" t="s" s="0">
         <v>96</v>
       </c>
@@ -10134,7 +8726,7 @@
       <c r="C179" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D179" s="293" t="s">
+      <c r="D179" s="183" t="s">
         <v>423</v>
       </c>
       <c r="E179" t="s" s="0">
@@ -10150,7 +8742,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" t="s" s="0">
         <v>99</v>
       </c>
@@ -10160,7 +8752,7 @@
       <c r="C180" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D180" s="296" t="s">
+      <c r="D180" s="184" t="s">
         <v>423</v>
       </c>
       <c r="E180" t="s" s="0">
@@ -10176,7 +8768,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" t="s" s="0">
         <v>102</v>
       </c>
@@ -10186,7 +8778,7 @@
       <c r="C181" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D181" s="299" t="s">
+      <c r="D181" s="185" t="s">
         <v>423</v>
       </c>
       <c r="E181" t="s" s="0">
@@ -10202,7 +8794,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" t="s" s="0">
         <v>8</v>
       </c>
@@ -10212,7 +8804,7 @@
       <c r="C182" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D182" s="302" t="s">
+      <c r="D182" s="186" t="s">
         <v>423</v>
       </c>
       <c r="E182" t="s" s="0">
@@ -10228,7 +8820,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" t="s" s="0">
         <v>16</v>
       </c>
@@ -10238,7 +8830,7 @@
       <c r="C183" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D183" s="305" t="s">
+      <c r="D183" s="187" t="s">
         <v>447</v>
       </c>
       <c r="E183" t="s" s="0">
@@ -10254,7 +8846,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" t="s" s="0">
         <v>84</v>
       </c>
@@ -10264,7 +8856,7 @@
       <c r="C184" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D184" s="308" t="s">
+      <c r="D184" s="188" t="s">
         <v>423</v>
       </c>
       <c r="E184" t="s" s="0">
@@ -10280,7 +8872,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" t="s" s="0">
         <v>112</v>
       </c>
@@ -10290,7 +8882,7 @@
       <c r="C185" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D185" s="311" t="s">
+      <c r="D185" s="189" t="s">
         <v>423</v>
       </c>
       <c r="E185" t="s" s="0">
@@ -10306,7 +8898,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" t="s" s="0">
         <v>87</v>
       </c>
@@ -10316,7 +8908,7 @@
       <c r="C186" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D186" s="314" t="s">
+      <c r="D186" s="190" t="s">
         <v>423</v>
       </c>
       <c r="E186" t="s" s="0">
@@ -10332,7 +8924,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" t="s" s="0">
         <v>90</v>
       </c>
@@ -10342,10 +8934,9 @@
       <c r="C187" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D187" s="317" t="s">
+      <c r="D187" s="191" t="s">
         <v>91</v>
       </c>
-      <c r="E187" s="0"/>
       <c r="F187" t="s" s="0">
         <v>377</v>
       </c>
@@ -10356,7 +8947,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" t="s" s="0">
         <v>16</v>
       </c>
@@ -10366,7 +8957,7 @@
       <c r="C188" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D188" s="320" t="s">
+      <c r="D188" s="192" t="s">
         <v>423</v>
       </c>
       <c r="E188" t="s" s="0">
@@ -10382,7 +8973,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" t="s" s="0">
         <v>19</v>
       </c>
@@ -10392,7 +8983,7 @@
       <c r="C189" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D189" s="323" t="s">
+      <c r="D189" s="193" t="s">
         <v>423</v>
       </c>
       <c r="E189" t="s" s="0">
@@ -10408,7 +8999,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" t="s" s="0">
         <v>122</v>
       </c>
@@ -10418,10 +9009,9 @@
       <c r="C190" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D190" s="325" t="s">
+      <c r="D190" s="194" t="s">
         <v>123</v>
       </c>
-      <c r="E190" s="0"/>
       <c r="F190" t="s" s="0">
         <v>377</v>
       </c>
@@ -10432,7 +9022,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" t="s" s="0">
         <v>125</v>
       </c>
@@ -10442,10 +9032,9 @@
       <c r="C191" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D191" s="328" t="s">
+      <c r="D191" s="195" t="s">
         <v>123</v>
       </c>
-      <c r="E191" s="0"/>
       <c r="F191" t="s" s="0">
         <v>377</v>
       </c>
@@ -10456,7 +9045,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" t="s" s="0">
         <v>127</v>
       </c>
@@ -10466,10 +9055,9 @@
       <c r="C192" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D192" s="331" t="s">
+      <c r="D192" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="E192" s="0"/>
       <c r="F192" t="s" s="0">
         <v>377</v>
       </c>
@@ -10480,7 +9068,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" t="s" s="0">
         <v>129</v>
       </c>
@@ -10490,10 +9078,9 @@
       <c r="C193" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D193" s="334" t="s">
+      <c r="D193" s="197" t="s">
         <v>123</v>
       </c>
-      <c r="E193" s="0"/>
       <c r="F193" t="s" s="0">
         <v>377</v>
       </c>
@@ -10504,7 +9091,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" t="s" s="0">
         <v>131</v>
       </c>
@@ -10514,10 +9101,9 @@
       <c r="C194" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D194" s="337" t="s">
+      <c r="D194" s="198" t="s">
         <v>123</v>
       </c>
-      <c r="E194" s="0"/>
       <c r="F194" t="s" s="0">
         <v>377</v>
       </c>
@@ -10528,7 +9114,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" t="s" s="0">
         <v>133</v>
       </c>
@@ -10538,10 +9124,9 @@
       <c r="C195" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D195" s="340" t="s">
+      <c r="D195" s="199" t="s">
         <v>123</v>
       </c>
-      <c r="E195" s="0"/>
       <c r="F195" t="s" s="0">
         <v>377</v>
       </c>
@@ -10552,7 +9137,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" t="s" s="0">
         <v>135</v>
       </c>
@@ -10562,10 +9147,9 @@
       <c r="C196" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D196" s="343" t="s">
+      <c r="D196" s="200" t="s">
         <v>123</v>
       </c>
-      <c r="E196" s="0"/>
       <c r="F196" t="s" s="0">
         <v>377</v>
       </c>
@@ -10576,7 +9160,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" t="s" s="0">
         <v>137</v>
       </c>
@@ -10586,10 +9170,9 @@
       <c r="C197" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D197" s="346" t="s">
+      <c r="D197" s="201" t="s">
         <v>123</v>
       </c>
-      <c r="E197" s="0"/>
       <c r="F197" t="s" s="0">
         <v>377</v>
       </c>
@@ -10600,7 +9183,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" t="s" s="0">
         <v>139</v>
       </c>
@@ -10610,10 +9193,9 @@
       <c r="C198" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D198" s="349" t="s">
+      <c r="D198" s="202" t="s">
         <v>123</v>
       </c>
-      <c r="E198" s="0"/>
       <c r="F198" t="s" s="0">
         <v>377</v>
       </c>
@@ -10624,7 +9206,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" t="s" s="0">
         <v>141</v>
       </c>
@@ -10634,10 +9216,9 @@
       <c r="C199" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D199" s="352" t="s">
+      <c r="D199" s="203" t="s">
         <v>123</v>
       </c>
-      <c r="E199" s="0"/>
       <c r="F199" t="s" s="0">
         <v>377</v>
       </c>
@@ -10648,7 +9229,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" t="s" s="0">
         <v>143</v>
       </c>
@@ -10658,10 +9239,9 @@
       <c r="C200" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D200" s="355" t="s">
+      <c r="D200" s="204" t="s">
         <v>123</v>
       </c>
-      <c r="E200" s="0"/>
       <c r="F200" t="s" s="0">
         <v>377</v>
       </c>
@@ -10672,7 +9252,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s" s="0">
         <v>145</v>
       </c>
@@ -10682,10 +9262,9 @@
       <c r="C201" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D201" s="358" t="s">
+      <c r="D201" s="205" t="s">
         <v>123</v>
       </c>
-      <c r="E201" s="0"/>
       <c r="F201" t="s" s="0">
         <v>377</v>
       </c>
@@ -10696,7 +9275,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" t="s" s="0">
         <v>147</v>
       </c>
@@ -10706,10 +9285,9 @@
       <c r="C202" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D202" s="361" t="s">
+      <c r="D202" s="206" t="s">
         <v>123</v>
       </c>
-      <c r="E202" s="0"/>
       <c r="F202" t="s" s="0">
         <v>377</v>
       </c>
@@ -10720,7 +9298,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" t="s" s="0">
         <v>149</v>
       </c>
@@ -10730,10 +9308,9 @@
       <c r="C203" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D203" s="364" t="s">
+      <c r="D203" s="207" t="s">
         <v>123</v>
       </c>
-      <c r="E203" s="0"/>
       <c r="F203" t="s" s="0">
         <v>377</v>
       </c>
@@ -10744,7 +9321,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" t="s" s="0">
         <v>151</v>
       </c>
@@ -10754,7 +9331,7 @@
       <c r="C204" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D204" s="367" t="s">
+      <c r="D204" s="208" t="s">
         <v>423</v>
       </c>
       <c r="E204" t="s" s="0">
@@ -10770,7 +9347,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" t="s" s="0">
         <v>155</v>
       </c>
@@ -10780,7 +9357,7 @@
       <c r="C205" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D205" s="370" t="s">
+      <c r="D205" s="209" t="s">
         <v>423</v>
       </c>
       <c r="E205" t="s" s="0">
@@ -10796,7 +9373,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" t="s" s="0">
         <v>158</v>
       </c>
@@ -10806,10 +9383,9 @@
       <c r="C206" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D206" s="373" t="s">
+      <c r="D206" s="210" t="s">
         <v>123</v>
       </c>
-      <c r="E206" s="0"/>
       <c r="F206" t="s" s="0">
         <v>377</v>
       </c>
@@ -10820,7 +9396,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" t="s" s="0">
         <v>160</v>
       </c>
@@ -10830,10 +9406,9 @@
       <c r="C207" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D207" s="376" t="s">
+      <c r="D207" s="211" t="s">
         <v>123</v>
       </c>
-      <c r="E207" s="0"/>
       <c r="F207" t="s" s="0">
         <v>377</v>
       </c>
@@ -10844,7 +9419,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" t="s" s="0">
         <v>162</v>
       </c>
@@ -10854,10 +9429,9 @@
       <c r="C208" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D208" s="379" t="s">
+      <c r="D208" s="212" t="s">
         <v>123</v>
       </c>
-      <c r="E208" s="0"/>
       <c r="F208" t="s" s="0">
         <v>377</v>
       </c>
@@ -10868,7 +9442,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" t="s" s="0">
         <v>164</v>
       </c>
@@ -10878,10 +9452,9 @@
       <c r="C209" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D209" s="382" t="s">
+      <c r="D209" s="213" t="s">
         <v>123</v>
       </c>
-      <c r="E209" s="0"/>
       <c r="F209" t="s" s="0">
         <v>377</v>
       </c>
@@ -10892,7 +9465,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" t="s" s="0">
         <v>139</v>
       </c>
@@ -10902,10 +9475,9 @@
       <c r="C210" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D210" s="385" t="s">
+      <c r="D210" s="214" t="s">
         <v>123</v>
       </c>
-      <c r="E210" s="0"/>
       <c r="F210" t="s" s="0">
         <v>377</v>
       </c>
@@ -10916,7 +9488,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" t="s" s="0">
         <v>141</v>
       </c>
@@ -10926,10 +9498,9 @@
       <c r="C211" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D211" s="388" t="s">
+      <c r="D211" s="215" t="s">
         <v>123</v>
       </c>
-      <c r="E211" s="0"/>
       <c r="F211" t="s" s="0">
         <v>377</v>
       </c>
@@ -10940,7 +9511,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" t="s" s="0">
         <v>143</v>
       </c>
@@ -10950,10 +9521,9 @@
       <c r="C212" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D212" s="391" t="s">
+      <c r="D212" s="216" t="s">
         <v>123</v>
       </c>
-      <c r="E212" s="0"/>
       <c r="F212" t="s" s="0">
         <v>377</v>
       </c>
@@ -10964,7 +9534,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" t="s" s="0">
         <v>145</v>
       </c>
@@ -10974,10 +9544,9 @@
       <c r="C213" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D213" s="394" t="s">
+      <c r="D213" s="217" t="s">
         <v>123</v>
       </c>
-      <c r="E213" s="0"/>
       <c r="F213" t="s" s="0">
         <v>377</v>
       </c>
@@ -10988,7 +9557,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" t="s" s="0">
         <v>147</v>
       </c>
@@ -10998,10 +9567,9 @@
       <c r="C214" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D214" s="397" t="s">
+      <c r="D214" s="218" t="s">
         <v>123</v>
       </c>
-      <c r="E214" s="0"/>
       <c r="F214" t="s" s="0">
         <v>377</v>
       </c>
@@ -11010,6 +9578,84 @@
       </c>
       <c r="H214" t="s" s="0">
         <v>487</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C215" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D215" s="221" t="s">
+        <v>488</v>
+      </c>
+      <c r="E215" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="F215" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="G215" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H215" t="s" s="0">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C216" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D216" s="224" t="s">
+        <v>492</v>
+      </c>
+      <c r="E216" t="s" s="0">
+        <v>493</v>
+      </c>
+      <c r="F216" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="G216" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H216" t="s" s="0">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B217" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C217" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D217" s="227" t="s">
+        <v>495</v>
+      </c>
+      <c r="E217" t="s" s="0">
+        <v>496</v>
+      </c>
+      <c r="F217" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="G217" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H217" t="s" s="0">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -11084,7 +9730,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
         <v>189</v>
       </c>
@@ -11094,7 +9740,7 @@
       <c r="C3" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="129" t="s">
         <v>297</v>
       </c>
       <c r="E3" t="s" s="0">
@@ -11110,7 +9756,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
         <v>189</v>
       </c>
@@ -11120,7 +9766,7 @@
       <c r="C4" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="D4" s="133" t="s">
+      <c r="D4" s="130" t="s">
         <v>297</v>
       </c>
       <c r="E4" t="s" s="0">

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="504">
   <si>
     <t>Test Data</t>
   </si>
@@ -1718,13 +1718,31 @@
   <si>
     <t>2026-03-12 11:04:03</t>
   </si>
+  <si>
+    <t>69b3b9eff25c5f9cc3a01e1d</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:47:48</t>
+  </si>
+  <si>
+    <t>69b3ccadf25c5f9cc3a09192</t>
+  </si>
+  <si>
+    <t>2026-03-13 14:07:46</t>
+  </si>
+  <si>
+    <t>69b3cd0ff25c5f9cc3a0952a</t>
+  </si>
+  <si>
+    <t>2026-03-13 14:09:20</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="228" x14ac:knownFonts="1">
+  <fonts count="237" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3037,6 +3055,57 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -3130,7 +3199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3811,6 +3880,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="227" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4156,7 +4252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -9656,6 +9752,84 @@
       </c>
       <c r="H217" t="s" s="0">
         <v>497</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B218" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C218" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D218" s="230" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="F218" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G218" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H218" t="s" s="0">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B219" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C219" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D219" s="233" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="F219" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G219" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H219" t="s" s="0">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B220" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C220" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D220" s="236" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" t="s" s="0">
+        <v>502</v>
+      </c>
+      <c r="F220" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="G220" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H220" t="s" s="0">
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="526">
   <si>
     <t>Test Data</t>
   </si>
@@ -1736,13 +1736,84 @@
   <si>
     <t>2026-03-13 14:09:20</t>
   </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://x3d-sim.credorax.net/acs/challenge" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.80, chrome: {chromedriverVersion: 146.0.7680.80 (f08938029c88..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56382}, goog:processID: 22512, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56382/devtoo..., se:cdpVersion: 146.0.7680.80, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 7be8685af2f634980df09d4415616493</t>
+  </si>
+  <si>
+    <t>69b91587b0e58eeb582883c7</t>
+  </si>
+  <si>
+    <t>shift4</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:20:09</t>
+  </si>
+  <si>
+    <t>69b917dfb0e58eeb58288d56</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:30:04</t>
+  </si>
+  <si>
+    <t>69b91837b0e58eeb58289130</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:31:26</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Unsupported PSP: shift4Frictionless</t>
+  </si>
+  <si>
+    <t>69b919a2b0e58eeb58289e47</t>
+  </si>
+  <si>
+    <t>shift4Frictionless</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:36:53</t>
+  </si>
+  <si>
+    <t>69b919e6b0e58eeb5828a643</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:38:41</t>
+  </si>
+  <si>
+    <t>69b91a53b0e58eeb5828aa0e</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:39:51</t>
+  </si>
+  <si>
+    <t>69b91d15b0e58eeb5828bcb6</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:51:37</t>
+  </si>
+  <si>
+    <t>69b91d30b0e58eeb5828c074</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:52:02</t>
+  </si>
+  <si>
+    <t>69b91d4ab0e58eeb5828c6ac</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:52:28</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="237" x14ac:knownFonts="1">
+  <fonts count="264" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3055,6 +3126,159 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -3199,7 +3423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3907,6 +4131,87 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="236" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4252,7 +4557,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -9830,6 +10135,240 @@
       </c>
       <c r="H220" t="s" s="0">
         <v>503</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B221" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C221" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D221" s="239" t="s">
+        <v>504</v>
+      </c>
+      <c r="E221" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="F221" t="s" s="0">
+        <v>506</v>
+      </c>
+      <c r="G221" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H221" t="s" s="0">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B222" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C222" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D222" s="241" t="s">
+        <v>26</v>
+      </c>
+      <c r="E222" t="s" s="0">
+        <v>508</v>
+      </c>
+      <c r="F222" t="s" s="0">
+        <v>506</v>
+      </c>
+      <c r="G222" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H222" t="s" s="0">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B223" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C223" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D223" s="244" t="s">
+        <v>26</v>
+      </c>
+      <c r="E223" t="s" s="0">
+        <v>510</v>
+      </c>
+      <c r="F223" t="s" s="0">
+        <v>506</v>
+      </c>
+      <c r="G223" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H223" t="s" s="0">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B224" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C224" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D224" s="248" t="s">
+        <v>512</v>
+      </c>
+      <c r="E224" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="F224" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="G224" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H224" t="s" s="0">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B225" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C225" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D225" s="251" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" t="s" s="0">
+        <v>516</v>
+      </c>
+      <c r="F225" t="s" s="0">
+        <v>506</v>
+      </c>
+      <c r="G225" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H225" t="s" s="0">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B226" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C226" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D226" s="254" t="s">
+        <v>512</v>
+      </c>
+      <c r="E226" t="s" s="0">
+        <v>518</v>
+      </c>
+      <c r="F226" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="G226" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H226" t="s" s="0">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B227" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C227" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D227" s="257" t="s">
+        <v>512</v>
+      </c>
+      <c r="E227" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="F227" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="G227" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H227" t="s" s="0">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B228" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C228" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D228" s="260" t="s">
+        <v>512</v>
+      </c>
+      <c r="E228" t="s" s="0">
+        <v>522</v>
+      </c>
+      <c r="F228" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="G228" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H228" t="s" s="0">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B229" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C229" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D229" s="263" t="s">
+        <v>512</v>
+      </c>
+      <c r="E229" t="s" s="0">
+        <v>524</v>
+      </c>
+      <c r="F229" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="G229" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H229" t="s" s="0">
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="529">
   <si>
     <t>Test Data</t>
   </si>
@@ -1807,13 +1807,22 @@
   <si>
     <t>2026-03-17 14:52:28</t>
   </si>
+  <si>
+    <t>69bcdb1931f5cace0479f761</t>
+  </si>
+  <si>
+    <t>payaza-card</t>
+  </si>
+  <si>
+    <t>2026-03-20 11:00:41</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="264" x14ac:knownFonts="1">
+  <fonts count="267" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3126,6 +3135,23 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -3423,7 +3449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4212,6 +4238,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="263" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4557,7 +4592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -10369,6 +10404,32 @@
       </c>
       <c r="H229" t="s" s="0">
         <v>525</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B230" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C230" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D230" s="266" t="s">
+        <v>423</v>
+      </c>
+      <c r="E230" t="s" s="0">
+        <v>526</v>
+      </c>
+      <c r="F230" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="G230" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H230" t="s" s="0">
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="536">
   <si>
     <t>Test Data</t>
   </si>
@@ -1816,13 +1816,34 @@
   <si>
     <t>2026-03-20 11:00:41</t>
   </si>
+  <si>
+    <t>FAIL → Exception occurred during payment flow: java.lang.RuntimeException: ✗ selectAuthResult dropdown NOT found in any iframe!</t>
+  </si>
+  <si>
+    <t>69bcdc2b31f5cace0479feca</t>
+  </si>
+  <si>
+    <t>2026-03-20 11:05:16</t>
+  </si>
+  <si>
+    <t>69bcde1731f5cace047a0ed7</t>
+  </si>
+  <si>
+    <t>2026-03-20 11:12:32</t>
+  </si>
+  <si>
+    <t>69bcdebf31f5cace047a12b1</t>
+  </si>
+  <si>
+    <t>2026-03-20 11:15:22</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="267" x14ac:knownFonts="1">
+  <fonts count="276" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3135,6 +3156,57 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -3449,7 +3521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4247,6 +4319,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="266" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4592,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -10430,6 +10529,84 @@
       </c>
       <c r="H230" t="s" s="0">
         <v>528</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B231" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C231" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D231" s="269" t="s">
+        <v>529</v>
+      </c>
+      <c r="E231" t="s" s="0">
+        <v>530</v>
+      </c>
+      <c r="F231" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G231" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="H231" t="s" s="0">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B232" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C232" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D232" s="271" t="s">
+        <v>208</v>
+      </c>
+      <c r="E232" t="s" s="0">
+        <v>532</v>
+      </c>
+      <c r="F232" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="G232" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H232" t="s" s="0">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B233" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C233" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D233" s="274" t="s">
+        <v>26</v>
+      </c>
+      <c r="E233" t="s" s="0">
+        <v>534</v>
+      </c>
+      <c r="F233" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="G233" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H233" t="s" s="0">
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Purchase_Result" sheetId="2" r:id="rId2"/>
     <sheet name="s2s_Result" sheetId="3" r:id="rId3"/>
+    <sheet name="EndToEnd_Result" r:id="rId7" sheetId="4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="610">
   <si>
     <t>Test Data</t>
   </si>
@@ -1837,13 +1838,275 @@
   <si>
     <t>2026-03-20 11:15:22</t>
   </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [5e414e48a2893b2d7103fab8e0132dd8, switchToFrame {id=null}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.165, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55771}, goog:processID: 7232, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55771/devtoo..., se:cdpVersion: 146.0.7680.165, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 5e414e48a2893b2d7103fab8e0132dd8</t>
+  </si>
+  <si>
+    <t>69ca1c6fba98768c4a5cd5e6</t>
+  </si>
+  <si>
+    <t>2026-03-30 12:17:40</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [d9f6b1265c1db2a98c611bdf84164c61, switchToFrame {id=null}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.165, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:49162}, goog:processID: 9968, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:49162/devtoo..., se:cdpVersion: 146.0.7680.165, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: d9f6b1265c1db2a98c611bdf84164c61</t>
+  </si>
+  <si>
+    <t>69ca1cd3ba98768c4a5cd60b</t>
+  </si>
+  <si>
+    <t>2026-03-30 12:19:37</t>
+  </si>
+  <si>
+    <t>GBP Netbanking</t>
+  </si>
+  <si>
+    <t>Payment Successfully</t>
+  </si>
+  <si>
+    <t>69ce55ec91fccd83bce069a1</t>
+  </si>
+  <si>
+    <t>EasyBuzz-NetBanking</t>
+  </si>
+  <si>
+    <t>Netbanking</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:11:58</t>
+  </si>
+  <si>
+    <t>69ce584491fccd83bce06fa2</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:21:58</t>
+  </si>
+  <si>
+    <t>69ce5d719ba1ee550c03f8b9</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:44:03</t>
+  </si>
+  <si>
+    <t>69ce5ed59ba1ee550c03fe8d</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:49:59</t>
+  </si>
+  <si>
+    <t>69ce5f6b9ba1ee550c04044b</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:52:28</t>
+  </si>
+  <si>
+    <t>69ce61089ba1ee550c041a6b</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:59:22</t>
+  </si>
+  <si>
+    <t>69d34210dd515144636d4306</t>
+  </si>
+  <si>
+    <t>2026-04-06 10:48:34</t>
+  </si>
+  <si>
+    <t>69d34239dd515144636d45e1</t>
+  </si>
+  <si>
+    <t>2026-04-06 10:49:15</t>
+  </si>
+  <si>
+    <t>69d34262dd515144636d48bc</t>
+  </si>
+  <si>
+    <t>2026-04-06 10:49:54</t>
+  </si>
+  <si>
+    <t>69d34288dd515144636d4b99</t>
+  </si>
+  <si>
+    <t>2026-04-06 10:50:32</t>
+  </si>
+  <si>
+    <t>69d342b0dd515144636d4e74</t>
+  </si>
+  <si>
+    <t>2026-04-06 10:51:12</t>
+  </si>
+  <si>
+    <t>69d372f8102d0a89d01a963c</t>
+  </si>
+  <si>
+    <t>2026-04-06 14:17:24</t>
+  </si>
+  <si>
+    <t>69d37335102d0a89d01a9935</t>
+  </si>
+  <si>
+    <t>2026-04-06 14:18:16</t>
+  </si>
+  <si>
+    <t>69d37365102d0a89d01aa064</t>
+  </si>
+  <si>
+    <t>2026-04-06 14:19:04</t>
+  </si>
+  <si>
+    <t>69d37397102d0a89d01aa362</t>
+  </si>
+  <si>
+    <t>2026-04-06 14:19:53</t>
+  </si>
+  <si>
+    <t>69d373c8102d0a89d01aa643</t>
+  </si>
+  <si>
+    <t>2026-04-06 14:20:44</t>
+  </si>
+  <si>
+    <t>69d393478519a511548f0b43</t>
+  </si>
+  <si>
+    <t>2026-04-06 16:35:10</t>
+  </si>
+  <si>
+    <t>69d3937a8519a511548f0e20</t>
+  </si>
+  <si>
+    <t>2026-04-06 16:35:56</t>
+  </si>
+  <si>
+    <t>69d393a88519a511548f10fd</t>
+  </si>
+  <si>
+    <t>2026-04-06 16:36:40</t>
+  </si>
+  <si>
+    <t>69d393d28519a511548f13e4</t>
+  </si>
+  <si>
+    <t>2026-04-06 16:37:21</t>
+  </si>
+  <si>
+    <t>69d393fb8519a511548f16bf</t>
+  </si>
+  <si>
+    <t>2026-04-06 16:38:03</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://pay4.sandbox.payabl.com/3dss/test/acs" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60476}, goog:processID: 31392, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60476/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 739c65924183add533a34453c95c5bec</t>
+  </si>
+  <si>
+    <t>69d3a3928519a511548f5867</t>
+  </si>
+  <si>
+    <t>payable-pix</t>
+  </si>
+  <si>
+    <t>2026-04-06 17:45:10</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://pay4.sandbox.payabl.com/3dss/test/acs" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60163}, goog:processID: 35960, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60163/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 63ca75314ea26a8c52dc9a92077292c7</t>
+  </si>
+  <si>
+    <t>69d3a4b88519a511548f5c92</t>
+  </si>
+  <si>
+    <t>2026-04-06 17:50:06</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://staging.paysecure.net/login" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:49679}, goog:processID: 21440, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:49679/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: fe61b0c7ae5c7bb2831e5c4565115a72</t>
+  </si>
+  <si>
+    <t>69d3a5d78519a511548f60d1</t>
+  </si>
+  <si>
+    <t>2026-04-06 17:54:49</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=146.0.7680.178)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [df58fb8d200839fbb5521bcb024b07ce, setCurrentWindowSize {height=720, width=1080}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62100}, goog:processID: 38820, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62100/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: df58fb8d200839fbb5521bcb024b07ce</t>
+  </si>
+  <si>
+    <t>69d3a6ac8519a511548f653e</t>
+  </si>
+  <si>
+    <t>2026-04-06 17:57:30</t>
+  </si>
+  <si>
+    <t>69d3a6d58519a511548f6558</t>
+  </si>
+  <si>
+    <t>2026-04-06 17:58:49</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://pay4.sandbox.payabl.com/3dss/test/acs" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64362}, goog:processID: 33424, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64362/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: c6eb6bdfda136a25d109af27adb06263</t>
+  </si>
+  <si>
+    <t>69d3a8f38519a511548f7109</t>
+  </si>
+  <si>
+    <t>2026-04-06 18:08:04</t>
+  </si>
+  <si>
+    <t>69d3abe68519a511548f79bc</t>
+  </si>
+  <si>
+    <t>2026-04-06 18:20:48</t>
+  </si>
+  <si>
+    <t>69d3ac478519a511548f7dd2</t>
+  </si>
+  <si>
+    <t>2026-04-06 18:22:15</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="276" x14ac:knownFonts="1">
+  <fonts count="369" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3156,6 +3419,533 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -3521,7 +4311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4346,6 +5136,285 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="275" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4691,7 +5760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -10607,6 +11676,266 @@
       </c>
       <c r="H233" t="s" s="0">
         <v>535</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B234" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C234" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D234" s="278" t="s">
+        <v>536</v>
+      </c>
+      <c r="E234" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="F234" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G234" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H234" t="s" s="0">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B235" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C235" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D235" s="281" t="s">
+        <v>539</v>
+      </c>
+      <c r="E235" t="s" s="0">
+        <v>540</v>
+      </c>
+      <c r="F235" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="G235" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H235" t="s" s="0">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B236" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C236" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D236" s="347" t="s">
+        <v>588</v>
+      </c>
+      <c r="E236" t="s" s="0">
+        <v>589</v>
+      </c>
+      <c r="F236" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G236" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H236" t="s" s="0">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B237" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C237" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D237" s="350" t="s">
+        <v>592</v>
+      </c>
+      <c r="E237" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="F237" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G237" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H237" t="s" s="0">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B238" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C238" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D238" s="353" t="s">
+        <v>595</v>
+      </c>
+      <c r="E238" t="s" s="0">
+        <v>596</v>
+      </c>
+      <c r="F238" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G238" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H238" t="s" s="0">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B239" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C239" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D239" s="356" t="s">
+        <v>598</v>
+      </c>
+      <c r="E239" t="s" s="0">
+        <v>599</v>
+      </c>
+      <c r="F239" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G239" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H239" t="s" s="0">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B240" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C240" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D240" s="359" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" t="s" s="0">
+        <v>601</v>
+      </c>
+      <c r="F240" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G240" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H240" t="s" s="0">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B241" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C241" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D241" s="362" t="s">
+        <v>603</v>
+      </c>
+      <c r="E241" t="s" s="0">
+        <v>604</v>
+      </c>
+      <c r="F241" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G241" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H241" t="s" s="0">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B242" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C242" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D242" s="365" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" t="s" s="0">
+        <v>606</v>
+      </c>
+      <c r="F242" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G242" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H242" t="s" s="0">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B243" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C243" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D243" s="368" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" t="s" s="0">
+        <v>608</v>
+      </c>
+      <c r="F243" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G243" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H243" t="s" s="0">
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -10736,4 +12065,596 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="14.58984375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.2734375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.171875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="17.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="24.37890625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="19.171875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.19140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.95703125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="282">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="282">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="282">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="282">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="282">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="282">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="282">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="282">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D2" s="283" t="s">
+        <v>543</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>544</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D3" s="286" t="s">
+        <v>543</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D4" s="289" t="s">
+        <v>543</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>550</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D5" s="292" t="s">
+        <v>543</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D6" s="295" t="s">
+        <v>543</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>554</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D7" s="298" t="s">
+        <v>543</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>556</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D8" s="301" t="s">
+        <v>543</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D9" s="304" t="s">
+        <v>543</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>560</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D10" s="307" t="s">
+        <v>543</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>562</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D11" s="310" t="s">
+        <v>543</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>564</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D12" s="313" t="s">
+        <v>543</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>566</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D13" s="316" t="s">
+        <v>543</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>568</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D14" s="319" t="s">
+        <v>543</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>570</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D15" s="322" t="s">
+        <v>543</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>572</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D16" s="325" t="s">
+        <v>543</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>574</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D17" s="328" t="s">
+        <v>543</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>576</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D18" s="331" t="s">
+        <v>543</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>578</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D19" s="334" t="s">
+        <v>543</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>580</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D20" s="337" t="s">
+        <v>543</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>582</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D21" s="340" t="s">
+        <v>543</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D22" s="343" t="s">
+        <v>543</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>586</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="635">
   <si>
     <t>Test Data</t>
   </si>
@@ -2100,13 +2100,103 @@
   <si>
     <t>2026-04-06 18:22:15</t>
   </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/2da1724d14ef49e1e950764b0f16510d/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64041}, goog:processID: 44592, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64041/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 4d011da0cacd2438ff5ae4d6e3227a4f</t>
+  </si>
+  <si>
+    <t>69d495998519a511548ffb31</t>
+  </si>
+  <si>
+    <t>2026-04-07 10:59:47</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/f2665ff86e281ced321ad226f942d8d8/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60795}, goog:processID: 45112, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60795/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: a235fad0159c029354ee92aa58056c7f</t>
+  </si>
+  <si>
+    <t>69d497218519a511548ffb6c</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:06:25</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/5b5ba002a03652f3df3450c4efc3781b/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56063}, goog:processID: 35312, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56063/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e1d91ef5721374be8bb0ac6920c598e0</t>
+  </si>
+  <si>
+    <t>69d499068519a511548ffbc7</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:14:32</t>
+  </si>
+  <si>
+    <t>69d4998a8519a511548ffbe4</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:14:38</t>
+  </si>
+  <si>
+    <t>69d49dbb8519a51154900377</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:32:34</t>
+  </si>
+  <si>
+    <t>69d49e738519a51154900785</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:35:30</t>
+  </si>
+  <si>
+    <t>69d49f398519a51154900faf</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:38:53</t>
+  </si>
+  <si>
+    <t>69d4a0c48519a51154901c3a</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:45:29</t>
+  </si>
+  <si>
+    <t>69d4a4238519a511549032f7</t>
+  </si>
+  <si>
+    <t>2026-04-07 11:59:49</t>
+  </si>
+  <si>
+    <t>69d4a46e8519a51154903753</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:01:04</t>
+  </si>
+  <si>
+    <t>69d4a50c8519a51154903e42</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:08:28</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="369" x14ac:knownFonts="1">
+  <fonts count="402" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3419,6 +3509,193 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -4311,7 +4588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="369">
+  <cellXfs count="402">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5415,6 +5692,105 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="368" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5760,7 +6136,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -11936,6 +12312,292 @@
       </c>
       <c r="H243" t="s" s="0">
         <v>609</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B244" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C244" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D244" s="371" t="s">
+        <v>610</v>
+      </c>
+      <c r="E244" t="s" s="0">
+        <v>611</v>
+      </c>
+      <c r="F244" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G244" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H244" t="s" s="0">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B245" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C245" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D245" s="374" t="s">
+        <v>613</v>
+      </c>
+      <c r="E245" t="s" s="0">
+        <v>614</v>
+      </c>
+      <c r="F245" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G245" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H245" t="s" s="0">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B246" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C246" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D246" s="377" t="s">
+        <v>616</v>
+      </c>
+      <c r="E246" t="s" s="0">
+        <v>617</v>
+      </c>
+      <c r="F246" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G246" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="H246" t="s" s="0">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B247" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C247" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D247" s="379" t="s">
+        <v>26</v>
+      </c>
+      <c r="E247" t="s" s="0">
+        <v>619</v>
+      </c>
+      <c r="F247" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G247" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H247" t="s" s="0">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B248" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C248" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D248" s="382" t="s">
+        <v>26</v>
+      </c>
+      <c r="E248" t="s" s="0">
+        <v>621</v>
+      </c>
+      <c r="F248" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G248" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H248" t="s" s="0">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B249" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C249" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D249" s="385" t="s">
+        <v>26</v>
+      </c>
+      <c r="E249" t="s" s="0">
+        <v>623</v>
+      </c>
+      <c r="F249" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G249" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H249" t="s" s="0">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B250" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C250" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D250" s="388" t="s">
+        <v>26</v>
+      </c>
+      <c r="E250" t="s" s="0">
+        <v>625</v>
+      </c>
+      <c r="F250" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G250" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H250" t="s" s="0">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B251" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C251" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D251" s="391" t="s">
+        <v>26</v>
+      </c>
+      <c r="E251" t="s" s="0">
+        <v>627</v>
+      </c>
+      <c r="F251" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G251" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H251" t="s" s="0">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B252" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C252" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D252" s="394" t="s">
+        <v>26</v>
+      </c>
+      <c r="E252" t="s" s="0">
+        <v>629</v>
+      </c>
+      <c r="F252" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G252" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H252" t="s" s="0">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B253" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C253" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D253" s="397" t="s">
+        <v>26</v>
+      </c>
+      <c r="E253" t="s" s="0">
+        <v>631</v>
+      </c>
+      <c r="F253" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G253" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H253" t="s" s="0">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B254" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C254" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D254" s="401" t="s">
+        <v>11</v>
+      </c>
+      <c r="E254" t="s" s="0">
+        <v>633</v>
+      </c>
+      <c r="F254" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G254" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H254" t="s" s="0">
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="712">
   <si>
     <t>Test Data</t>
   </si>
@@ -2190,13 +2190,313 @@
   <si>
     <t>2026-04-07 12:08:28</t>
   </si>
+  <si>
+    <t>69d4aa4d8519a5115490638e</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:30:57</t>
+  </si>
+  <si>
+    <t>69d4abbb8519a51154907a3f</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:36:58</t>
+  </si>
+  <si>
+    <t>69d4ad248519a511549082de</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:42:59</t>
+  </si>
+  <si>
+    <t>69d4ae8e8519a5115490946a</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:49:00</t>
+  </si>
+  <si>
+    <t>69d4aff78519a5115490a974</t>
+  </si>
+  <si>
+    <t>2026-04-07 12:55:04</t>
+  </si>
+  <si>
+    <t>69d4b1638519a5115490bac5</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:01:07</t>
+  </si>
+  <si>
+    <t>69d4b2ce8519a5115490d121</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:07:10</t>
+  </si>
+  <si>
+    <t>69d4b4388519a5115490d9a9</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:13:11</t>
+  </si>
+  <si>
+    <t>69d4b5a2b8ede8a3289dc126</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:19:13</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/4dd305e0ade2a8e59c799a1b35676b77/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:52996}, goog:processID: 39792, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:52996/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 97ee5386c51f9bf00d96ae9d80fed564</t>
+  </si>
+  <si>
+    <t>69d4b70db8ede8a3289dc52c</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:22:32</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/c40366767ba097d0f5f18d4b312f3871/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:65014}, goog:processID: 38828, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:65014/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: fc037f5b0e009aff900911b32f856a44</t>
+  </si>
+  <si>
+    <t>69d4b970b8ede8a3289dc894</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:32:43</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/e322c16e1dd740542700a6251fee6c20/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:49300}, goog:processID: 41440, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:49300/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: b966d6efa99e6d7f014f25210c361675</t>
+  </si>
+  <si>
+    <t>69d4ba36b8ede8a3289dcba1</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:36:00</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/75eed97977316b58a1322523272b2bc6/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56395}, goog:processID: 38520, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56395/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 4e84cac8c72f0b55e48131fd048fa05b</t>
+  </si>
+  <si>
+    <t>69d4baf7b8ede8a3289dcbf2</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:39:13</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/bca2a3d838206366f56c022b60467b38/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54609}, goog:processID: 30412, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54609/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 7bf7f9400c852411c07a1fea3f5f7677</t>
+  </si>
+  <si>
+    <t>69d4bbbbb8ede8a3289dcc5b</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:42:29</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/a735c66ff064a75b07bf322ccfd94f1a/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:65428}, goog:processID: 17236, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:65428/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1fe15a04ff69b248ef28c46b19a27d11</t>
+  </si>
+  <si>
+    <t>69d4bc7eb8ede8a3289dd318</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:45:44</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/e24f953b2dadf4756984d1bd23d543cf/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60906}, goog:processID: 24084, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60906/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f53958122cd29d9d70ea9bc85b526412</t>
+  </si>
+  <si>
+    <t>69d4bd41b8ede8a3289dd745</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:48:59</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/3a3e68ad0169f1b226fd41afb6504bdf/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:49747}, goog:processID: 34204, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:49747/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: d1ccf7af3fe48fe975dc4bd11cb9a9bc</t>
+  </si>
+  <si>
+    <t>69d4be08b8ede8a3289dd76a</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:52:22</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Expected condition failed: waiting for url to contain "issucces". Current url: "https://test4.paymentsclub.net/payments/0170c1366788aa1df69d7f8aeb24d7d9/" (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60984}, goog:processID: 38864, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60984/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f858851dad5560ba14eb6434384b755a</t>
+  </si>
+  <si>
+    <t>69d4bed3b8ede8a3289ddb8d</t>
+  </si>
+  <si>
+    <t>2026-04-07 13:55:44</t>
+  </si>
+  <si>
+    <t>69d4bf9eb8ede8a3289ddbc7</t>
+  </si>
+  <si>
+    <t>2026-04-07 14:01:52</t>
+  </si>
+  <si>
+    <t>69d4c110b8ede8a3289de8af</t>
+  </si>
+  <si>
+    <t>2026-04-07 14:08:02</t>
+  </si>
+  <si>
+    <t>69d4c280b8ede8a3289decfe</t>
+  </si>
+  <si>
+    <t>2026-04-07 14:14:10</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [05698f576534bf734783e1ad97d1139e, getCurrentUrl {}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60950}, goog:processID: 49872, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60950/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 05698f576534bf734783e1ad97d1139e</t>
+  </si>
+  <si>
+    <t>69d632078189e9d43264d2cf</t>
+  </si>
+  <si>
+    <t>2026-04-08 16:17:17</t>
+  </si>
+  <si>
+    <t>69d632448189e9d43264d2ee</t>
+  </si>
+  <si>
+    <t>2026-04-08 16:23:15</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [cc72450f35767c9fecdc0da48c02151a, getCurrentUrl {}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:59808}, goog:processID: 7404, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:59808/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: cc72450f35767c9fecdc0da48c02151a</t>
+  </si>
+  <si>
+    <t>69d6345c8189e9d43264d441</t>
+  </si>
+  <si>
+    <t>2026-04-08 16:29:03</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [e6b0b1a9c634070a25941e7bfff9870c, getCurrentUrl {}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:63535}, goog:processID: 49224, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:63535/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e6b0b1a9c634070a25941e7bfff9870c</t>
+  </si>
+  <si>
+    <t>69d637f88189e9d43264d797</t>
+  </si>
+  <si>
+    <t>2026-04-08 16:42:54</t>
+  </si>
+  <si>
+    <t>2026-04-08 16:45:49</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: invalid session id
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [3e690eb221402d0335d35cb727f772a5, getCurrentUrl {}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:57472}, goog:processID: 1056, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:57472/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 3e690eb221402d0335d35cb727f772a5</t>
+  </si>
+  <si>
+    <t>69d744eaead38b2473c49470</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>2026-04-09 11:49:48</t>
+  </si>
+  <si>
+    <t>69d74804ead38b2473c499c5</t>
+  </si>
+  <si>
+    <t>2026-04-09 12:03:18</t>
+  </si>
+  <si>
+    <t>69d7483dead38b2473c49e75</t>
+  </si>
+  <si>
+    <t>2026-04-09 12:04:12</t>
+  </si>
+  <si>
+    <t>69d74b65ead38b2473c4ace3</t>
+  </si>
+  <si>
+    <t>2026-04-09 12:17:58</t>
+  </si>
+  <si>
+    <t>69d74baaead38b2473c4b183</t>
+  </si>
+  <si>
+    <t>2026-04-09 12:19:00</t>
+  </si>
+  <si>
+    <t>69d74be7ead38b2473c4b61e</t>
+  </si>
+  <si>
+    <t>2026-04-09 12:20:06</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="402" x14ac:knownFonts="1">
+  <fonts count="498" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3509,6 +3809,550 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -4588,7 +5432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="402">
+  <cellXfs count="498">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5791,6 +6635,294 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="401" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6136,7 +7268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -12598,6 +13730,836 @@
       </c>
       <c r="H254" t="s" s="0">
         <v>634</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B255" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C255" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D255" s="404" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" t="s" s="0">
+        <v>635</v>
+      </c>
+      <c r="F255" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G255" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H255" t="s" s="0">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B256" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C256" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D256" s="407" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" t="s" s="0">
+        <v>637</v>
+      </c>
+      <c r="F256" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G256" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H256" t="s" s="0">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B257" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C257" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D257" s="410" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" t="s" s="0">
+        <v>639</v>
+      </c>
+      <c r="F257" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G257" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H257" t="s" s="0">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B258" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C258" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D258" s="413" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" t="s" s="0">
+        <v>641</v>
+      </c>
+      <c r="F258" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G258" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H258" t="s" s="0">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B259" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C259" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D259" s="416" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" t="s" s="0">
+        <v>643</v>
+      </c>
+      <c r="F259" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G259" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H259" t="s" s="0">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B260" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C260" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D260" s="419" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" t="s" s="0">
+        <v>645</v>
+      </c>
+      <c r="F260" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G260" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H260" t="s" s="0">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B261" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C261" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D261" s="422" t="s">
+        <v>11</v>
+      </c>
+      <c r="E261" t="s" s="0">
+        <v>647</v>
+      </c>
+      <c r="F261" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G261" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H261" t="s" s="0">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B262" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C262" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D262" s="425" t="s">
+        <v>11</v>
+      </c>
+      <c r="E262" t="s" s="0">
+        <v>649</v>
+      </c>
+      <c r="F262" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G262" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H262" t="s" s="0">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B263" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C263" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D263" s="428" t="s">
+        <v>11</v>
+      </c>
+      <c r="E263" t="s" s="0">
+        <v>651</v>
+      </c>
+      <c r="F263" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G263" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H263" t="s" s="0">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B264" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C264" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D264" s="431" t="s">
+        <v>653</v>
+      </c>
+      <c r="E264" t="s" s="0">
+        <v>654</v>
+      </c>
+      <c r="F264" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G264" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H264" t="s" s="0">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B265" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C265" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D265" s="434" t="s">
+        <v>656</v>
+      </c>
+      <c r="E265" t="s" s="0">
+        <v>657</v>
+      </c>
+      <c r="F265" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G265" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H265" t="s" s="0">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B266" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C266" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D266" s="437" t="s">
+        <v>659</v>
+      </c>
+      <c r="E266" t="s" s="0">
+        <v>660</v>
+      </c>
+      <c r="F266" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G266" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H266" t="s" s="0">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B267" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C267" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D267" s="440" t="s">
+        <v>662</v>
+      </c>
+      <c r="E267" t="s" s="0">
+        <v>663</v>
+      </c>
+      <c r="F267" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G267" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H267" t="s" s="0">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B268" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C268" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D268" s="443" t="s">
+        <v>665</v>
+      </c>
+      <c r="E268" t="s" s="0">
+        <v>666</v>
+      </c>
+      <c r="F268" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G268" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H268" t="s" s="0">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B269" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C269" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D269" s="446" t="s">
+        <v>668</v>
+      </c>
+      <c r="E269" t="s" s="0">
+        <v>669</v>
+      </c>
+      <c r="F269" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G269" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H269" t="s" s="0">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B270" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C270" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D270" s="449" t="s">
+        <v>671</v>
+      </c>
+      <c r="E270" t="s" s="0">
+        <v>672</v>
+      </c>
+      <c r="F270" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G270" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H270" t="s" s="0">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B271" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C271" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D271" s="452" t="s">
+        <v>674</v>
+      </c>
+      <c r="E271" t="s" s="0">
+        <v>675</v>
+      </c>
+      <c r="F271" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G271" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H271" t="s" s="0">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B272" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C272" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D272" s="455" t="s">
+        <v>677</v>
+      </c>
+      <c r="E272" t="s" s="0">
+        <v>678</v>
+      </c>
+      <c r="F272" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G272" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H272" t="s" s="0">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B273" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C273" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D273" s="457" t="s">
+        <v>26</v>
+      </c>
+      <c r="E273" t="s" s="0">
+        <v>680</v>
+      </c>
+      <c r="F273" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G273" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H273" t="s" s="0">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B274" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C274" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D274" s="460" t="s">
+        <v>26</v>
+      </c>
+      <c r="E274" t="s" s="0">
+        <v>682</v>
+      </c>
+      <c r="F274" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G274" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H274" t="s" s="0">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B275" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C275" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D275" s="463" t="s">
+        <v>26</v>
+      </c>
+      <c r="E275" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="F275" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G275" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H275" t="s" s="0">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B276" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C276" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D276" s="467" t="s">
+        <v>686</v>
+      </c>
+      <c r="E276" t="s" s="0">
+        <v>687</v>
+      </c>
+      <c r="F276" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G276" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H276" t="s" s="0">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B277" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C277" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D277" s="470" t="s">
+        <v>11</v>
+      </c>
+      <c r="E277" t="s" s="0">
+        <v>689</v>
+      </c>
+      <c r="F277" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G277" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H277" t="s" s="0">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B278" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C278" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D278" s="473" t="s">
+        <v>691</v>
+      </c>
+      <c r="E278" t="s" s="0">
+        <v>692</v>
+      </c>
+      <c r="F278" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G278" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H278" t="s" s="0">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B279" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C279" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D279" s="476" t="s">
+        <v>694</v>
+      </c>
+      <c r="E279" t="s" s="0">
+        <v>695</v>
+      </c>
+      <c r="F279" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G279" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H279" t="s" s="0">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B280" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C280" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D280" s="479" t="s">
+        <v>91</v>
+      </c>
+      <c r="E280" s="0"/>
+      <c r="F280" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="G280" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H280" t="s" s="0">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B281" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C281" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D281" s="482" t="s">
+        <v>698</v>
+      </c>
+      <c r="E281" t="s" s="0">
+        <v>699</v>
+      </c>
+      <c r="F281" t="s" s="0">
+        <v>700</v>
+      </c>
+      <c r="G281" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H281" t="s" s="0">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B282" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C282" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D282" s="485" t="s">
+        <v>11</v>
+      </c>
+      <c r="E282" t="s" s="0">
+        <v>702</v>
+      </c>
+      <c r="F282" t="s" s="0">
+        <v>700</v>
+      </c>
+      <c r="G282" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H282" t="s" s="0">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B283" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C283" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D283" s="488" t="s">
+        <v>11</v>
+      </c>
+      <c r="E283" t="s" s="0">
+        <v>704</v>
+      </c>
+      <c r="F283" t="s" s="0">
+        <v>700</v>
+      </c>
+      <c r="G283" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H283" t="s" s="0">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B284" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C284" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D284" s="490" t="s">
+        <v>26</v>
+      </c>
+      <c r="E284" t="s" s="0">
+        <v>706</v>
+      </c>
+      <c r="F284" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G284" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H284" t="s" s="0">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B285" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C285" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D285" s="493" t="s">
+        <v>26</v>
+      </c>
+      <c r="E285" t="s" s="0">
+        <v>708</v>
+      </c>
+      <c r="F285" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G285" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H285" t="s" s="0">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B286" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C286" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D286" s="496" t="s">
+        <v>26</v>
+      </c>
+      <c r="E286" t="s" s="0">
+        <v>710</v>
+      </c>
+      <c r="F286" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G286" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H286" t="s" s="0">
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Results.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Results.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="809">
   <si>
     <t>Test Data</t>
   </si>
@@ -2490,13 +2490,312 @@
   <si>
     <t>2026-04-09 12:20:06</t>
   </si>
+  <si>
+    <t>FAIL → Exception: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=146.0.7680.178)
+Build info: version: '4.39.0', revision: '126f156aee'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.9'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [32f8a2cdf126d08f7dbb4648b31926ad, get {url=https://test4.paymentsclub.net/payments/7a4c3eb2e7bee53d3dc116dd3a9de128/}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 146.0.7680.178, chrome: {chromedriverVersion: 146.0.7680.165 (4b989da09e1..., userDataDir: C:\Users\LENOVO\AppData\Loc...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:54880}, goog:processID: 12264, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:54880/devtoo..., se:cdpVersion: 146.0.7680.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 32f8a2cdf126d08f7dbb4648b31926ad</t>
+  </si>
+  <si>
+    <t>69d76f79ead38b2473c4d78b</t>
+  </si>
+  <si>
+    <t>2026-04-09 14:51:01</t>
+  </si>
+  <si>
+    <t>69d8b9737cdd85078aaf636d</t>
+  </si>
+  <si>
+    <t>2026-04-10 14:19:45</t>
+  </si>
+  <si>
+    <t>69dc77ec95259019d887d78e</t>
+  </si>
+  <si>
+    <t>2026-04-13 10:29:23</t>
+  </si>
+  <si>
+    <t>FAIL → Exception: Unsupported PSP: yoyapayPayin</t>
+  </si>
+  <si>
+    <t>69e2187428bea6ca2e31c7dd</t>
+  </si>
+  <si>
+    <t>yoyapayPayin</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:54:47</t>
+  </si>
+  <si>
+    <t>69e2189128bea6ca2e31c7f9</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:55:13</t>
+  </si>
+  <si>
+    <t>69e2159828bea6ca2e31c71d</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:55:32</t>
+  </si>
+  <si>
+    <t>69e2178528bea6ca2e31c7aa</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:55:47</t>
+  </si>
+  <si>
+    <t>69e2160428bea6ca2e31c734</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:57:19</t>
+  </si>
+  <si>
+    <t>69e217ef28bea6ca2e31c7c4</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:57:34</t>
+  </si>
+  <si>
+    <t>69e2166f28bea6ca2e31c75d</t>
+  </si>
+  <si>
+    <t>2026-04-17 16:59:07</t>
+  </si>
+  <si>
+    <t>69e218cc28bea6ca2e31c83a</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:01:10</t>
+  </si>
+  <si>
+    <t>69e2193628bea6ca2e31c866</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:02:55</t>
+  </si>
+  <si>
+    <t>69e21a0e28bea6ca2e31c898</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:06:32</t>
+  </si>
+  <si>
+    <t>69e21a7728bea6ca2e31c8ae</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:08:16</t>
+  </si>
+  <si>
+    <t>69e218ba28bea6ca2e31c827</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:08:50</t>
+  </si>
+  <si>
+    <t>69e21c1d28bea6ca2e31c8dc</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:10:20</t>
+  </si>
+  <si>
+    <t>69e21c5a28bea6ca2e31c8fb</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:11:21</t>
+  </si>
+  <si>
+    <t>69e21caf28bea6ca2e31c91e</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:12:47</t>
+  </si>
+  <si>
+    <t>69e21ce928bea6ca2e31c93f</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:13:44</t>
+  </si>
+  <si>
+    <t>69e21d2228bea6ca2e31c95e</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:14:42</t>
+  </si>
+  <si>
+    <t>69e21f0e28bea6ca2e31cf87</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:22:53</t>
+  </si>
+  <si>
+    <t>69e21fb428bea6ca2e31d9b8</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:25:39</t>
+  </si>
+  <si>
+    <t>69e2201528bea6ca2e31de49</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:27:16</t>
+  </si>
+  <si>
+    <t>69e2214b28bea6ca2e31e2ef</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:32:27</t>
+  </si>
+  <si>
+    <t>69e2218128bea6ca2e31e778</t>
+  </si>
+  <si>
+    <t>2026-04-17 17:33:20</t>
+  </si>
+  <si>
+    <t>69e5e96644765c8e82cd517d</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:23:13</t>
+  </si>
+  <si>
+    <t>69e5edaf44765c8e82cd5b7c</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:41:26</t>
+  </si>
+  <si>
+    <t>69e5edf544765c8e82cd5b98</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:42:35</t>
+  </si>
+  <si>
+    <t>69e5ef9c44765c8e82cd6598</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:49:38</t>
+  </si>
+  <si>
+    <t>69e5eeef44765c8e82cd603c</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:51:45</t>
+  </si>
+  <si>
+    <t>69e5f0cb44765c8e82cd6ad0</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:54:40</t>
+  </si>
+  <si>
+    <t>69e5f36944765c8e82cd7a49</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:05:52</t>
+  </si>
+  <si>
+    <t>69e5f3d744765c8e82cd7f7f</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:07:42</t>
+  </si>
+  <si>
+    <t>69e5f52a44765c8e82cd84ca</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:13:22</t>
+  </si>
+  <si>
+    <t>69e5f72a44765c8e82cd946d</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:21:50</t>
+  </si>
+  <si>
+    <t>69e5f74c44765c8e82cd998b</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:22:24</t>
+  </si>
+  <si>
+    <t>69e5f79444765c8e82cda3e6</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:23:34</t>
+  </si>
+  <si>
+    <t>69e5f7ea44765c8e82cda8fa</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:25:03</t>
+  </si>
+  <si>
+    <t>69e5f88244765c8e82cdae25</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:27:28</t>
+  </si>
+  <si>
+    <t>69e5f8ad44765c8e82cdb333</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:28:11</t>
+  </si>
+  <si>
+    <t>69e5f90e44765c8e82cdb35c</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:29:48</t>
+  </si>
+  <si>
+    <t>69e5f95744765c8e82cdb87d</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:31:02</t>
+  </si>
+  <si>
+    <t>69e5f9d144765c8e82cdbda1</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:33:04</t>
+  </si>
+  <si>
+    <t>69e5fa0244765c8e82cdc2be</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:33:52</t>
+  </si>
+  <si>
+    <t>69e5fa9044765c8e82cdc875</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:36:59</t>
+  </si>
+  <si>
+    <t>69e5fb5844765c8e82cdd823</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:40:22</t>
+  </si>
+  <si>
+    <t>69e5fb9044765c8e82cddd5b</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:41:04</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="498" x14ac:knownFonts="1">
+  <fonts count="639" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3809,6 +4108,805 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -5432,7 +6530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="498">
+  <cellXfs count="639">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6923,6 +8021,429 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="497" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="541" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="571" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="577" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="581" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="583" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="589" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="2" borderId="0" xfId="0" applyFill="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7268,7 +8789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.7265625"/>
@@ -14560,6 +16081,1228 @@
       </c>
       <c r="H286" t="s" s="0">
         <v>711</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B287" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C287" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D287" s="500" t="s">
+        <v>712</v>
+      </c>
+      <c r="E287" t="s" s="0">
+        <v>713</v>
+      </c>
+      <c r="F287" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G287" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H287" t="s" s="0">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B288" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C288" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D288" s="503" t="s">
+        <v>11</v>
+      </c>
+      <c r="E288" t="s" s="0">
+        <v>715</v>
+      </c>
+      <c r="F288" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G288" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H288" t="s" s="0">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B289" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C289" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D289" s="506" t="s">
+        <v>11</v>
+      </c>
+      <c r="E289" t="s" s="0">
+        <v>717</v>
+      </c>
+      <c r="F289" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="G289" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H289" t="s" s="0">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B290" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C290" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D290" s="509" t="s">
+        <v>719</v>
+      </c>
+      <c r="E290" t="s" s="0">
+        <v>720</v>
+      </c>
+      <c r="F290" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G290" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H290" t="s" s="0">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B291" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C291" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D291" s="512" t="s">
+        <v>719</v>
+      </c>
+      <c r="E291" t="s" s="0">
+        <v>723</v>
+      </c>
+      <c r="F291" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G291" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H291" t="s" s="0">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B292" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C292" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D292" s="515" t="s">
+        <v>719</v>
+      </c>
+      <c r="E292" t="s" s="0">
+        <v>725</v>
+      </c>
+      <c r="F292" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G292" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H292" t="s" s="0">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B293" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C293" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D293" s="518" t="s">
+        <v>719</v>
+      </c>
+      <c r="E293" t="s" s="0">
+        <v>727</v>
+      </c>
+      <c r="F293" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G293" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H293" t="s" s="0">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B294" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C294" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D294" s="521" t="s">
+        <v>719</v>
+      </c>
+      <c r="E294" t="s" s="0">
+        <v>729</v>
+      </c>
+      <c r="F294" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G294" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H294" t="s" s="0">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B295" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C295" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D295" s="524" t="s">
+        <v>719</v>
+      </c>
+      <c r="E295" t="s" s="0">
+        <v>731</v>
+      </c>
+      <c r="F295" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G295" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H295" t="s" s="0">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B296" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C296" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D296" s="527" t="s">
+        <v>719</v>
+      </c>
+      <c r="E296" t="s" s="0">
+        <v>733</v>
+      </c>
+      <c r="F296" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G296" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H296" t="s" s="0">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B297" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C297" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D297" s="530" t="s">
+        <v>719</v>
+      </c>
+      <c r="E297" t="s" s="0">
+        <v>735</v>
+      </c>
+      <c r="F297" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G297" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H297" t="s" s="0">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B298" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C298" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D298" s="533" t="s">
+        <v>719</v>
+      </c>
+      <c r="E298" t="s" s="0">
+        <v>737</v>
+      </c>
+      <c r="F298" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G298" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H298" t="s" s="0">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B299" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C299" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D299" s="536" t="s">
+        <v>719</v>
+      </c>
+      <c r="E299" t="s" s="0">
+        <v>739</v>
+      </c>
+      <c r="F299" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G299" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H299" t="s" s="0">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B300" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C300" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D300" s="539" t="s">
+        <v>719</v>
+      </c>
+      <c r="E300" t="s" s="0">
+        <v>741</v>
+      </c>
+      <c r="F300" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G300" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H300" t="s" s="0">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B301" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C301" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D301" s="542" t="s">
+        <v>719</v>
+      </c>
+      <c r="E301" t="s" s="0">
+        <v>743</v>
+      </c>
+      <c r="F301" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G301" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H301" t="s" s="0">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B302" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C302" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D302" s="545" t="s">
+        <v>719</v>
+      </c>
+      <c r="E302" t="s" s="0">
+        <v>745</v>
+      </c>
+      <c r="F302" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G302" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H302" t="s" s="0">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B303" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C303" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D303" s="548" t="s">
+        <v>719</v>
+      </c>
+      <c r="E303" t="s" s="0">
+        <v>747</v>
+      </c>
+      <c r="F303" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G303" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H303" t="s" s="0">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B304" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C304" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D304" s="551" t="s">
+        <v>719</v>
+      </c>
+      <c r="E304" t="s" s="0">
+        <v>749</v>
+      </c>
+      <c r="F304" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G304" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H304" t="s" s="0">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B305" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C305" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D305" s="554" t="s">
+        <v>719</v>
+      </c>
+      <c r="E305" t="s" s="0">
+        <v>751</v>
+      </c>
+      <c r="F305" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G305" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H305" t="s" s="0">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B306" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C306" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D306" s="557" t="s">
+        <v>719</v>
+      </c>
+      <c r="E306" t="s" s="0">
+        <v>753</v>
+      </c>
+      <c r="F306" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G306" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H306" t="s" s="0">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B307" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C307" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D307" s="560" t="s">
+        <v>719</v>
+      </c>
+      <c r="E307" t="s" s="0">
+        <v>755</v>
+      </c>
+      <c r="F307" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G307" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H307" t="s" s="0">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B308" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C308" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D308" s="563" t="s">
+        <v>719</v>
+      </c>
+      <c r="E308" t="s" s="0">
+        <v>757</v>
+      </c>
+      <c r="F308" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G308" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H308" t="s" s="0">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B309" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C309" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D309" s="566" t="s">
+        <v>719</v>
+      </c>
+      <c r="E309" t="s" s="0">
+        <v>759</v>
+      </c>
+      <c r="F309" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G309" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H309" t="s" s="0">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B310" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C310" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D310" s="569" t="s">
+        <v>719</v>
+      </c>
+      <c r="E310" t="s" s="0">
+        <v>761</v>
+      </c>
+      <c r="F310" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G310" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H310" t="s" s="0">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B311" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C311" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D311" s="572" t="s">
+        <v>719</v>
+      </c>
+      <c r="E311" t="s" s="0">
+        <v>763</v>
+      </c>
+      <c r="F311" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G311" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H311" t="s" s="0">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B312" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C312" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D312" s="575" t="s">
+        <v>719</v>
+      </c>
+      <c r="E312" t="s" s="0">
+        <v>765</v>
+      </c>
+      <c r="F312" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G312" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H312" t="s" s="0">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B313" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C313" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D313" s="578" t="s">
+        <v>719</v>
+      </c>
+      <c r="E313" t="s" s="0">
+        <v>767</v>
+      </c>
+      <c r="F313" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G313" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H313" t="s" s="0">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B314" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C314" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D314" s="581" t="s">
+        <v>719</v>
+      </c>
+      <c r="E314" t="s" s="0">
+        <v>769</v>
+      </c>
+      <c r="F314" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G314" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H314" t="s" s="0">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B315" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C315" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D315" s="584" t="s">
+        <v>719</v>
+      </c>
+      <c r="E315" t="s" s="0">
+        <v>771</v>
+      </c>
+      <c r="F315" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G315" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H315" t="s" s="0">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B316" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C316" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D316" s="587" t="s">
+        <v>719</v>
+      </c>
+      <c r="E316" t="s" s="0">
+        <v>773</v>
+      </c>
+      <c r="F316" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G316" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H316" t="s" s="0">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B317" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C317" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D317" s="590" t="s">
+        <v>719</v>
+      </c>
+      <c r="E317" t="s" s="0">
+        <v>775</v>
+      </c>
+      <c r="F317" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G317" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H317" t="s" s="0">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B318" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C318" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D318" s="593" t="s">
+        <v>719</v>
+      </c>
+      <c r="E318" t="s" s="0">
+        <v>777</v>
+      </c>
+      <c r="F318" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G318" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H318" t="s" s="0">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B319" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C319" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D319" s="596" t="s">
+        <v>719</v>
+      </c>
+      <c r="E319" t="s" s="0">
+        <v>779</v>
+      </c>
+      <c r="F319" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G319" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H319" t="s" s="0">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B320" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C320" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D320" s="599" t="s">
+        <v>719</v>
+      </c>
+      <c r="E320" t="s" s="0">
+        <v>781</v>
+      </c>
+      <c r="F320" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G320" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H320" t="s" s="0">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B321" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C321" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D321" s="602" t="s">
+        <v>719</v>
+      </c>
+      <c r="E321" t="s" s="0">
+        <v>783</v>
+      </c>
+      <c r="F321" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G321" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H321" t="s" s="0">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B322" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C322" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D322" s="605" t="s">
+        <v>719</v>
+      </c>
+      <c r="E322" t="s" s="0">
+        <v>785</v>
+      </c>
+      <c r="F322" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G322" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H322" t="s" s="0">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B323" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C323" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D323" s="608" t="s">
+        <v>719</v>
+      </c>
+      <c r="E323" t="s" s="0">
+        <v>787</v>
+      </c>
+      <c r="F323" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G323" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H323" t="s" s="0">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B324" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C324" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D324" s="611" t="s">
+        <v>719</v>
+      </c>
+      <c r="E324" t="s" s="0">
+        <v>789</v>
+      </c>
+      <c r="F324" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G324" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H324" t="s" s="0">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B325" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C325" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D325" s="614" t="s">
+        <v>719</v>
+      </c>
+      <c r="E325" t="s" s="0">
+        <v>791</v>
+      </c>
+      <c r="F325" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G325" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H325" t="s" s="0">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B326" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C326" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D326" s="617" t="s">
+        <v>719</v>
+      </c>
+      <c r="E326" t="s" s="0">
+        <v>793</v>
+      </c>
+      <c r="F326" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G326" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H326" t="s" s="0">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B327" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C327" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D327" s="620" t="s">
+        <v>719</v>
+      </c>
+      <c r="E327" t="s" s="0">
+        <v>795</v>
+      </c>
+      <c r="F327" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G327" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H327" t="s" s="0">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B328" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C328" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D328" s="623" t="s">
+        <v>719</v>
+      </c>
+      <c r="E328" t="s" s="0">
+        <v>797</v>
+      </c>
+      <c r="F328" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G328" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H328" t="s" s="0">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B329" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C329" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D329" s="626" t="s">
+        <v>719</v>
+      </c>
+      <c r="E329" t="s" s="0">
+        <v>799</v>
+      </c>
+      <c r="F329" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G329" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H329" t="s" s="0">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B330" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C330" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D330" s="629" t="s">
+        <v>719</v>
+      </c>
+      <c r="E330" t="s" s="0">
+        <v>801</v>
+      </c>
+      <c r="F330" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G330" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H330" t="s" s="0">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B331" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C331" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D331" s="631" t="s">
+        <v>26</v>
+      </c>
+      <c r="E331" t="s" s="0">
+        <v>803</v>
+      </c>
+      <c r="F331" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G331" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H331" t="s" s="0">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B332" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C332" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D332" s="634" t="s">
+        <v>26</v>
+      </c>
+      <c r="E332" t="s" s="0">
+        <v>805</v>
+      </c>
+      <c r="F332" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G332" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H332" t="s" s="0">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B333" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C333" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D333" s="637" t="s">
+        <v>26</v>
+      </c>
+      <c r="E333" t="s" s="0">
+        <v>807</v>
+      </c>
+      <c r="F333" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="G333" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H333" t="s" s="0">
+        <v>808</v>
       </c>
     </row>
   </sheetData>
